--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -62874,7 +62874,7 @@
         <v>57.9000015258789</v>
       </c>
       <c r="D2718" t="n">
-        <v>54.7999992370605</v>
+        <v>54.4000015258789</v>
       </c>
       <c r="E2718" t="n">
         <v>54.7999992370605</v>
@@ -62883,6 +62883,29 @@
         <v>54.4000015258789</v>
       </c>
       <c r="G2718" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>50929</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>54.5</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>52.7000007629395</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>54.4000015258789</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>53.4000015258789</v>
+      </c>
+      <c r="G2719" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -62909,6 +62909,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>36271</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>54.2000007629395</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>52.5999984741211</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>53.5999984741211</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>53.0999984741211</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>29514</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>53.7999992370605</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>53.7000007629395</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>57481</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>54.2000007629395</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>53.7000007629395</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>53.4000015258789</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>30320</v>
+        <v>33416</v>
       </c>
       <c r="C2715" t="n">
-        <v>58.5</v>
+        <v>58</v>
       </c>
       <c r="D2715" t="n">
-        <v>57.0999984741211</v>
+        <v>56.5999984741211</v>
       </c>
       <c r="E2715" t="n">
-        <v>57.5</v>
+        <v>56.5999984741211</v>
       </c>
       <c r="F2715" t="n">
-        <v>58.0999984741211</v>
+        <v>57.5999984741211</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>70824</v>
+        <v>30320</v>
       </c>
       <c r="C2716" t="n">
-        <v>58.7000007629395</v>
+        <v>58.5</v>
       </c>
       <c r="D2716" t="n">
-        <v>56.7000007629395</v>
+        <v>57.0999984741211</v>
       </c>
       <c r="E2716" t="n">
-        <v>58.2000007629395</v>
+        <v>57.5</v>
       </c>
       <c r="F2716" t="n">
-        <v>57.5</v>
+        <v>58.0999984741211</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>125316</v>
+        <v>70824</v>
       </c>
       <c r="C2717" t="n">
-        <v>59</v>
+        <v>58.7000007629395</v>
       </c>
       <c r="D2717" t="n">
-        <v>54.2000007629395</v>
+        <v>56.7000007629395</v>
       </c>
       <c r="E2717" t="n">
-        <v>57.2999992370605</v>
+        <v>58.2000007629395</v>
       </c>
       <c r="F2717" t="n">
-        <v>54.2000007629395</v>
+        <v>57.5</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>61266</v>
+        <v>125316</v>
       </c>
       <c r="C2718" t="n">
-        <v>57.9000015258789</v>
+        <v>59</v>
       </c>
       <c r="D2718" t="n">
-        <v>54.4000015258789</v>
+        <v>54.2000007629395</v>
       </c>
       <c r="E2718" t="n">
-        <v>54.7999992370605</v>
+        <v>57.2999992370605</v>
       </c>
       <c r="F2718" t="n">
-        <v>54.4000015258789</v>
+        <v>54.2000007629395</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>50929</v>
+        <v>61266</v>
       </c>
       <c r="C2719" t="n">
-        <v>54.5</v>
+        <v>57.9000015258789</v>
       </c>
       <c r="D2719" t="n">
-        <v>52.7000007629395</v>
+        <v>54.4000015258789</v>
       </c>
       <c r="E2719" t="n">
+        <v>54.7999992370605</v>
+      </c>
+      <c r="F2719" t="n">
         <v>54.4000015258789</v>
-      </c>
-      <c r="F2719" t="n">
-        <v>53.4000015258789</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>36271</v>
+        <v>50929</v>
       </c>
       <c r="C2720" t="n">
-        <v>54.2000007629395</v>
+        <v>54.5</v>
       </c>
       <c r="D2720" t="n">
-        <v>52.5999984741211</v>
+        <v>52.7000007629395</v>
       </c>
       <c r="E2720" t="n">
-        <v>53.5999984741211</v>
+        <v>54.4000015258789</v>
       </c>
       <c r="F2720" t="n">
-        <v>53.0999984741211</v>
+        <v>53.4000015258789</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>29514</v>
+        <v>36271</v>
       </c>
       <c r="C2721" t="n">
-        <v>53.7999992370605</v>
+        <v>54.2000007629395</v>
       </c>
       <c r="D2721" t="n">
-        <v>52.7999992370605</v>
+        <v>52.5999984741211</v>
       </c>
       <c r="E2721" t="n">
-        <v>52.7999992370605</v>
+        <v>53.5999984741211</v>
       </c>
       <c r="F2721" t="n">
-        <v>53.7000007629395</v>
+        <v>53.0999984741211</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>57481</v>
+        <v>29514</v>
       </c>
       <c r="C2722" t="n">
-        <v>54.2000007629395</v>
+        <v>53.7999992370605</v>
       </c>
       <c r="D2722" t="n">
         <v>52.7999992370605</v>
       </c>
       <c r="E2722" t="n">
+        <v>52.7999992370605</v>
+      </c>
+      <c r="F2722" t="n">
         <v>53.7000007629395</v>
       </c>
-      <c r="F2722" t="n">
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>88763</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>54.7999992370605</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>53.2000007629395</v>
+      </c>
+      <c r="E2723" t="n">
         <v>53.4000015258789</v>
       </c>
-      <c r="G2722" t="s">
+      <c r="F2723" t="n">
+        <v>54.9000015258789</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>55</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>55.5999984741211</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>121679</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>59.2000007629395</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>56.2000007629395</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>56.2000007629395</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>57.5999984741211</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>38254</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>58.9000015258789</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>57.0999984741211</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>57.5999984741211</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>57.5999984741211</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>57.7999992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>55810</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>58</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>56.7000007629395</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>58</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>58</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>57</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>23658</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>58.2999992370605</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>57.4000015258789</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>98073</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>58.5999984741211</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>57</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>57</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>58.4000015258789</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.09495496749878</v>
+        <v>7.09495449066162</v>
       </c>
       <c r="H2" t="n">
         <v>5513</v>
@@ -456,7 +456,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G3" t="n">
-        <v>7.08630180358887</v>
+        <v>7.08630228042603</v>
       </c>
       <c r="H3" t="n">
         <v>15304</v>
@@ -485,7 +485,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G4" t="n">
-        <v>7.13388967514038</v>
+        <v>7.13388919830322</v>
       </c>
       <c r="H4" t="n">
         <v>1896</v>
@@ -514,7 +514,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G5" t="n">
-        <v>7.10793256759644</v>
+        <v>7.10793399810791</v>
       </c>
       <c r="H5" t="n">
         <v>16215</v>
@@ -543,7 +543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>7.00843191146851</v>
+        <v>7.00843095779419</v>
       </c>
       <c r="H6" t="n">
         <v>12867</v>
@@ -572,7 +572,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>6.85701417922974</v>
+        <v>6.85701370239258</v>
       </c>
       <c r="H7" t="n">
         <v>13353</v>
@@ -601,7 +601,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G8" t="n">
-        <v>7.00843191146851</v>
+        <v>7.00843095779419</v>
       </c>
       <c r="H8" t="n">
         <v>1721</v>
@@ -659,7 +659,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>6.89594984054565</v>
+        <v>6.89594888687134</v>
       </c>
       <c r="H10" t="n">
         <v>3804</v>
@@ -688,7 +688,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G11" t="n">
-        <v>6.66666126251221</v>
+        <v>6.66666173934937</v>
       </c>
       <c r="H11" t="n">
         <v>7723</v>
@@ -746,7 +746,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>6.66233587265015</v>
+        <v>6.66233539581299</v>
       </c>
       <c r="H13" t="n">
         <v>30396</v>
@@ -775,7 +775,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>6.25134658813477</v>
+        <v>6.25134754180908</v>
       </c>
       <c r="H14" t="n">
         <v>20146</v>
@@ -804,7 +804,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>6.31623983383179</v>
+        <v>6.3162407875061</v>
       </c>
       <c r="H15" t="n">
         <v>28633</v>
@@ -862,7 +862,7 @@
         <v>7.35500001907349</v>
       </c>
       <c r="G17" t="n">
-        <v>6.36382818222046</v>
+        <v>6.36382865905762</v>
       </c>
       <c r="H17" t="n">
         <v>21809</v>
@@ -891,7 +891,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>6.39843845367432</v>
+        <v>6.39843702316284</v>
       </c>
       <c r="H18" t="n">
         <v>3118</v>
@@ -920,7 +920,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G19" t="n">
-        <v>6.16049671173096</v>
+        <v>6.16049718856812</v>
       </c>
       <c r="H19" t="n">
         <v>9829</v>
@@ -949,7 +949,7 @@
         <v>7.07999992370605</v>
       </c>
       <c r="G20" t="n">
-        <v>6.12588787078857</v>
+        <v>6.12588739395142</v>
       </c>
       <c r="H20" t="n">
         <v>7398</v>
@@ -978,7 +978,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G21" t="n">
-        <v>6.31623983383179</v>
+        <v>6.3162407875061</v>
       </c>
       <c r="H21" t="n">
         <v>15596</v>
@@ -1007,7 +1007,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>6.41141510009766</v>
+        <v>6.41141557693481</v>
       </c>
       <c r="H22" t="n">
         <v>4042</v>
@@ -1036,7 +1036,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>6.49794006347656</v>
+        <v>6.4979395866394</v>
       </c>
       <c r="H23" t="n">
         <v>8653</v>
@@ -1094,7 +1094,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G25" t="n">
-        <v>6.46333122253418</v>
+        <v>6.46333026885986</v>
       </c>
       <c r="H25" t="n">
         <v>5091</v>
@@ -1239,7 +1239,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>6.31623983383179</v>
+        <v>6.3162407875061</v>
       </c>
       <c r="H30" t="n">
         <v>11382</v>
@@ -1297,7 +1297,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G32" t="n">
-        <v>6.66666126251221</v>
+        <v>6.66666173934937</v>
       </c>
       <c r="H32" t="n">
         <v>5106</v>
@@ -1326,7 +1326,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G33" t="n">
-        <v>6.74885940551758</v>
+        <v>6.74885845184326</v>
       </c>
       <c r="H33" t="n">
         <v>7781</v>
@@ -1384,7 +1384,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G35" t="n">
-        <v>6.74885940551758</v>
+        <v>6.74885845184326</v>
       </c>
       <c r="H35" t="n">
         <v>730</v>
@@ -1442,7 +1442,7 @@
         <v>7.70499992370605</v>
       </c>
       <c r="G37" t="n">
-        <v>6.66666126251221</v>
+        <v>6.66666173934937</v>
       </c>
       <c r="H37" t="n">
         <v>41008</v>
@@ -1471,7 +1471,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G38" t="n">
-        <v>6.95651626586914</v>
+        <v>6.95651578903198</v>
       </c>
       <c r="H38" t="n">
         <v>19565</v>
@@ -1500,7 +1500,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H39" t="n">
         <v>690</v>
@@ -1529,7 +1529,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>7.02573537826538</v>
+        <v>7.02573585510254</v>
       </c>
       <c r="H40" t="n">
         <v>7574</v>
@@ -1558,7 +1558,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G41" t="n">
-        <v>6.83105564117432</v>
+        <v>6.83105707168579</v>
       </c>
       <c r="H41" t="n">
         <v>9646</v>
@@ -1587,7 +1587,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>6.91325426101685</v>
+        <v>6.91325378417969</v>
       </c>
       <c r="H42" t="n">
         <v>3640</v>
@@ -1616,7 +1616,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>7.03438806533813</v>
+        <v>7.03438711166382</v>
       </c>
       <c r="H43" t="n">
         <v>13506</v>
@@ -1645,7 +1645,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>6.6839656829834</v>
+        <v>6.68396615982056</v>
       </c>
       <c r="H44" t="n">
         <v>13599</v>
@@ -1674,7 +1674,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>6.77914333343506</v>
+        <v>6.77914190292358</v>
       </c>
       <c r="H45" t="n">
         <v>2568</v>
@@ -1703,7 +1703,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.62772464752197</v>
+        <v>6.62772607803345</v>
       </c>
       <c r="H46" t="n">
         <v>11062</v>
@@ -1790,7 +1790,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G49" t="n">
-        <v>6.62772464752197</v>
+        <v>6.62772607803345</v>
       </c>
       <c r="H49" t="n">
         <v>5221</v>
@@ -1819,7 +1819,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G50" t="n">
-        <v>6.63637781143188</v>
+        <v>6.63637828826904</v>
       </c>
       <c r="H50" t="n">
         <v>2582</v>
@@ -1877,7 +1877,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G52" t="n">
-        <v>6.73155403137207</v>
+        <v>6.73155450820923</v>
       </c>
       <c r="H52" t="n">
         <v>12666</v>
@@ -1906,7 +1906,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G53" t="n">
-        <v>6.73155403137207</v>
+        <v>6.73155450820923</v>
       </c>
       <c r="H53" t="n">
         <v>41259</v>
@@ -1935,7 +1935,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.72722816467285</v>
+        <v>6.72722768783569</v>
       </c>
       <c r="H54" t="n">
         <v>338</v>
@@ -1964,7 +1964,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>6.76183795928955</v>
+        <v>6.76183843612671</v>
       </c>
       <c r="H55" t="n">
         <v>2198</v>
@@ -2022,7 +2022,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H57" t="n">
         <v>1915</v>
@@ -2080,7 +2080,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H59" t="n">
         <v>1556</v>
@@ -2109,7 +2109,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>6.7445330619812</v>
+        <v>6.74453353881836</v>
       </c>
       <c r="H60" t="n">
         <v>157</v>
@@ -2138,7 +2138,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>6.66233587265015</v>
+        <v>6.66233539581299</v>
       </c>
       <c r="H61" t="n">
         <v>17259</v>
@@ -2167,7 +2167,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>6.6450309753418</v>
+        <v>6.64503002166748</v>
       </c>
       <c r="H62" t="n">
         <v>11309</v>
@@ -2196,7 +2196,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>6.76616382598877</v>
+        <v>6.76616430282593</v>
       </c>
       <c r="H63" t="n">
         <v>4360</v>
@@ -2225,7 +2225,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G64" t="n">
-        <v>6.8224048614502</v>
+        <v>6.82240390777588</v>
       </c>
       <c r="H64" t="n">
         <v>6114</v>
@@ -2254,7 +2254,7 @@
         <v>7.92999982833862</v>
       </c>
       <c r="G65" t="n">
-        <v>6.8613395690918</v>
+        <v>6.86134004592896</v>
       </c>
       <c r="H65" t="n">
         <v>1932</v>
@@ -2283,7 +2283,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G66" t="n">
-        <v>6.62340021133423</v>
+        <v>6.62339925765991</v>
       </c>
       <c r="H66" t="n">
         <v>2419</v>
@@ -2341,7 +2341,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G68" t="n">
-        <v>6.49794006347656</v>
+        <v>6.4979395866394</v>
       </c>
       <c r="H68" t="n">
         <v>2771</v>
@@ -2370,7 +2370,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>6.5022668838501</v>
+        <v>6.50226593017578</v>
       </c>
       <c r="H69" t="n">
         <v>4219</v>
@@ -2399,7 +2399,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>6.41574239730835</v>
+        <v>6.41574287414551</v>
       </c>
       <c r="H70" t="n">
         <v>459</v>
@@ -2486,7 +2486,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G73" t="n">
-        <v>6.82673072814941</v>
+        <v>6.82673025131226</v>
       </c>
       <c r="H73" t="n">
         <v>3947</v>
@@ -2515,7 +2515,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G74" t="n">
-        <v>6.89594984054565</v>
+        <v>6.89594888687134</v>
       </c>
       <c r="H74" t="n">
         <v>16592</v>
@@ -2573,7 +2573,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G76" t="n">
-        <v>6.76616382598877</v>
+        <v>6.76616430282593</v>
       </c>
       <c r="H76" t="n">
         <v>302</v>
@@ -2631,7 +2631,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>6.79644680023193</v>
+        <v>6.79644727706909</v>
       </c>
       <c r="H78" t="n">
         <v>8992</v>
@@ -2660,7 +2660,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H79" t="n">
         <v>850</v>
@@ -2689,7 +2689,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H80" t="n">
         <v>329</v>
@@ -2718,7 +2718,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G81" t="n">
-        <v>6.80509996414185</v>
+        <v>6.80509948730469</v>
       </c>
       <c r="H81" t="n">
         <v>6352</v>
@@ -2747,7 +2747,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G82" t="n">
-        <v>6.69694519042969</v>
+        <v>6.69694423675537</v>
       </c>
       <c r="H82" t="n">
         <v>10136</v>
@@ -2805,7 +2805,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G84" t="n">
-        <v>6.66233587265015</v>
+        <v>6.66233539581299</v>
       </c>
       <c r="H84" t="n">
         <v>18991</v>
@@ -2834,7 +2834,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>6.46765613555908</v>
+        <v>6.46765661239624</v>
       </c>
       <c r="H85" t="n">
         <v>12826</v>
@@ -2863,7 +2863,7 @@
         <v>7.30999994277954</v>
       </c>
       <c r="G86" t="n">
-        <v>6.32489204406738</v>
+        <v>6.32489252090454</v>
       </c>
       <c r="H86" t="n">
         <v>21013</v>
@@ -2892,7 +2892,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>6.5022668838501</v>
+        <v>6.50226593017578</v>
       </c>
       <c r="H87" t="n">
         <v>4249</v>
@@ -2921,7 +2921,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>6.51524543762207</v>
+        <v>6.51524496078491</v>
       </c>
       <c r="H88" t="n">
         <v>3423</v>
@@ -2950,7 +2950,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G89" t="n">
-        <v>6.51524543762207</v>
+        <v>6.51524496078491</v>
       </c>
       <c r="H89" t="n">
         <v>4113</v>
@@ -2979,7 +2979,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G90" t="n">
-        <v>6.51524543762207</v>
+        <v>6.51524496078491</v>
       </c>
       <c r="H90" t="n">
         <v>1713</v>
@@ -3008,7 +3008,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>6.46765613555908</v>
+        <v>6.46765661239624</v>
       </c>
       <c r="H91" t="n">
         <v>4973</v>
@@ -3066,7 +3066,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G93" t="n">
-        <v>6.71857500076294</v>
+        <v>6.71857595443726</v>
       </c>
       <c r="H93" t="n">
         <v>12759</v>
@@ -3182,7 +3182,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H97" t="n">
         <v>2484</v>
@@ -3240,7 +3240,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>6.79212045669556</v>
+        <v>6.79212141036987</v>
       </c>
       <c r="H99" t="n">
         <v>4098</v>
@@ -3269,7 +3269,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G100" t="n">
-        <v>6.88877487182617</v>
+        <v>6.88877534866333</v>
       </c>
       <c r="H100" t="n">
         <v>3625</v>
@@ -3298,7 +3298,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H101" t="n">
         <v>3327</v>
@@ -3327,7 +3327,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H102" t="n">
         <v>886</v>
@@ -3356,7 +3356,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G103" t="n">
-        <v>6.83166122436523</v>
+        <v>6.83166074752808</v>
       </c>
       <c r="H103" t="n">
         <v>2092</v>
@@ -3385,7 +3385,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G104" t="n">
-        <v>6.84923458099365</v>
+        <v>6.84923505783081</v>
       </c>
       <c r="H104" t="n">
         <v>47568</v>
@@ -3443,7 +3443,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>7.16994953155518</v>
+        <v>7.16994905471802</v>
       </c>
       <c r="H106" t="n">
         <v>8878</v>
@@ -3472,7 +3472,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>7.36325693130493</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H107" t="n">
         <v>10304</v>
@@ -3501,7 +3501,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G108" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H108" t="n">
         <v>2205</v>
@@ -3530,7 +3530,7 @@
         <v>8.31999969482422</v>
       </c>
       <c r="G109" t="n">
-        <v>7.31053638458252</v>
+        <v>7.31053686141968</v>
       </c>
       <c r="H109" t="n">
         <v>23096</v>
@@ -3617,7 +3617,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G112" t="n">
-        <v>7.34568357467651</v>
+        <v>7.34568309783936</v>
       </c>
       <c r="H112" t="n">
         <v>1577</v>
@@ -3646,7 +3646,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G113" t="n">
-        <v>7.3896164894104</v>
+        <v>7.38961696624756</v>
       </c>
       <c r="H113" t="n">
         <v>1885</v>
@@ -3675,7 +3675,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G114" t="n">
-        <v>7.32810974121094</v>
+        <v>7.3281102180481</v>
       </c>
       <c r="H114" t="n">
         <v>3885</v>
@@ -3704,7 +3704,7 @@
         <v>7.95499992370605</v>
       </c>
       <c r="G115" t="n">
-        <v>6.98982238769531</v>
+        <v>6.98982191085815</v>
       </c>
       <c r="H115" t="n">
         <v>18990</v>
@@ -3762,7 +3762,7 @@
         <v>8.02999973297119</v>
       </c>
       <c r="G117" t="n">
-        <v>7.05572175979614</v>
+        <v>7.0557222366333</v>
       </c>
       <c r="H117" t="n">
         <v>57370</v>
@@ -3791,7 +3791,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H118" t="n">
         <v>16702</v>
@@ -3820,7 +3820,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G119" t="n">
-        <v>7.1523756980896</v>
+        <v>7.15237665176392</v>
       </c>
       <c r="H119" t="n">
         <v>48342</v>
@@ -3849,7 +3849,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G120" t="n">
-        <v>7.32810974121094</v>
+        <v>7.3281102180481</v>
       </c>
       <c r="H120" t="n">
         <v>2357</v>
@@ -3878,7 +3878,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G121" t="n">
-        <v>7.3149299621582</v>
+        <v>7.31492900848389</v>
       </c>
       <c r="H121" t="n">
         <v>2398</v>
@@ -3907,7 +3907,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>7.51263093948364</v>
+        <v>7.51263046264648</v>
       </c>
       <c r="H122" t="n">
         <v>7693</v>
@@ -3936,7 +3936,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G123" t="n">
-        <v>7.63564300537109</v>
+        <v>7.63564395904541</v>
       </c>
       <c r="H123" t="n">
         <v>27887</v>
@@ -3965,7 +3965,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G124" t="n">
-        <v>7.63564300537109</v>
+        <v>7.63564395904541</v>
       </c>
       <c r="H124" t="n">
         <v>10411</v>
@@ -3994,7 +3994,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>7.64443111419678</v>
+        <v>7.64443016052246</v>
       </c>
       <c r="H125" t="n">
         <v>11739</v>
@@ -4023,7 +4023,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65321779251099</v>
+        <v>7.6532187461853</v>
       </c>
       <c r="H126" t="n">
         <v>6833</v>
@@ -4081,7 +4081,7 @@
         <v>9.08500003814697</v>
       </c>
       <c r="G128" t="n">
-        <v>7.98271942138672</v>
+        <v>7.9827184677124</v>
       </c>
       <c r="H128" t="n">
         <v>98861</v>
@@ -4110,7 +4110,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G129" t="n">
-        <v>7.556565284729</v>
+        <v>7.55656433105469</v>
       </c>
       <c r="H129" t="n">
         <v>54591</v>
@@ -4139,7 +4139,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G130" t="n">
-        <v>7.24024295806885</v>
+        <v>7.24024248123169</v>
       </c>
       <c r="H130" t="n">
         <v>12512</v>
@@ -4168,7 +4168,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G131" t="n">
-        <v>6.94149589538574</v>
+        <v>6.94149541854858</v>
       </c>
       <c r="H131" t="n">
         <v>10710</v>
@@ -4197,7 +4197,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G132" t="n">
-        <v>7.04693603515625</v>
+        <v>7.04693555831909</v>
       </c>
       <c r="H132" t="n">
         <v>4855</v>
@@ -4226,7 +4226,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G133" t="n">
-        <v>7.49505758285522</v>
+        <v>7.49505710601807</v>
       </c>
       <c r="H133" t="n">
         <v>14238</v>
@@ -4255,7 +4255,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G134" t="n">
-        <v>7.25781679153442</v>
+        <v>7.25781583786011</v>
       </c>
       <c r="H134" t="n">
         <v>2751</v>
@@ -4313,7 +4313,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G136" t="n">
-        <v>7.3676495552063</v>
+        <v>7.36765098571777</v>
       </c>
       <c r="H136" t="n">
         <v>8303</v>
@@ -4342,7 +4342,7 @@
         <v>8.32499980926514</v>
       </c>
       <c r="G137" t="n">
-        <v>7.3149299621582</v>
+        <v>7.31492900848389</v>
       </c>
       <c r="H137" t="n">
         <v>6243</v>
@@ -4371,7 +4371,7 @@
         <v>8.32999992370605</v>
       </c>
       <c r="G138" t="n">
-        <v>7.31932306289673</v>
+        <v>7.31932353973389</v>
       </c>
       <c r="H138" t="n">
         <v>6414</v>
@@ -4400,7 +4400,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="n">
-        <v>7.46869707107544</v>
+        <v>7.46869802474976</v>
       </c>
       <c r="H139" t="n">
         <v>5308</v>
@@ -4458,7 +4458,7 @@
         <v>8.375</v>
       </c>
       <c r="G141" t="n">
-        <v>7.35886335372925</v>
+        <v>7.35886383056641</v>
       </c>
       <c r="H141" t="n">
         <v>18281</v>
@@ -4487,7 +4487,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>7.16116189956665</v>
+        <v>7.16116285324097</v>
       </c>
       <c r="H142" t="n">
         <v>22169</v>
@@ -4516,7 +4516,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G143" t="n">
-        <v>7.16994953155518</v>
+        <v>7.16994905471802</v>
       </c>
       <c r="H143" t="n">
         <v>18680</v>
@@ -4545,7 +4545,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>6.93710088729858</v>
+        <v>6.9371018409729</v>
       </c>
       <c r="H144" t="n">
         <v>13893</v>
@@ -4632,7 +4632,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G147" t="n">
-        <v>6.88877487182617</v>
+        <v>6.88877534866333</v>
       </c>
       <c r="H147" t="n">
         <v>13704</v>
@@ -4661,7 +4661,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H148" t="n">
         <v>3800</v>
@@ -4690,7 +4690,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.95467519760132</v>
+        <v>6.95467472076416</v>
       </c>
       <c r="H149" t="n">
         <v>16736</v>
@@ -4719,7 +4719,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>6.95467519760132</v>
+        <v>6.95467472076416</v>
       </c>
       <c r="H150" t="n">
         <v>3409</v>
@@ -4748,7 +4748,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G151" t="n">
-        <v>7.16116189956665</v>
+        <v>7.16116285324097</v>
       </c>
       <c r="H151" t="n">
         <v>8656</v>
@@ -4777,7 +4777,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G152" t="n">
-        <v>7.16116189956665</v>
+        <v>7.16116285324097</v>
       </c>
       <c r="H152" t="n">
         <v>3978</v>
@@ -4806,7 +4806,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G153" t="n">
-        <v>7.16116189956665</v>
+        <v>7.16116285324097</v>
       </c>
       <c r="H153" t="n">
         <v>5138</v>
@@ -4893,7 +4893,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.28857040405273</v>
+        <v>7.28856992721558</v>
       </c>
       <c r="H156" t="n">
         <v>38786</v>
@@ -4922,7 +4922,7 @@
         <v>8.26000022888184</v>
       </c>
       <c r="G157" t="n">
-        <v>7.25781679153442</v>
+        <v>7.25781583786011</v>
       </c>
       <c r="H157" t="n">
         <v>2344</v>
@@ -4951,7 +4951,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G158" t="n">
-        <v>7.40719079971313</v>
+        <v>7.40718984603882</v>
       </c>
       <c r="H158" t="n">
         <v>4438</v>
@@ -4980,7 +4980,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>7.36325693130493</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H159" t="n">
         <v>8082</v>
@@ -5009,7 +5009,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G160" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H160" t="n">
         <v>6187</v>
@@ -5038,7 +5038,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>7.36325693130493</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H161" t="n">
         <v>1145</v>
@@ -5067,7 +5067,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G162" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H162" t="n">
         <v>4942</v>
@@ -5096,7 +5096,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G163" t="n">
-        <v>7.40719079971313</v>
+        <v>7.40718984603882</v>
       </c>
       <c r="H163" t="n">
         <v>11925</v>
@@ -5125,7 +5125,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>7.45990991592407</v>
+        <v>7.45991039276123</v>
       </c>
       <c r="H164" t="n">
         <v>1298</v>
@@ -5154,7 +5154,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>7.45990991592407</v>
+        <v>7.45991039276123</v>
       </c>
       <c r="H165" t="n">
         <v>2126</v>
@@ -5183,7 +5183,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G166" t="n">
-        <v>7.33689594268799</v>
+        <v>7.33689641952515</v>
       </c>
       <c r="H166" t="n">
         <v>9454</v>
@@ -5212,7 +5212,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.39840412139893</v>
+        <v>7.39840316772461</v>
       </c>
       <c r="H167" t="n">
         <v>2349</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H168" t="n">
         <v>8638</v>
@@ -5270,7 +5270,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G169" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H169" t="n">
         <v>1652</v>
@@ -5328,7 +5328,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G171" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H171" t="n">
         <v>6170</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.27538871765137</v>
+        <v>7.27538967132568</v>
       </c>
       <c r="H173" t="n">
         <v>1597</v>
@@ -5415,7 +5415,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G174" t="n">
-        <v>7.34128999710083</v>
+        <v>7.34128952026367</v>
       </c>
       <c r="H174" t="n">
         <v>1536</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.19630908966064</v>
+        <v>7.1963095664978</v>
       </c>
       <c r="H177" t="n">
         <v>2108</v>
@@ -5531,7 +5531,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.10844278335571</v>
+        <v>7.10844230651855</v>
       </c>
       <c r="H178" t="n">
         <v>6045</v>
@@ -5589,7 +5589,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.82726860046387</v>
+        <v>6.82726764678955</v>
       </c>
       <c r="H180" t="n">
         <v>23452</v>
@@ -5618,7 +5618,7 @@
         <v>7.80499982833862</v>
       </c>
       <c r="G181" t="n">
-        <v>6.85802221298218</v>
+        <v>6.8580207824707</v>
       </c>
       <c r="H181" t="n">
         <v>7549</v>
@@ -5676,7 +5676,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H183" t="n">
         <v>14070</v>
@@ -5705,7 +5705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G184" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605432510376</v>
       </c>
       <c r="H184" t="n">
         <v>7690</v>
@@ -5734,7 +5734,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G185" t="n">
-        <v>6.88877487182617</v>
+        <v>6.88877534866333</v>
       </c>
       <c r="H185" t="n">
         <v>17952</v>
@@ -5763,7 +5763,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G186" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H186" t="n">
         <v>39341</v>
@@ -5792,7 +5792,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G187" t="n">
-        <v>6.90634822845459</v>
+        <v>6.90634870529175</v>
       </c>
       <c r="H187" t="n">
         <v>9815</v>
@@ -5821,7 +5821,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>6.80530071258545</v>
+        <v>6.80530118942261</v>
       </c>
       <c r="H188" t="n">
         <v>3149</v>
@@ -5879,7 +5879,7 @@
         <v>7.61999988555908</v>
       </c>
       <c r="G190" t="n">
-        <v>6.69546794891357</v>
+        <v>6.69546699523926</v>
       </c>
       <c r="H190" t="n">
         <v>7774</v>
@@ -5937,7 +5937,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>6.63396072387695</v>
+        <v>6.63396120071411</v>
       </c>
       <c r="H192" t="n">
         <v>2140</v>
@@ -5995,7 +5995,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>6.85362815856934</v>
+        <v>6.85362720489502</v>
       </c>
       <c r="H194" t="n">
         <v>3730</v>
@@ -6024,7 +6024,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>6.94149589538574</v>
+        <v>6.94149541854858</v>
       </c>
       <c r="H195" t="n">
         <v>4152</v>
@@ -6053,7 +6053,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G196" t="n">
-        <v>6.96346235275269</v>
+        <v>6.96346187591553</v>
       </c>
       <c r="H196" t="n">
         <v>19913</v>
@@ -6082,7 +6082,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>6.95467519760132</v>
+        <v>6.95467472076416</v>
       </c>
       <c r="H197" t="n">
         <v>4610</v>
@@ -6169,7 +6169,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G200" t="n">
-        <v>6.78333377838135</v>
+        <v>6.78333425521851</v>
       </c>
       <c r="H200" t="n">
         <v>917</v>
@@ -6198,7 +6198,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G201" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H201" t="n">
         <v>8692</v>
@@ -6227,7 +6227,7 @@
         <v>7.75</v>
       </c>
       <c r="G202" t="n">
-        <v>6.80969381332397</v>
+        <v>6.80969476699829</v>
       </c>
       <c r="H202" t="n">
         <v>896</v>
@@ -6256,7 +6256,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>6.90634822845459</v>
+        <v>6.90634870529175</v>
       </c>
       <c r="H203" t="n">
         <v>4470</v>
@@ -6285,7 +6285,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605432510376</v>
       </c>
       <c r="H204" t="n">
         <v>10055</v>
@@ -6314,7 +6314,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G205" t="n">
-        <v>6.87120151519775</v>
+        <v>6.87120199203491</v>
       </c>
       <c r="H205" t="n">
         <v>10123</v>
@@ -6343,7 +6343,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>6.87120151519775</v>
+        <v>6.87120199203491</v>
       </c>
       <c r="H206" t="n">
         <v>20447</v>
@@ -6372,7 +6372,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G207" t="n">
-        <v>6.78333377838135</v>
+        <v>6.78333425521851</v>
       </c>
       <c r="H207" t="n">
         <v>11706</v>
@@ -6401,7 +6401,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G208" t="n">
-        <v>6.84923458099365</v>
+        <v>6.84923505783081</v>
       </c>
       <c r="H208" t="n">
         <v>6959</v>
@@ -6430,7 +6430,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G209" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605432510376</v>
       </c>
       <c r="H209" t="n">
         <v>1774</v>
@@ -6459,7 +6459,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>6.85362815856934</v>
+        <v>6.85362720489502</v>
       </c>
       <c r="H210" t="n">
         <v>3875</v>
@@ -6488,7 +6488,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G211" t="n">
-        <v>6.92392110824585</v>
+        <v>6.92392206192017</v>
       </c>
       <c r="H211" t="n">
         <v>4655</v>
@@ -6517,7 +6517,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>6.95028162002563</v>
+        <v>6.95028066635132</v>
       </c>
       <c r="H212" t="n">
         <v>240</v>
@@ -6546,7 +6546,7 @@
         <v>7.80999994277954</v>
       </c>
       <c r="G213" t="n">
-        <v>6.86241436004639</v>
+        <v>6.86241483688354</v>
       </c>
       <c r="H213" t="n">
         <v>2182</v>
@@ -6575,7 +6575,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.86680841445923</v>
+        <v>6.86680889129639</v>
       </c>
       <c r="H214" t="n">
         <v>2631</v>
@@ -6604,7 +6604,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>6.88438177108765</v>
+        <v>6.88438129425049</v>
       </c>
       <c r="H215" t="n">
         <v>288</v>
@@ -6720,7 +6720,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G219" t="n">
-        <v>6.87120151519775</v>
+        <v>6.87120199203491</v>
       </c>
       <c r="H219" t="n">
         <v>9141</v>
@@ -6778,7 +6778,7 @@
         <v>7.8899998664856</v>
       </c>
       <c r="G221" t="n">
-        <v>6.93270826339722</v>
+        <v>6.93270778656006</v>
       </c>
       <c r="H221" t="n">
         <v>3503</v>
@@ -6807,7 +6807,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G222" t="n">
-        <v>6.78333377838135</v>
+        <v>6.78333425521851</v>
       </c>
       <c r="H222" t="n">
         <v>3935</v>
@@ -6865,7 +6865,7 @@
         <v>7.625</v>
       </c>
       <c r="G224" t="n">
-        <v>6.69986057281494</v>
+        <v>6.6998610496521</v>
       </c>
       <c r="H224" t="n">
         <v>6965</v>
@@ -6894,7 +6894,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G225" t="n">
-        <v>6.72622156143188</v>
+        <v>6.72622108459473</v>
       </c>
       <c r="H225" t="n">
         <v>353</v>
@@ -6923,7 +6923,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>6.59881353378296</v>
+        <v>6.59881401062012</v>
       </c>
       <c r="H226" t="n">
         <v>16592</v>
@@ -6981,7 +6981,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>6.32203245162964</v>
+        <v>6.3220329284668</v>
       </c>
       <c r="H228" t="n">
         <v>6999</v>
@@ -7039,7 +7039,7 @@
         <v>7.20499992370605</v>
       </c>
       <c r="G230" t="n">
-        <v>6.33081865310669</v>
+        <v>6.33081912994385</v>
       </c>
       <c r="H230" t="n">
         <v>14180</v>
@@ -7126,7 +7126,7 @@
         <v>7.31500005722046</v>
       </c>
       <c r="G233" t="n">
-        <v>6.4274730682373</v>
+        <v>6.42747259140015</v>
       </c>
       <c r="H233" t="n">
         <v>2952</v>
@@ -7155,7 +7155,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G234" t="n">
-        <v>6.49337291717529</v>
+        <v>6.49337339401245</v>
       </c>
       <c r="H234" t="n">
         <v>1679</v>
@@ -7184,7 +7184,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.41429281234741</v>
+        <v>6.41429328918457</v>
       </c>
       <c r="H235" t="n">
         <v>7879</v>
@@ -7213,7 +7213,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>6.41429281234741</v>
+        <v>6.41429328918457</v>
       </c>
       <c r="H236" t="n">
         <v>4615</v>
@@ -7242,7 +7242,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G237" t="n">
-        <v>6.19462537765503</v>
+        <v>6.19462585449219</v>
       </c>
       <c r="H237" t="n">
         <v>52499</v>
@@ -7271,7 +7271,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G238" t="n">
-        <v>6.21219873428345</v>
+        <v>6.21219825744629</v>
       </c>
       <c r="H238" t="n">
         <v>4620</v>
@@ -7300,7 +7300,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.17705202102661</v>
+        <v>6.17705249786377</v>
       </c>
       <c r="H239" t="n">
         <v>8669</v>
@@ -7358,7 +7358,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>6.59442043304443</v>
+        <v>6.59441947937012</v>
       </c>
       <c r="H241" t="n">
         <v>17531</v>
@@ -7416,7 +7416,7 @@
         <v>7.5</v>
       </c>
       <c r="G243" t="n">
-        <v>6.59002685546875</v>
+        <v>6.59002780914307</v>
       </c>
       <c r="H243" t="n">
         <v>16241</v>
@@ -7445,7 +7445,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.96346235275269</v>
+        <v>6.96346187591553</v>
       </c>
       <c r="H244" t="n">
         <v>21249</v>
@@ -7474,7 +7474,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.98542833328247</v>
+        <v>6.98542785644531</v>
       </c>
       <c r="H245" t="n">
         <v>12507</v>
@@ -7503,7 +7503,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G246" t="n">
-        <v>6.83166122436523</v>
+        <v>6.83166074752808</v>
       </c>
       <c r="H246" t="n">
         <v>14792</v>
@@ -7532,7 +7532,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>6.82726860046387</v>
+        <v>6.82726764678955</v>
       </c>
       <c r="H247" t="n">
         <v>4566</v>
@@ -7619,7 +7619,7 @@
         <v>7.67000007629395</v>
       </c>
       <c r="G250" t="n">
-        <v>6.7394003868103</v>
+        <v>6.73940134048462</v>
       </c>
       <c r="H250" t="n">
         <v>2760</v>
@@ -7648,7 +7648,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>6.65153360366821</v>
+        <v>6.65153408050537</v>
       </c>
       <c r="H251" t="n">
         <v>9506</v>
@@ -7677,7 +7677,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.65592575073242</v>
+        <v>6.6559271812439</v>
       </c>
       <c r="H252" t="n">
         <v>2025</v>
@@ -7706,7 +7706,7 @@
         <v>7.51999998092651</v>
       </c>
       <c r="G253" t="n">
-        <v>6.60760068893433</v>
+        <v>6.60760021209717</v>
       </c>
       <c r="H253" t="n">
         <v>8643</v>
@@ -7735,7 +7735,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G254" t="n">
-        <v>6.53291416168213</v>
+        <v>6.53291368484497</v>
       </c>
       <c r="H254" t="n">
         <v>10512</v>
@@ -7764,7 +7764,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G255" t="n">
-        <v>6.53291416168213</v>
+        <v>6.53291368484497</v>
       </c>
       <c r="H255" t="n">
         <v>17323</v>
@@ -7851,7 +7851,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H258" t="n">
         <v>15659</v>
@@ -7880,7 +7880,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>7.06011533737183</v>
+        <v>7.06011486053467</v>
       </c>
       <c r="H259" t="n">
         <v>43150</v>
@@ -7909,7 +7909,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>7.16116189956665</v>
+        <v>7.16116285324097</v>
       </c>
       <c r="H260" t="n">
         <v>9680</v>
@@ -7938,7 +7938,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G261" t="n">
-        <v>7.04693603515625</v>
+        <v>7.04693555831909</v>
       </c>
       <c r="H261" t="n">
         <v>20263</v>
@@ -7967,7 +7967,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H262" t="n">
         <v>2360</v>
@@ -8025,7 +8025,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G264" t="n">
-        <v>7.29296255111694</v>
+        <v>7.2929630279541</v>
       </c>
       <c r="H264" t="n">
         <v>8064</v>
@@ -8054,7 +8054,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G265" t="n">
-        <v>7.19630908966064</v>
+        <v>7.1963095664978</v>
       </c>
       <c r="H265" t="n">
         <v>7870</v>
@@ -8083,7 +8083,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G266" t="n">
-        <v>7.19630908966064</v>
+        <v>7.1963095664978</v>
       </c>
       <c r="H266" t="n">
         <v>2986</v>
@@ -8112,7 +8112,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G267" t="n">
-        <v>7.19630908966064</v>
+        <v>7.1963095664978</v>
       </c>
       <c r="H267" t="n">
         <v>3709</v>
@@ -8141,7 +8141,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G268" t="n">
-        <v>7.29296255111694</v>
+        <v>7.2929630279541</v>
       </c>
       <c r="H268" t="n">
         <v>4992</v>
@@ -8199,7 +8199,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G270" t="n">
-        <v>7.04693603515625</v>
+        <v>7.04693555831909</v>
       </c>
       <c r="H270" t="n">
         <v>8451</v>
@@ -8228,7 +8228,7 @@
         <v>8.02000045776367</v>
       </c>
       <c r="G271" t="n">
-        <v>7.04693603515625</v>
+        <v>7.04693555831909</v>
       </c>
       <c r="H271" t="n">
         <v>4297</v>
@@ -8257,7 +8257,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>7.07329607009888</v>
+        <v>7.07329559326172</v>
       </c>
       <c r="H272" t="n">
         <v>4062</v>
@@ -8286,7 +8286,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G273" t="n">
-        <v>7.07329607009888</v>
+        <v>7.07329559326172</v>
       </c>
       <c r="H273" t="n">
         <v>4804</v>
@@ -8315,7 +8315,7 @@
         <v>8.125</v>
       </c>
       <c r="G274" t="n">
-        <v>7.13919639587402</v>
+        <v>7.13919544219971</v>
       </c>
       <c r="H274" t="n">
         <v>4849</v>
@@ -8344,7 +8344,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>7.07329607009888</v>
+        <v>7.07329559326172</v>
       </c>
       <c r="H275" t="n">
         <v>7892</v>
@@ -8373,7 +8373,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G276" t="n">
-        <v>7.18752288818359</v>
+        <v>7.18752241134644</v>
       </c>
       <c r="H276" t="n">
         <v>11564</v>
@@ -8402,7 +8402,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G277" t="n">
-        <v>7.16994953155518</v>
+        <v>7.16994905471802</v>
       </c>
       <c r="H277" t="n">
         <v>7983</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.33689594268799</v>
+        <v>7.33689641952515</v>
       </c>
       <c r="H279" t="n">
         <v>7090</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H280" t="n">
         <v>15652</v>
@@ -8518,7 +8518,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35446977615356</v>
+        <v>7.35446929931641</v>
       </c>
       <c r="H281" t="n">
         <v>3123</v>
@@ -8547,7 +8547,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G282" t="n">
-        <v>7.3676495552063</v>
+        <v>7.36765098571777</v>
       </c>
       <c r="H282" t="n">
         <v>692</v>
@@ -8576,7 +8576,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G283" t="n">
-        <v>7.40719079971313</v>
+        <v>7.40718984603882</v>
       </c>
       <c r="H283" t="n">
         <v>7273</v>
@@ -8605,7 +8605,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>7.42476415634155</v>
+        <v>7.42476272583008</v>
       </c>
       <c r="H284" t="n">
         <v>2943</v>
@@ -8634,7 +8634,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>7.51263093948364</v>
+        <v>7.51263046264648</v>
       </c>
       <c r="H285" t="n">
         <v>9255</v>
@@ -8663,7 +8663,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>7.42476415634155</v>
+        <v>7.42476272583008</v>
       </c>
       <c r="H286" t="n">
         <v>4018</v>
@@ -8692,7 +8692,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G287" t="n">
-        <v>7.49505758285522</v>
+        <v>7.49505710601807</v>
       </c>
       <c r="H287" t="n">
         <v>8846</v>
@@ -8721,7 +8721,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G288" t="n">
-        <v>7.29296255111694</v>
+        <v>7.2929630279541</v>
       </c>
       <c r="H288" t="n">
         <v>14040</v>
@@ -8779,7 +8779,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H290" t="n">
         <v>31344</v>
@@ -8808,7 +8808,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H291" t="n">
         <v>14166</v>
@@ -8837,7 +8837,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H292" t="n">
         <v>12124</v>
@@ -8866,7 +8866,7 @@
         <v>8.18000030517578</v>
       </c>
       <c r="G293" t="n">
-        <v>7.18752288818359</v>
+        <v>7.18752241134644</v>
       </c>
       <c r="H293" t="n">
         <v>3403</v>
@@ -8895,7 +8895,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.42476415634155</v>
+        <v>7.42476272583008</v>
       </c>
       <c r="H294" t="n">
         <v>7818</v>
@@ -8924,7 +8924,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G295" t="n">
-        <v>7.28857040405273</v>
+        <v>7.28856992721558</v>
       </c>
       <c r="H295" t="n">
         <v>18039</v>
@@ -8953,7 +8953,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G296" t="n">
-        <v>7.21827507019043</v>
+        <v>7.21827697753906</v>
       </c>
       <c r="H296" t="n">
         <v>21519</v>
@@ -8982,7 +8982,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H297" t="n">
         <v>3447</v>
@@ -9011,7 +9011,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G298" t="n">
-        <v>7.12162256240845</v>
+        <v>7.12162160873413</v>
       </c>
       <c r="H298" t="n">
         <v>587</v>
@@ -9040,7 +9040,7 @@
         <v>8.30000019073486</v>
       </c>
       <c r="G299" t="n">
-        <v>7.29296255111694</v>
+        <v>7.2929630279541</v>
       </c>
       <c r="H299" t="n">
         <v>8445</v>
@@ -9098,7 +9098,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>6.99421501159668</v>
+        <v>6.99421548843384</v>
       </c>
       <c r="H301" t="n">
         <v>29954</v>
@@ -9127,7 +9127,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>6.99421501159668</v>
+        <v>6.99421548843384</v>
       </c>
       <c r="H302" t="n">
         <v>10238</v>
@@ -9156,7 +9156,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G303" t="n">
-        <v>7.11723041534424</v>
+        <v>7.11722898483276</v>
       </c>
       <c r="H303" t="n">
         <v>7511</v>
@@ -9185,7 +9185,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.17873525619507</v>
+        <v>7.17873573303223</v>
       </c>
       <c r="H304" t="n">
         <v>4105</v>
@@ -9214,7 +9214,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>7.17873525619507</v>
+        <v>7.17873573303223</v>
       </c>
       <c r="H305" t="n">
         <v>13454</v>
@@ -9301,7 +9301,7 @@
         <v>8.23499965667725</v>
       </c>
       <c r="G308" t="n">
-        <v>7.23584890365601</v>
+        <v>7.23584842681885</v>
       </c>
       <c r="H308" t="n">
         <v>5412</v>
@@ -9388,7 +9388,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G311" t="n">
-        <v>7.37204360961914</v>
+        <v>7.3720440864563</v>
       </c>
       <c r="H311" t="n">
         <v>29965</v>
@@ -9417,7 +9417,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>7.36325693130493</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H312" t="n">
         <v>22522</v>
@@ -9446,7 +9446,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>7.42476415634155</v>
+        <v>7.42476272583008</v>
       </c>
       <c r="H313" t="n">
         <v>20571</v>
@@ -9504,7 +9504,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.77623081207275</v>
+        <v>7.77623176574707</v>
       </c>
       <c r="H315" t="n">
         <v>29110</v>
@@ -9533,7 +9533,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>7.7674446105957</v>
+        <v>7.76744556427002</v>
       </c>
       <c r="H316" t="n">
         <v>17411</v>
@@ -9591,7 +9591,7 @@
         <v>9.35000038146973</v>
       </c>
       <c r="G318" t="n">
-        <v>8.21556568145752</v>
+        <v>8.21556854248047</v>
       </c>
       <c r="H318" t="n">
         <v>53646</v>
@@ -9678,7 +9678,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G321" t="n">
-        <v>8.465989112854</v>
+        <v>8.46598625183105</v>
       </c>
       <c r="H321" t="n">
         <v>76746</v>
@@ -9707,7 +9707,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G322" t="n">
-        <v>8.43523502349854</v>
+        <v>8.43523597717285</v>
       </c>
       <c r="H322" t="n">
         <v>38737</v>
@@ -9736,7 +9736,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.19799518585205</v>
+        <v>8.19799327850342</v>
       </c>
       <c r="H323" t="n">
         <v>17848</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.52310085296631</v>
+        <v>8.52310276031494</v>
       </c>
       <c r="H325" t="n">
         <v>52944</v>
@@ -9823,7 +9823,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G326" t="n">
-        <v>8.90971565246582</v>
+        <v>8.90971755981445</v>
       </c>
       <c r="H326" t="n">
         <v>66582</v>
@@ -9939,7 +9939,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G330" t="n">
-        <v>9.18210411071777</v>
+        <v>9.18210315704346</v>
       </c>
       <c r="H330" t="n">
         <v>36798</v>
@@ -9968,7 +9968,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G331" t="n">
-        <v>8.95365142822266</v>
+        <v>8.95365047454834</v>
       </c>
       <c r="H331" t="n">
         <v>17183</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.78670310974121</v>
+        <v>8.78670215606689</v>
       </c>
       <c r="H332" t="n">
         <v>34355</v>
@@ -10026,7 +10026,7 @@
         <v>9.97000026702881</v>
       </c>
       <c r="G333" t="n">
-        <v>8.76034355163574</v>
+        <v>8.76034164428711</v>
       </c>
       <c r="H333" t="n">
         <v>17604</v>
@@ -10084,7 +10084,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G335" t="n">
-        <v>8.64611625671387</v>
+        <v>8.64611530303955</v>
       </c>
       <c r="H335" t="n">
         <v>19956</v>
@@ -10171,7 +10171,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74276828765869</v>
+        <v>8.74276638031006</v>
       </c>
       <c r="H338" t="n">
         <v>19588</v>
@@ -10200,7 +10200,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>8.74276828765869</v>
+        <v>8.74276638031006</v>
       </c>
       <c r="H339" t="n">
         <v>52366</v>
@@ -10258,7 +10258,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G341" t="n">
-        <v>8.64611625671387</v>
+        <v>8.64611530303955</v>
       </c>
       <c r="H341" t="n">
         <v>20750</v>
@@ -10287,7 +10287,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G342" t="n">
-        <v>8.64611625671387</v>
+        <v>8.64611530303955</v>
       </c>
       <c r="H342" t="n">
         <v>6154</v>
@@ -10345,7 +10345,7 @@
         <v>9.85000038146973</v>
       </c>
       <c r="G344" t="n">
-        <v>8.6549015045166</v>
+        <v>8.65490341186523</v>
       </c>
       <c r="H344" t="n">
         <v>30227</v>
@@ -10374,7 +10374,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G345" t="n">
-        <v>8.71640777587891</v>
+        <v>8.71640968322754</v>
       </c>
       <c r="H345" t="n">
         <v>27443</v>
@@ -10403,7 +10403,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G346" t="n">
-        <v>8.74276828765869</v>
+        <v>8.74276638031006</v>
       </c>
       <c r="H346" t="n">
         <v>38460</v>
@@ -10432,7 +10432,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>8.61096954345703</v>
+        <v>8.61096858978271</v>
       </c>
       <c r="H347" t="n">
         <v>25037</v>
@@ -10548,7 +10548,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G351" t="n">
-        <v>9.03272914886475</v>
+        <v>9.03273010253906</v>
       </c>
       <c r="H351" t="n">
         <v>40243</v>
@@ -10606,7 +10606,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>8.87457180023193</v>
+        <v>8.8745698928833</v>
       </c>
       <c r="H353" t="n">
         <v>7452</v>
@@ -10664,7 +10664,7 @@
         <v>10.5</v>
       </c>
       <c r="G355" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H355" t="n">
         <v>13733</v>
@@ -10838,7 +10838,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G361" t="n">
-        <v>9.35213565826416</v>
+        <v>9.35213756561279</v>
       </c>
       <c r="H361" t="n">
         <v>4291</v>
@@ -10867,7 +10867,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H362" t="n">
         <v>9456</v>
@@ -10925,7 +10925,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G364" t="n">
-        <v>9.60176563262939</v>
+        <v>9.60176658630371</v>
       </c>
       <c r="H364" t="n">
         <v>7605</v>
@@ -10954,7 +10954,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G365" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H365" t="n">
         <v>19352</v>
@@ -10983,7 +10983,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G366" t="n">
-        <v>10.4398021697998</v>
+        <v>10.4398012161255</v>
       </c>
       <c r="H366" t="n">
         <v>68065</v>
@@ -11012,7 +11012,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G367" t="n">
-        <v>9.98512268066406</v>
+        <v>9.98512363433838</v>
       </c>
       <c r="H367" t="n">
         <v>29675</v>
@@ -11041,7 +11041,7 @@
         <v>11</v>
       </c>
       <c r="G368" t="n">
-        <v>9.80681896209717</v>
+        <v>9.80681800842285</v>
       </c>
       <c r="H368" t="n">
         <v>22352</v>
@@ -11070,7 +11070,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>9.67308712005615</v>
+        <v>9.67308902740479</v>
       </c>
       <c r="H369" t="n">
         <v>20493</v>
@@ -11099,7 +11099,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G370" t="n">
-        <v>9.49478149414062</v>
+        <v>9.49478244781494</v>
       </c>
       <c r="H370" t="n">
         <v>20575</v>
@@ -11157,7 +11157,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G372" t="n">
-        <v>9.4680347442627</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H372" t="n">
         <v>20681</v>
@@ -11244,7 +11244,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G375" t="n">
-        <v>9.49478149414062</v>
+        <v>9.49478244781494</v>
       </c>
       <c r="H375" t="n">
         <v>10082</v>
@@ -11273,7 +11273,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G376" t="n">
-        <v>9.43237495422363</v>
+        <v>9.43237590789795</v>
       </c>
       <c r="H376" t="n">
         <v>8357</v>
@@ -11302,7 +11302,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G377" t="n">
-        <v>9.4145450592041</v>
+        <v>9.41454410552979</v>
       </c>
       <c r="H377" t="n">
         <v>29660</v>
@@ -11331,7 +11331,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H378" t="n">
         <v>18961</v>
@@ -11360,7 +11360,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H379" t="n">
         <v>28104</v>
@@ -11389,7 +11389,7 @@
         <v>10.8800001144409</v>
       </c>
       <c r="G380" t="n">
-        <v>9.69983291625977</v>
+        <v>9.6998348236084</v>
       </c>
       <c r="H380" t="n">
         <v>35557</v>
@@ -11476,7 +11476,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G383" t="n">
-        <v>9.39671421051025</v>
+        <v>9.39671325683594</v>
       </c>
       <c r="H383" t="n">
         <v>32134</v>
@@ -11534,7 +11534,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G385" t="n">
-        <v>9.39671421051025</v>
+        <v>9.39671325683594</v>
       </c>
       <c r="H385" t="n">
         <v>7898</v>
@@ -11650,7 +11650,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H389" t="n">
         <v>14464</v>
@@ -11708,7 +11708,7 @@
         <v>10.5</v>
       </c>
       <c r="G391" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11824,7 +11824,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H395" t="n">
         <v>13222</v>
@@ -11853,7 +11853,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G396" t="n">
-        <v>9.49478149414062</v>
+        <v>9.49478244781494</v>
       </c>
       <c r="H396" t="n">
         <v>29029</v>
@@ -11882,7 +11882,7 @@
         <v>10.5</v>
       </c>
       <c r="G397" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H397" t="n">
         <v>13753</v>
@@ -11911,7 +11911,7 @@
         <v>10.5</v>
       </c>
       <c r="G398" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H398" t="n">
         <v>7506</v>
@@ -11969,7 +11969,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H400" t="n">
         <v>11923</v>
@@ -12056,7 +12056,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G403" t="n">
-        <v>9.14708709716797</v>
+        <v>9.14708518981934</v>
       </c>
       <c r="H403" t="n">
         <v>10030</v>
@@ -12114,7 +12114,7 @@
         <v>10.25</v>
       </c>
       <c r="G405" t="n">
-        <v>9.13817024230957</v>
+        <v>9.13817119598389</v>
       </c>
       <c r="H405" t="n">
         <v>12431</v>
@@ -12143,7 +12143,7 @@
         <v>10.25</v>
       </c>
       <c r="G406" t="n">
-        <v>9.13817024230957</v>
+        <v>9.13817119598389</v>
       </c>
       <c r="H406" t="n">
         <v>5490</v>
@@ -12201,7 +12201,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H408" t="n">
         <v>22288</v>
@@ -12259,7 +12259,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G410" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H410" t="n">
         <v>19678</v>
@@ -12433,7 +12433,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G416" t="n">
-        <v>9.37888240814209</v>
+        <v>9.37888336181641</v>
       </c>
       <c r="H416" t="n">
         <v>13661</v>
@@ -12462,7 +12462,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G417" t="n">
-        <v>9.4680347442627</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H417" t="n">
         <v>1987</v>
@@ -12491,7 +12491,7 @@
         <v>10.6700000762939</v>
       </c>
       <c r="G418" t="n">
-        <v>9.51261329650879</v>
+        <v>9.51261234283447</v>
       </c>
       <c r="H418" t="n">
         <v>982</v>
@@ -12520,7 +12520,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G419" t="n">
-        <v>9.4145450592041</v>
+        <v>9.41454410552979</v>
       </c>
       <c r="H419" t="n">
         <v>11130</v>
@@ -12578,7 +12578,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G421" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H421" t="n">
         <v>13775</v>
@@ -12607,7 +12607,7 @@
         <v>10.5</v>
       </c>
       <c r="G422" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H422" t="n">
         <v>9242</v>
@@ -12636,7 +12636,7 @@
         <v>10.5</v>
       </c>
       <c r="G423" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H423" t="n">
         <v>4076</v>
@@ -12665,7 +12665,7 @@
         <v>10.5</v>
       </c>
       <c r="G424" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H424" t="n">
         <v>845</v>
@@ -12694,7 +12694,7 @@
         <v>10.5</v>
       </c>
       <c r="G425" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H425" t="n">
         <v>5285</v>
@@ -12723,7 +12723,7 @@
         <v>10.5</v>
       </c>
       <c r="G426" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H426" t="n">
         <v>1963</v>
@@ -12781,7 +12781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H428" t="n">
         <v>4642</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H429" t="n">
         <v>1070</v>
@@ -12868,7 +12868,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G431" t="n">
-        <v>9.52152824401855</v>
+        <v>9.52152919769287</v>
       </c>
       <c r="H431" t="n">
         <v>5497</v>
@@ -12897,7 +12897,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G432" t="n">
-        <v>9.59285068511963</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H432" t="n">
         <v>6357</v>
@@ -12926,7 +12926,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G433" t="n">
-        <v>9.63742637634277</v>
+        <v>9.63742733001709</v>
       </c>
       <c r="H433" t="n">
         <v>3228</v>
@@ -12955,7 +12955,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>9.52152824401855</v>
+        <v>9.52152919769287</v>
       </c>
       <c r="H434" t="n">
         <v>9019</v>
@@ -12984,7 +12984,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G435" t="n">
-        <v>9.4145450592041</v>
+        <v>9.41454410552979</v>
       </c>
       <c r="H435" t="n">
         <v>16590</v>
@@ -13071,7 +13071,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G438" t="n">
-        <v>9.4680347442627</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H438" t="n">
         <v>32980</v>
@@ -13100,7 +13100,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G439" t="n">
-        <v>9.59285068511963</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H439" t="n">
         <v>11645</v>
@@ -13129,7 +13129,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G440" t="n">
-        <v>9.4680347442627</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H440" t="n">
         <v>12649</v>
@@ -13187,7 +13187,7 @@
         <v>10.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H442" t="n">
         <v>30432</v>
@@ -13216,7 +13216,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="n">
-        <v>9.33430671691895</v>
+        <v>9.33430767059326</v>
       </c>
       <c r="H443" t="n">
         <v>7591</v>
@@ -13361,7 +13361,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H448" t="n">
         <v>28520</v>
@@ -13390,7 +13390,7 @@
         <v>10.5</v>
       </c>
       <c r="G449" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H449" t="n">
         <v>12077</v>
@@ -13419,7 +13419,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G450" t="n">
-        <v>9.37888240814209</v>
+        <v>9.37888336181641</v>
       </c>
       <c r="H450" t="n">
         <v>4357</v>
@@ -13651,7 +13651,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H458" t="n">
         <v>39732</v>
@@ -13796,7 +13796,7 @@
         <v>10.5</v>
       </c>
       <c r="G463" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H463" t="n">
         <v>10385</v>
@@ -13825,7 +13825,7 @@
         <v>10.4899997711182</v>
       </c>
       <c r="G464" t="n">
-        <v>9.35213565826416</v>
+        <v>9.35213756561279</v>
       </c>
       <c r="H464" t="n">
         <v>5364</v>
@@ -13970,7 +13970,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H469" t="n">
         <v>21920</v>
@@ -13999,7 +13999,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G470" t="n">
-        <v>9.22732353210449</v>
+        <v>9.22732448577881</v>
       </c>
       <c r="H470" t="n">
         <v>4876</v>
@@ -14028,7 +14028,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H471" t="n">
         <v>11273</v>
@@ -14057,7 +14057,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H472" t="n">
         <v>7887</v>
@@ -14086,7 +14086,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H473" t="n">
         <v>4137</v>
@@ -14115,7 +14115,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H474" t="n">
         <v>104971</v>
@@ -14202,7 +14202,7 @@
         <v>10.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H477" t="n">
         <v>8518</v>
@@ -14231,7 +14231,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H478" t="n">
         <v>5316</v>
@@ -14289,7 +14289,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>9.40563011169434</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H480" t="n">
         <v>9052</v>
@@ -14318,7 +14318,7 @@
         <v>10.25</v>
       </c>
       <c r="G481" t="n">
-        <v>9.13817024230957</v>
+        <v>9.13817119598389</v>
       </c>
       <c r="H481" t="n">
         <v>16931</v>
@@ -14434,7 +14434,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H485" t="n">
         <v>23241</v>
@@ -14463,7 +14463,7 @@
         <v>10.75</v>
       </c>
       <c r="G486" t="n">
-        <v>9.58393383026123</v>
+        <v>9.58393669128418</v>
       </c>
       <c r="H486" t="n">
         <v>15348</v>
@@ -14492,7 +14492,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>9.67308712005615</v>
+        <v>9.67308902740479</v>
       </c>
       <c r="H487" t="n">
         <v>57982</v>
@@ -14550,7 +14550,7 @@
         <v>10.8699998855591</v>
       </c>
       <c r="G489" t="n">
-        <v>9.69091892242432</v>
+        <v>9.69091987609863</v>
       </c>
       <c r="H489" t="n">
         <v>19447</v>
@@ -14579,7 +14579,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>9.64634132385254</v>
+        <v>9.64634323120117</v>
       </c>
       <c r="H490" t="n">
         <v>21920</v>
@@ -14608,7 +14608,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G491" t="n">
-        <v>9.73549365997314</v>
+        <v>9.73549747467041</v>
       </c>
       <c r="H491" t="n">
         <v>4719</v>
@@ -14666,7 +14666,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G493" t="n">
-        <v>9.30755996704102</v>
+        <v>9.30756092071533</v>
       </c>
       <c r="H493" t="n">
         <v>15192</v>
@@ -14695,7 +14695,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>9.60176563262939</v>
+        <v>9.60176658630371</v>
       </c>
       <c r="H494" t="n">
         <v>12114</v>
@@ -14724,7 +14724,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="n">
-        <v>9.83356380462646</v>
+        <v>9.83356189727783</v>
       </c>
       <c r="H495" t="n">
         <v>11597</v>
@@ -14753,7 +14753,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="n">
-        <v>9.74441242218018</v>
+        <v>9.74441051483154</v>
       </c>
       <c r="H496" t="n">
         <v>8197</v>
@@ -14782,7 +14782,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G497" t="n">
-        <v>9.6641731262207</v>
+        <v>9.66417026519775</v>
       </c>
       <c r="H497" t="n">
         <v>1051</v>
@@ -14811,7 +14811,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>9.70874881744385</v>
+        <v>9.70874786376953</v>
       </c>
       <c r="H498" t="n">
         <v>483</v>
@@ -14840,7 +14840,7 @@
         <v>10.789999961853</v>
       </c>
       <c r="G499" t="n">
-        <v>9.61959552764893</v>
+        <v>9.61959457397461</v>
       </c>
       <c r="H499" t="n">
         <v>7892</v>
@@ -14869,7 +14869,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H500" t="n">
         <v>3490</v>
@@ -14985,7 +14985,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G504" t="n">
-        <v>9.01335525512695</v>
+        <v>9.01335620880127</v>
       </c>
       <c r="H504" t="n">
         <v>33740</v>
@@ -15014,7 +15014,7 @@
         <v>10.3699998855591</v>
       </c>
       <c r="G505" t="n">
-        <v>9.24515438079834</v>
+        <v>9.24515342712402</v>
       </c>
       <c r="H505" t="n">
         <v>12894</v>
@@ -15130,7 +15130,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G509" t="n">
-        <v>9.15600299835205</v>
+        <v>9.15600109100342</v>
       </c>
       <c r="H509" t="n">
         <v>1553</v>
@@ -15159,7 +15159,7 @@
         <v>10.5</v>
       </c>
       <c r="G510" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H510" t="n">
         <v>20934</v>
@@ -15246,7 +15246,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G513" t="n">
-        <v>9.3253927230835</v>
+        <v>9.32539176940918</v>
       </c>
       <c r="H513" t="n">
         <v>9657</v>
@@ -15275,7 +15275,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G514" t="n">
-        <v>9.30755996704102</v>
+        <v>9.30756092071533</v>
       </c>
       <c r="H514" t="n">
         <v>32641</v>
@@ -15333,7 +15333,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G516" t="n">
-        <v>9.37888240814209</v>
+        <v>9.37888336181641</v>
       </c>
       <c r="H516" t="n">
         <v>3585</v>
@@ -15536,7 +15536,7 @@
         <v>10.5</v>
       </c>
       <c r="G523" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H523" t="n">
         <v>8693</v>
@@ -15565,7 +15565,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>9.4145450592041</v>
+        <v>9.41454410552979</v>
       </c>
       <c r="H524" t="n">
         <v>5293</v>
@@ -15594,7 +15594,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>9.53935813903809</v>
+        <v>9.53936004638672</v>
       </c>
       <c r="H525" t="n">
         <v>7037</v>
@@ -15652,7 +15652,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G527" t="n">
-        <v>9.59285068511963</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H527" t="n">
         <v>15071</v>
@@ -15681,7 +15681,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G528" t="n">
-        <v>9.6641731262207</v>
+        <v>9.66417026519775</v>
       </c>
       <c r="H528" t="n">
         <v>16591</v>
@@ -15710,7 +15710,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>9.61067962646484</v>
+        <v>9.61068058013916</v>
       </c>
       <c r="H529" t="n">
         <v>7263</v>
@@ -15739,7 +15739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H530" t="n">
         <v>80</v>
@@ -15768,7 +15768,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G531" t="n">
-        <v>9.64634132385254</v>
+        <v>9.64634323120117</v>
       </c>
       <c r="H531" t="n">
         <v>6447</v>
@@ -15797,7 +15797,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G532" t="n">
-        <v>9.39671421051025</v>
+        <v>9.39671325683594</v>
       </c>
       <c r="H532" t="n">
         <v>1624</v>
@@ -15884,7 +15884,7 @@
         <v>10.5</v>
       </c>
       <c r="G535" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H535" t="n">
         <v>14368</v>
@@ -15942,7 +15942,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G537" t="n">
-        <v>9.02227210998535</v>
+        <v>9.02227306365967</v>
       </c>
       <c r="H537" t="n">
         <v>19004</v>
@@ -15971,7 +15971,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G538" t="n">
-        <v>9.39671421051025</v>
+        <v>9.39671325683594</v>
       </c>
       <c r="H538" t="n">
         <v>15318</v>
@@ -16000,7 +16000,7 @@
         <v>10.5</v>
       </c>
       <c r="G539" t="n">
-        <v>9.36105346679688</v>
+        <v>9.36105251312256</v>
       </c>
       <c r="H539" t="n">
         <v>7725</v>
@@ -16087,7 +16087,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="n">
-        <v>8.98661136627197</v>
+        <v>8.98661041259766</v>
       </c>
       <c r="H542" t="n">
         <v>20475</v>
@@ -16174,7 +16174,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G545" t="n">
-        <v>9.07576274871826</v>
+        <v>9.07576370239258</v>
       </c>
       <c r="H545" t="n">
         <v>28970</v>
@@ -16203,7 +16203,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G546" t="n">
-        <v>8.98661136627197</v>
+        <v>8.98661041259766</v>
       </c>
       <c r="H546" t="n">
         <v>8062</v>
@@ -16232,7 +16232,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G547" t="n">
-        <v>8.82613563537598</v>
+        <v>8.82613658905029</v>
       </c>
       <c r="H547" t="n">
         <v>10799</v>
@@ -16261,7 +16261,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G548" t="n">
-        <v>9.04010200500488</v>
+        <v>9.0401029586792</v>
       </c>
       <c r="H548" t="n">
         <v>36378</v>
@@ -16290,7 +16290,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G549" t="n">
-        <v>9.16491603851318</v>
+        <v>9.16491508483887</v>
       </c>
       <c r="H549" t="n">
         <v>16031</v>
@@ -16319,7 +16319,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G550" t="n">
-        <v>9.3253927230835</v>
+        <v>9.32539176940918</v>
       </c>
       <c r="H550" t="n">
         <v>6723</v>
@@ -16348,7 +16348,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G551" t="n">
-        <v>9.02227210998535</v>
+        <v>9.02227306365967</v>
       </c>
       <c r="H551" t="n">
         <v>9669</v>
@@ -16435,7 +16435,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H554" t="n">
         <v>100659</v>
@@ -16464,7 +16464,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G555" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H555" t="n">
         <v>23195</v>
@@ -16493,7 +16493,7 @@
         <v>11</v>
       </c>
       <c r="G556" t="n">
-        <v>9.80681896209717</v>
+        <v>9.80681800842285</v>
       </c>
       <c r="H556" t="n">
         <v>59233</v>
@@ -16551,7 +16551,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G558" t="n">
-        <v>10.43088722229</v>
+        <v>10.4308881759644</v>
       </c>
       <c r="H558" t="n">
         <v>215011</v>
@@ -16580,7 +16580,7 @@
         <v>11.960000038147</v>
       </c>
       <c r="G559" t="n">
-        <v>10.6626844406128</v>
+        <v>10.6626853942871</v>
       </c>
       <c r="H559" t="n">
         <v>59685</v>
@@ -16609,7 +16609,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G560" t="n">
-        <v>10.4665489196777</v>
+        <v>10.4665498733521</v>
       </c>
       <c r="H560" t="n">
         <v>39068</v>
@@ -16638,7 +16638,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G561" t="n">
-        <v>10.6091938018799</v>
+        <v>10.6091928482056</v>
       </c>
       <c r="H561" t="n">
         <v>88988</v>
@@ -16667,7 +16667,7 @@
         <v>12.1400003433228</v>
       </c>
       <c r="G562" t="n">
-        <v>10.8231601715088</v>
+        <v>10.8231620788574</v>
       </c>
       <c r="H562" t="n">
         <v>55087</v>
@@ -16754,7 +16754,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G565" t="n">
-        <v>10.5735330581665</v>
+        <v>10.5735311508179</v>
       </c>
       <c r="H565" t="n">
         <v>259538</v>
@@ -16812,7 +16812,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G567" t="n">
-        <v>10.359564781189</v>
+        <v>10.3595657348633</v>
       </c>
       <c r="H567" t="n">
         <v>9008</v>
@@ -16870,7 +16870,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G569" t="n">
-        <v>10.0921068191528</v>
+        <v>10.0921058654785</v>
       </c>
       <c r="H569" t="n">
         <v>16994</v>
@@ -16899,7 +16899,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G570" t="n">
-        <v>10.109938621521</v>
+        <v>10.109935760498</v>
       </c>
       <c r="H570" t="n">
         <v>11326</v>
@@ -16957,7 +16957,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G572" t="n">
-        <v>9.98512268066406</v>
+        <v>9.98512363433838</v>
       </c>
       <c r="H572" t="n">
         <v>22699</v>
@@ -16986,7 +16986,7 @@
         <v>11.3400001525879</v>
       </c>
       <c r="G573" t="n">
-        <v>10.109938621521</v>
+        <v>10.109935760498</v>
       </c>
       <c r="H573" t="n">
         <v>9826</v>
@@ -17015,7 +17015,7 @@
         <v>11</v>
       </c>
       <c r="G574" t="n">
-        <v>9.80681896209717</v>
+        <v>9.80681800842285</v>
       </c>
       <c r="H574" t="n">
         <v>15974</v>
@@ -17044,7 +17044,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H575" t="n">
         <v>16571</v>
@@ -17073,7 +17073,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G576" t="n">
-        <v>9.68200397491455</v>
+        <v>9.6820011138916</v>
       </c>
       <c r="H576" t="n">
         <v>27025</v>
@@ -17131,7 +17131,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>9.62851238250732</v>
+        <v>9.62851142883301</v>
       </c>
       <c r="H578" t="n">
         <v>25531</v>
@@ -17160,7 +17160,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G579" t="n">
-        <v>9.4145450592041</v>
+        <v>9.41454410552979</v>
       </c>
       <c r="H579" t="n">
         <v>26470</v>
@@ -17189,7 +17189,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G580" t="n">
-        <v>9.73549365997314</v>
+        <v>9.73549747467041</v>
       </c>
       <c r="H580" t="n">
         <v>29642</v>
@@ -17218,7 +17218,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G581" t="n">
-        <v>9.93163204193115</v>
+        <v>9.93163108825684</v>
       </c>
       <c r="H581" t="n">
         <v>10411</v>
@@ -17334,7 +17334,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G585" t="n">
-        <v>9.77115535736084</v>
+        <v>9.77115440368652</v>
       </c>
       <c r="H585" t="n">
         <v>204901</v>
@@ -17363,7 +17363,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>9.73549365997314</v>
+        <v>9.73549747467041</v>
       </c>
       <c r="H586" t="n">
         <v>10236</v>
@@ -17421,7 +17421,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G588" t="n">
-        <v>10.0921068191528</v>
+        <v>10.0921058654785</v>
       </c>
       <c r="H588" t="n">
         <v>13867</v>
@@ -17450,7 +17450,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G589" t="n">
-        <v>10.0207843780518</v>
+        <v>10.0207834243774</v>
       </c>
       <c r="H589" t="n">
         <v>10485</v>
@@ -17508,7 +17508,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G591" t="n">
-        <v>10.1277666091919</v>
+        <v>10.1277675628662</v>
       </c>
       <c r="H591" t="n">
         <v>883</v>
@@ -17566,7 +17566,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G593" t="n">
-        <v>10.1990900039673</v>
+        <v>10.199089050293</v>
       </c>
       <c r="H593" t="n">
         <v>4351</v>
@@ -17595,7 +17595,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>10.1455993652344</v>
+        <v>10.1455984115601</v>
       </c>
       <c r="H594" t="n">
         <v>6655</v>
@@ -17624,7 +17624,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>10.1634292602539</v>
+        <v>10.1634283065796</v>
       </c>
       <c r="H595" t="n">
         <v>2549</v>
@@ -17653,7 +17653,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G596" t="n">
-        <v>10.1277666091919</v>
+        <v>10.1277675628662</v>
       </c>
       <c r="H596" t="n">
         <v>1030</v>
@@ -17682,7 +17682,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G597" t="n">
-        <v>10.680516242981</v>
+        <v>10.6805143356323</v>
       </c>
       <c r="H597" t="n">
         <v>27249</v>
@@ -17711,7 +17711,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>10.43088722229</v>
+        <v>10.4308881759644</v>
       </c>
       <c r="H598" t="n">
         <v>11050</v>
@@ -17798,7 +17798,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G601" t="n">
-        <v>9.4680347442627</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H601" t="n">
         <v>52636</v>
@@ -17856,7 +17856,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G603" t="n">
-        <v>9.73549365997314</v>
+        <v>9.73549747467041</v>
       </c>
       <c r="H603" t="n">
         <v>66416</v>
@@ -17914,7 +17914,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G605" t="n">
-        <v>9.39671421051025</v>
+        <v>9.39671325683594</v>
       </c>
       <c r="H605" t="n">
         <v>36929</v>
@@ -17943,7 +17943,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G606" t="n">
-        <v>9.82464790344238</v>
+        <v>9.8246488571167</v>
       </c>
       <c r="H606" t="n">
         <v>36151</v>
@@ -18001,7 +18001,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G608" t="n">
-        <v>9.60014915466309</v>
+        <v>9.60014820098877</v>
       </c>
       <c r="H608" t="n">
         <v>36907</v>
@@ -18059,7 +18059,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>9.79902267456055</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H610" t="n">
         <v>20207</v>
@@ -18088,7 +18088,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882930755615</v>
       </c>
       <c r="H611" t="n">
         <v>17961</v>
@@ -18117,7 +18117,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H612" t="n">
         <v>13121</v>
@@ -18146,7 +18146,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G613" t="n">
-        <v>9.56398868560791</v>
+        <v>9.56398963928223</v>
       </c>
       <c r="H613" t="n">
         <v>8798</v>
@@ -18204,7 +18204,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G615" t="n">
-        <v>9.69054698944092</v>
+        <v>9.6905460357666</v>
       </c>
       <c r="H615" t="n">
         <v>28069</v>
@@ -18233,7 +18233,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G616" t="n">
-        <v>9.56398868560791</v>
+        <v>9.56398963928223</v>
       </c>
       <c r="H616" t="n">
         <v>7008</v>
@@ -18262,7 +18262,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G617" t="n">
-        <v>9.69054698944092</v>
+        <v>9.6905460357666</v>
       </c>
       <c r="H617" t="n">
         <v>18097</v>
@@ -18320,7 +18320,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G619" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H619" t="n">
         <v>35644</v>
@@ -18349,7 +18349,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G620" t="n">
-        <v>10.1606101989746</v>
+        <v>10.160608291626</v>
       </c>
       <c r="H620" t="n">
         <v>32298</v>
@@ -18378,7 +18378,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>10.3052425384521</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H621" t="n">
         <v>12133</v>
@@ -18407,7 +18407,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G622" t="n">
-        <v>10.341402053833</v>
+        <v>10.3414011001587</v>
       </c>
       <c r="H622" t="n">
         <v>38574</v>
@@ -18436,7 +18436,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G623" t="n">
-        <v>10.7210702896118</v>
+        <v>10.7210693359375</v>
       </c>
       <c r="H623" t="n">
         <v>19755</v>
@@ -18465,7 +18465,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G624" t="n">
-        <v>10.6125936508179</v>
+        <v>10.6125926971436</v>
       </c>
       <c r="H624" t="n">
         <v>15870</v>
@@ -18494,7 +18494,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G625" t="n">
-        <v>10.5402755737305</v>
+        <v>10.5402765274048</v>
       </c>
       <c r="H625" t="n">
         <v>17727</v>
@@ -18523,7 +18523,7 @@
         <v>11.8400001525879</v>
       </c>
       <c r="G626" t="n">
-        <v>10.7029895782471</v>
+        <v>10.7029886245728</v>
       </c>
       <c r="H626" t="n">
         <v>8187</v>
@@ -18581,7 +18581,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G628" t="n">
-        <v>10.3233242034912</v>
+        <v>10.3233232498169</v>
       </c>
       <c r="H628" t="n">
         <v>8829</v>
@@ -18610,7 +18610,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>10.3052425384521</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H629" t="n">
         <v>7309</v>
@@ -18639,7 +18639,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G630" t="n">
-        <v>10.1425294876099</v>
+        <v>10.1425313949585</v>
       </c>
       <c r="H630" t="n">
         <v>7952</v>
@@ -18668,7 +18668,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G631" t="n">
-        <v>10.0702114105225</v>
+        <v>10.0702123641968</v>
       </c>
       <c r="H631" t="n">
         <v>24542</v>
@@ -18726,7 +18726,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G633" t="n">
-        <v>10.5041170120239</v>
+        <v>10.5041179656982</v>
       </c>
       <c r="H633" t="n">
         <v>15986</v>
@@ -18755,7 +18755,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G634" t="n">
-        <v>10.2690849304199</v>
+        <v>10.2690858840942</v>
       </c>
       <c r="H634" t="n">
         <v>6424</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H637" t="n">
         <v>32207</v>
@@ -18958,7 +18958,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G641" t="n">
-        <v>10.0340547561646</v>
+        <v>10.0340538024902</v>
       </c>
       <c r="H641" t="n">
         <v>30585</v>
@@ -19016,7 +19016,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G643" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882930755615</v>
       </c>
       <c r="H643" t="n">
         <v>12748</v>
@@ -19045,7 +19045,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G644" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882930755615</v>
       </c>
       <c r="H644" t="n">
         <v>21220</v>
@@ -19074,7 +19074,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H645" t="n">
         <v>2324</v>
@@ -19103,7 +19103,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G646" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H646" t="n">
         <v>7707</v>
@@ -19132,7 +19132,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G647" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H647" t="n">
         <v>9144</v>
@@ -19161,7 +19161,7 @@
         <v>11</v>
       </c>
       <c r="G648" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H648" t="n">
         <v>13457</v>
@@ -19190,7 +19190,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G649" t="n">
-        <v>10.0340547561646</v>
+        <v>10.0340538024902</v>
       </c>
       <c r="H649" t="n">
         <v>3688</v>
@@ -19248,7 +19248,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G651" t="n">
-        <v>10.0159740447998</v>
+        <v>10.0159730911255</v>
       </c>
       <c r="H651" t="n">
         <v>3865</v>
@@ -19277,7 +19277,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G652" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H652" t="n">
         <v>15725</v>
@@ -19335,7 +19335,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H654" t="n">
         <v>4117</v>
@@ -19364,7 +19364,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G655" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87134075164795</v>
       </c>
       <c r="H655" t="n">
         <v>1822</v>
@@ -19393,7 +19393,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H656" t="n">
         <v>7599</v>
@@ -19422,7 +19422,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G657" t="n">
-        <v>9.79902267456055</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H657" t="n">
         <v>3469</v>
@@ -19451,7 +19451,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G658" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H658" t="n">
         <v>5957</v>
@@ -19480,7 +19480,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G659" t="n">
-        <v>9.81710052490234</v>
+        <v>9.81709957122803</v>
       </c>
       <c r="H659" t="n">
         <v>13056</v>
@@ -19509,7 +19509,7 @@
         <v>11</v>
       </c>
       <c r="G660" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H660" t="n">
         <v>6088</v>
@@ -19538,7 +19538,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G661" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H661" t="n">
         <v>17339</v>
@@ -19567,7 +19567,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H662" t="n">
         <v>7902</v>
@@ -19654,7 +19654,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H665" t="n">
         <v>2732</v>
@@ -19712,7 +19712,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G667" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H667" t="n">
         <v>16460</v>
@@ -19741,7 +19741,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G668" t="n">
-        <v>9.56398868560791</v>
+        <v>9.56398963928223</v>
       </c>
       <c r="H668" t="n">
         <v>10152</v>
@@ -19828,7 +19828,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H671" t="n">
         <v>11434</v>
@@ -19944,7 +19944,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H675" t="n">
         <v>9236</v>
@@ -20002,7 +20002,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G677" t="n">
-        <v>9.79902267456055</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H677" t="n">
         <v>796</v>
@@ -20031,7 +20031,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G678" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H678" t="n">
         <v>4044</v>
@@ -20147,7 +20147,7 @@
         <v>10.5</v>
       </c>
       <c r="G682" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H682" t="n">
         <v>3455</v>
@@ -20176,7 +20176,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G683" t="n">
-        <v>9.60014915466309</v>
+        <v>9.60014820098877</v>
       </c>
       <c r="H683" t="n">
         <v>2728</v>
@@ -20234,7 +20234,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G685" t="n">
-        <v>9.60014915466309</v>
+        <v>9.60014820098877</v>
       </c>
       <c r="H685" t="n">
         <v>6381</v>
@@ -20321,7 +20321,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G688" t="n">
-        <v>10.0340547561646</v>
+        <v>10.0340538024902</v>
       </c>
       <c r="H688" t="n">
         <v>30729</v>
@@ -20350,7 +20350,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H689" t="n">
         <v>40400</v>
@@ -20379,7 +20379,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G690" t="n">
-        <v>10.0159740447998</v>
+        <v>10.0159730911255</v>
       </c>
       <c r="H690" t="n">
         <v>9889</v>
@@ -20408,7 +20408,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G691" t="n">
-        <v>10.0159740447998</v>
+        <v>10.0159730911255</v>
       </c>
       <c r="H691" t="n">
         <v>3173</v>
@@ -20437,7 +20437,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G692" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87134075164795</v>
       </c>
       <c r="H692" t="n">
         <v>17631</v>
@@ -20466,7 +20466,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G693" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87134075164795</v>
       </c>
       <c r="H693" t="n">
         <v>31130</v>
@@ -20495,7 +20495,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G694" t="n">
-        <v>9.90749645233154</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H694" t="n">
         <v>2518</v>
@@ -20553,7 +20553,7 @@
         <v>11</v>
       </c>
       <c r="G696" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H696" t="n">
         <v>20059</v>
@@ -20611,7 +20611,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H698" t="n">
         <v>55492</v>
@@ -20640,7 +20640,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G699" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H699" t="n">
         <v>10609</v>
@@ -20669,7 +20669,7 @@
         <v>10.5</v>
       </c>
       <c r="G700" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H700" t="n">
         <v>19523</v>
@@ -20872,7 +20872,7 @@
         <v>10</v>
       </c>
       <c r="G707" t="n">
-        <v>9.03968715667725</v>
+        <v>9.03968811035156</v>
       </c>
       <c r="H707" t="n">
         <v>24243</v>
@@ -20988,7 +20988,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G711" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H711" t="n">
         <v>17094</v>
@@ -21046,7 +21046,7 @@
         <v>10.5</v>
       </c>
       <c r="G713" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H713" t="n">
         <v>5500</v>
@@ -21075,7 +21075,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H714" t="n">
         <v>5090</v>
@@ -21191,7 +21191,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G718" t="n">
-        <v>9.20240306854248</v>
+        <v>9.20240211486816</v>
       </c>
       <c r="H718" t="n">
         <v>8624</v>
@@ -21220,7 +21220,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H719" t="n">
         <v>7840</v>
@@ -21249,7 +21249,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G720" t="n">
-        <v>9.20240306854248</v>
+        <v>9.20240211486816</v>
       </c>
       <c r="H720" t="n">
         <v>3455</v>
@@ -21278,7 +21278,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H721" t="n">
         <v>7096</v>
@@ -21307,7 +21307,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G722" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H722" t="n">
         <v>15953</v>
@@ -21336,7 +21336,7 @@
         <v>10.5</v>
       </c>
       <c r="G723" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H723" t="n">
         <v>14143</v>
@@ -21394,7 +21394,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G725" t="n">
-        <v>9.63630771636963</v>
+        <v>9.63630676269531</v>
       </c>
       <c r="H725" t="n">
         <v>1284</v>
@@ -21423,7 +21423,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H726" t="n">
         <v>2824</v>
@@ -21452,7 +21452,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G727" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H727" t="n">
         <v>4825</v>
@@ -21568,7 +21568,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H731" t="n">
         <v>12349</v>
@@ -21626,7 +21626,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G733" t="n">
-        <v>9.50975131988525</v>
+        <v>9.50975227355957</v>
       </c>
       <c r="H733" t="n">
         <v>8632</v>
@@ -21713,7 +21713,7 @@
         <v>10.5</v>
       </c>
       <c r="G736" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H736" t="n">
         <v>4129</v>
@@ -21742,7 +21742,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G737" t="n">
-        <v>9.22048091888428</v>
+        <v>9.22048187255859</v>
       </c>
       <c r="H737" t="n">
         <v>11370</v>
@@ -21771,7 +21771,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G738" t="n">
-        <v>9.07584571838379</v>
+        <v>9.07584667205811</v>
       </c>
       <c r="H738" t="n">
         <v>213763</v>
@@ -21916,7 +21916,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G743" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H743" t="n">
         <v>6091</v>
@@ -21945,7 +21945,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G744" t="n">
-        <v>9.79902267456055</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H744" t="n">
         <v>8959</v>
@@ -21974,7 +21974,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G745" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H745" t="n">
         <v>887</v>
@@ -22003,7 +22003,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H746" t="n">
         <v>14467</v>
@@ -22032,7 +22032,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H747" t="n">
         <v>30322</v>
@@ -22061,7 +22061,7 @@
         <v>11</v>
       </c>
       <c r="G748" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H748" t="n">
         <v>18473</v>
@@ -22090,7 +22090,7 @@
         <v>11</v>
       </c>
       <c r="G749" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H749" t="n">
         <v>4869</v>
@@ -22119,7 +22119,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G750" t="n">
-        <v>10.2871656417847</v>
+        <v>10.2871646881104</v>
       </c>
       <c r="H750" t="n">
         <v>13018</v>
@@ -22206,7 +22206,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H753" t="n">
         <v>6719</v>
@@ -22235,7 +22235,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G754" t="n">
-        <v>9.56398868560791</v>
+        <v>9.56398963928223</v>
       </c>
       <c r="H754" t="n">
         <v>101447</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H755" t="n">
         <v>4220</v>
@@ -22641,7 +22641,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G768" t="n">
-        <v>10.1606101989746</v>
+        <v>10.160608291626</v>
       </c>
       <c r="H768" t="n">
         <v>22749</v>
@@ -22815,7 +22815,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G774" t="n">
-        <v>10.0159740447998</v>
+        <v>10.0159730911255</v>
       </c>
       <c r="H774" t="n">
         <v>5108</v>
@@ -22902,7 +22902,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G777" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H777" t="n">
         <v>16106</v>
@@ -22931,7 +22931,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H778" t="n">
         <v>12021</v>
@@ -23018,7 +23018,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>10.0340547561646</v>
+        <v>10.0340538024902</v>
       </c>
       <c r="H781" t="n">
         <v>9947</v>
@@ -23047,7 +23047,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G782" t="n">
-        <v>9.90749645233154</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H782" t="n">
         <v>4037</v>
@@ -23076,7 +23076,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G783" t="n">
-        <v>10.2148475646973</v>
+        <v>10.2148466110229</v>
       </c>
       <c r="H783" t="n">
         <v>56394</v>
@@ -23105,7 +23105,7 @@
         <v>11.2399997711182</v>
       </c>
       <c r="G784" t="n">
-        <v>10.1606101989746</v>
+        <v>10.160608291626</v>
       </c>
       <c r="H784" t="n">
         <v>7827</v>
@@ -23163,7 +23163,7 @@
         <v>10.5</v>
       </c>
       <c r="G786" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H786" t="n">
         <v>47266</v>
@@ -23192,7 +23192,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G787" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H787" t="n">
         <v>10528</v>
@@ -23250,7 +23250,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H789" t="n">
         <v>8577</v>
@@ -23279,7 +23279,7 @@
         <v>10.5200004577637</v>
       </c>
       <c r="G790" t="n">
-        <v>9.50975131988525</v>
+        <v>9.50975227355957</v>
       </c>
       <c r="H790" t="n">
         <v>19851</v>
@@ -23308,7 +23308,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>9.58206844329834</v>
+        <v>9.58207035064697</v>
       </c>
       <c r="H791" t="n">
         <v>1816</v>
@@ -23366,7 +23366,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G793" t="n">
-        <v>9.56398868560791</v>
+        <v>9.56398963928223</v>
       </c>
       <c r="H793" t="n">
         <v>16136</v>
@@ -23453,7 +23453,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G796" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H796" t="n">
         <v>7098</v>
@@ -23482,7 +23482,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G797" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H797" t="n">
         <v>19404</v>
@@ -23511,7 +23511,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>9.76286315917969</v>
+        <v>9.76286220550537</v>
       </c>
       <c r="H798" t="n">
         <v>3557</v>
@@ -23540,7 +23540,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G799" t="n">
-        <v>9.81710052490234</v>
+        <v>9.81709957122803</v>
       </c>
       <c r="H799" t="n">
         <v>13868</v>
@@ -23569,7 +23569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H800" t="n">
         <v>3357</v>
@@ -23598,7 +23598,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H801" t="n">
         <v>3647</v>
@@ -23627,7 +23627,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G802" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H802" t="n">
         <v>1774</v>
@@ -23656,7 +23656,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G803" t="n">
-        <v>9.81710052490234</v>
+        <v>9.81709957122803</v>
       </c>
       <c r="H803" t="n">
         <v>23009</v>
@@ -23685,7 +23685,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G804" t="n">
-        <v>9.72670459747314</v>
+        <v>9.72670364379883</v>
       </c>
       <c r="H804" t="n">
         <v>18395</v>
@@ -23714,7 +23714,7 @@
         <v>10.8599996566772</v>
       </c>
       <c r="G805" t="n">
-        <v>9.81710052490234</v>
+        <v>9.81709957122803</v>
       </c>
       <c r="H805" t="n">
         <v>11612</v>
@@ -23743,7 +23743,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G806" t="n">
-        <v>9.90749645233154</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H806" t="n">
         <v>3793</v>
@@ -23830,7 +23830,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G809" t="n">
-        <v>10.0159740447998</v>
+        <v>10.0159730911255</v>
       </c>
       <c r="H809" t="n">
         <v>34701</v>
@@ -23917,7 +23917,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G812" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882930755615</v>
       </c>
       <c r="H812" t="n">
         <v>6418</v>
@@ -23946,7 +23946,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>9.85325813293457</v>
+        <v>9.8532600402832</v>
       </c>
       <c r="H813" t="n">
         <v>10082</v>
@@ -23975,7 +23975,7 @@
         <v>11</v>
       </c>
       <c r="G814" t="n">
-        <v>9.9436559677124</v>
+        <v>9.94365692138672</v>
       </c>
       <c r="H814" t="n">
         <v>6928</v>
@@ -24004,7 +24004,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G815" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H815" t="n">
         <v>5006</v>
@@ -24033,7 +24033,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G816" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521335601807</v>
       </c>
       <c r="H816" t="n">
         <v>14899</v>
@@ -24062,7 +24062,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G817" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H817" t="n">
         <v>1778</v>
@@ -24091,7 +24091,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G818" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521335601807</v>
       </c>
       <c r="H818" t="n">
         <v>1167</v>
@@ -24236,7 +24236,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G823" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H823" t="n">
         <v>7047</v>
@@ -24294,7 +24294,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G825" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87134075164795</v>
       </c>
       <c r="H825" t="n">
         <v>15736</v>
@@ -24352,7 +24352,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G827" t="n">
-        <v>10.1425294876099</v>
+        <v>10.1425313949585</v>
       </c>
       <c r="H827" t="n">
         <v>6100</v>
@@ -24410,7 +24410,7 @@
         <v>11.0600004196167</v>
       </c>
       <c r="G829" t="n">
-        <v>9.99789524078369</v>
+        <v>9.99789428710938</v>
       </c>
       <c r="H829" t="n">
         <v>6853</v>
@@ -24439,7 +24439,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G830" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521335601807</v>
       </c>
       <c r="H830" t="n">
         <v>3659</v>
@@ -24468,7 +24468,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G831" t="n">
-        <v>10.1063709259033</v>
+        <v>10.1063718795776</v>
       </c>
       <c r="H831" t="n">
         <v>7589</v>
@@ -24497,7 +24497,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>10.2690849304199</v>
+        <v>10.2690858840942</v>
       </c>
       <c r="H832" t="n">
         <v>2890</v>
@@ -24526,7 +24526,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>10.3052425384521</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H833" t="n">
         <v>1557</v>
@@ -24584,7 +24584,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G835" t="n">
-        <v>10.3233242034912</v>
+        <v>10.3233232498169</v>
       </c>
       <c r="H835" t="n">
         <v>1416</v>
@@ -24613,7 +24613,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G836" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882930755615</v>
       </c>
       <c r="H836" t="n">
         <v>23721</v>
@@ -24671,7 +24671,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2871656417847</v>
+        <v>10.2871646881104</v>
       </c>
       <c r="H838" t="n">
         <v>8300</v>
@@ -24700,7 +24700,7 @@
         <v>11.4399995803833</v>
       </c>
       <c r="G839" t="n">
-        <v>10.341402053833</v>
+        <v>10.3414011001587</v>
       </c>
       <c r="H839" t="n">
         <v>7718</v>
@@ -24816,7 +24816,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G843" t="n">
-        <v>10.630672454834</v>
+        <v>10.6306734085083</v>
       </c>
       <c r="H843" t="n">
         <v>1266</v>
@@ -24932,7 +24932,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G847" t="n">
-        <v>10.7933874130249</v>
+        <v>10.7933855056763</v>
       </c>
       <c r="H847" t="n">
         <v>2716</v>
@@ -25019,7 +25019,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G850" t="n">
-        <v>10.576434135437</v>
+        <v>10.5764350891113</v>
       </c>
       <c r="H850" t="n">
         <v>3246</v>
@@ -25048,7 +25048,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G851" t="n">
-        <v>10.5041170120239</v>
+        <v>10.5041179656982</v>
       </c>
       <c r="H851" t="n">
         <v>1739</v>
@@ -25135,7 +25135,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G854" t="n">
-        <v>10.5041170120239</v>
+        <v>10.5041179656982</v>
       </c>
       <c r="H854" t="n">
         <v>7715</v>
@@ -25193,7 +25193,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="n">
-        <v>10.3052425384521</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H856" t="n">
         <v>4772</v>
@@ -25251,7 +25251,7 @@
         <v>11.6199998855591</v>
       </c>
       <c r="G858" t="n">
-        <v>10.5041170120239</v>
+        <v>10.5041179656982</v>
       </c>
       <c r="H858" t="n">
         <v>36908</v>
@@ -25425,7 +25425,7 @@
         <v>12.1599998474121</v>
       </c>
       <c r="G864" t="n">
-        <v>11.1603374481201</v>
+        <v>11.1603384017944</v>
       </c>
       <c r="H864" t="n">
         <v>7555</v>
@@ -25541,7 +25541,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G868" t="n">
-        <v>10.7381534576416</v>
+        <v>10.7381525039673</v>
       </c>
       <c r="H868" t="n">
         <v>10832</v>
@@ -25686,7 +25686,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G873" t="n">
-        <v>10.5913076400757</v>
+        <v>10.5913066864014</v>
       </c>
       <c r="H873" t="n">
         <v>6868</v>
@@ -25715,7 +25715,7 @@
         <v>11.5200004577637</v>
       </c>
       <c r="G874" t="n">
-        <v>10.5729513168335</v>
+        <v>10.5729522705078</v>
       </c>
       <c r="H874" t="n">
         <v>3413</v>
@@ -25744,7 +25744,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G875" t="n">
-        <v>10.7014427185059</v>
+        <v>10.7014417648315</v>
       </c>
       <c r="H875" t="n">
         <v>4362</v>
@@ -25773,7 +25773,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G876" t="n">
-        <v>10.5913076400757</v>
+        <v>10.5913066864014</v>
       </c>
       <c r="H876" t="n">
         <v>7097</v>
@@ -25802,7 +25802,7 @@
         <v>11.6400003433228</v>
       </c>
       <c r="G877" t="n">
-        <v>10.6830863952637</v>
+        <v>10.683087348938</v>
       </c>
       <c r="H877" t="n">
         <v>13386</v>
@@ -25918,7 +25918,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G881" t="n">
-        <v>10.7014427185059</v>
+        <v>10.7014417648315</v>
       </c>
       <c r="H881" t="n">
         <v>1323</v>
@@ -26121,7 +26121,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G888" t="n">
-        <v>10.2241916656494</v>
+        <v>10.2241926193237</v>
       </c>
       <c r="H888" t="n">
         <v>12964</v>
@@ -26150,7 +26150,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G889" t="n">
-        <v>10.2241916656494</v>
+        <v>10.2241926193237</v>
       </c>
       <c r="H889" t="n">
         <v>19719</v>
@@ -26179,7 +26179,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G890" t="n">
-        <v>10.4261054992676</v>
+        <v>10.4261045455933</v>
       </c>
       <c r="H890" t="n">
         <v>1679</v>
@@ -26208,7 +26208,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G891" t="n">
-        <v>10.2609024047852</v>
+        <v>10.2609033584595</v>
       </c>
       <c r="H891" t="n">
         <v>10764</v>
@@ -26266,7 +26266,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G893" t="n">
-        <v>10.0589876174927</v>
+        <v>10.0589866638184</v>
       </c>
       <c r="H893" t="n">
         <v>17220</v>
@@ -26295,7 +26295,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G894" t="n">
-        <v>10.0589876174927</v>
+        <v>10.0589866638184</v>
       </c>
       <c r="H894" t="n">
         <v>35211</v>
@@ -26353,7 +26353,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H896" t="n">
         <v>6500</v>
@@ -26382,7 +26382,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G897" t="n">
-        <v>10.0222778320312</v>
+        <v>10.0222768783569</v>
       </c>
       <c r="H897" t="n">
         <v>8539</v>
@@ -26440,7 +26440,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G899" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H899" t="n">
         <v>16004</v>
@@ -26469,7 +26469,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G900" t="n">
-        <v>9.85707473754883</v>
+        <v>9.85707378387451</v>
       </c>
       <c r="H900" t="n">
         <v>44216</v>
@@ -26498,7 +26498,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G901" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H901" t="n">
         <v>28647</v>
@@ -26614,7 +26614,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G905" t="n">
-        <v>10.0589876174927</v>
+        <v>10.0589866638184</v>
       </c>
       <c r="H905" t="n">
         <v>2782</v>
@@ -26730,7 +26730,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G909" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H909" t="n">
         <v>4903</v>
@@ -26788,7 +26788,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G911" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H911" t="n">
         <v>22398</v>
@@ -26817,7 +26817,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G912" t="n">
-        <v>9.94885349273682</v>
+        <v>9.9488525390625</v>
       </c>
       <c r="H912" t="n">
         <v>24470</v>
@@ -26875,7 +26875,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G914" t="n">
-        <v>9.85707473754883</v>
+        <v>9.85707378387451</v>
       </c>
       <c r="H914" t="n">
         <v>27648</v>
@@ -26933,7 +26933,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G916" t="n">
-        <v>10.0222778320312</v>
+        <v>10.0222768783569</v>
       </c>
       <c r="H916" t="n">
         <v>8550</v>
@@ -27136,7 +27136,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G923" t="n">
-        <v>9.60009288787842</v>
+        <v>9.6000919342041</v>
       </c>
       <c r="H923" t="n">
         <v>10738</v>
@@ -27223,7 +27223,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G926" t="n">
-        <v>9.60009288787842</v>
+        <v>9.6000919342041</v>
       </c>
       <c r="H926" t="n">
         <v>10973</v>
@@ -27281,7 +27281,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G928" t="n">
-        <v>9.47160148620605</v>
+        <v>9.47160243988037</v>
       </c>
       <c r="H928" t="n">
         <v>4839</v>
@@ -27339,7 +27339,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G930" t="n">
-        <v>9.3798246383667</v>
+        <v>9.37982368469238</v>
       </c>
       <c r="H930" t="n">
         <v>9699</v>
@@ -27397,7 +27397,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G932" t="n">
-        <v>9.28804492950439</v>
+        <v>9.28804397583008</v>
       </c>
       <c r="H932" t="n">
         <v>26076</v>
@@ -27571,7 +27571,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G938" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844921112061</v>
       </c>
       <c r="H938" t="n">
         <v>21054</v>
@@ -27600,7 +27600,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G939" t="n">
-        <v>9.85707473754883</v>
+        <v>9.85707378387451</v>
       </c>
       <c r="H939" t="n">
         <v>24198</v>
@@ -27658,7 +27658,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G941" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H941" t="n">
         <v>27317</v>
@@ -27745,7 +27745,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H944" t="n">
         <v>26985</v>
@@ -27861,7 +27861,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H948" t="n">
         <v>19638</v>
@@ -27890,7 +27890,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H949" t="n">
         <v>1402</v>
@@ -27919,7 +27919,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G950" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H950" t="n">
         <v>26624</v>
@@ -27948,7 +27948,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G951" t="n">
-        <v>9.71022796630859</v>
+        <v>9.71022701263428</v>
       </c>
       <c r="H951" t="n">
         <v>204</v>
@@ -28006,7 +28006,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G953" t="n">
-        <v>9.78365135192871</v>
+        <v>9.78365230560303</v>
       </c>
       <c r="H953" t="n">
         <v>4481</v>
@@ -28035,7 +28035,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G954" t="n">
-        <v>9.78365135192871</v>
+        <v>9.78365230560303</v>
       </c>
       <c r="H954" t="n">
         <v>9011</v>
@@ -28122,7 +28122,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G957" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H957" t="n">
         <v>3996</v>
@@ -28325,7 +28325,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G964" t="n">
-        <v>9.60009288787842</v>
+        <v>9.6000919342041</v>
       </c>
       <c r="H964" t="n">
         <v>26638</v>
@@ -28354,7 +28354,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>9.72858333587646</v>
+        <v>9.72858428955078</v>
       </c>
       <c r="H965" t="n">
         <v>3128</v>
@@ -28412,7 +28412,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G967" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844921112061</v>
       </c>
       <c r="H967" t="n">
         <v>6277</v>
@@ -28470,7 +28470,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G969" t="n">
-        <v>9.71022796630859</v>
+        <v>9.71022701263428</v>
       </c>
       <c r="H969" t="n">
         <v>9842</v>
@@ -28615,7 +28615,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G974" t="n">
-        <v>9.60009288787842</v>
+        <v>9.6000919342041</v>
       </c>
       <c r="H974" t="n">
         <v>6350</v>
@@ -28731,7 +28731,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G978" t="n">
-        <v>9.67351627349854</v>
+        <v>9.67351722717285</v>
       </c>
       <c r="H978" t="n">
         <v>5885</v>
@@ -28789,7 +28789,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G980" t="n">
-        <v>9.67351627349854</v>
+        <v>9.67351722717285</v>
       </c>
       <c r="H980" t="n">
         <v>16583</v>
@@ -28847,7 +28847,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844921112061</v>
       </c>
       <c r="H982" t="n">
         <v>13221</v>
@@ -28876,7 +28876,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G983" t="n">
-        <v>9.67351627349854</v>
+        <v>9.67351722717285</v>
       </c>
       <c r="H983" t="n">
         <v>16050</v>
@@ -28905,7 +28905,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G984" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844921112061</v>
       </c>
       <c r="H984" t="n">
         <v>32880</v>
@@ -28963,7 +28963,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G986" t="n">
-        <v>9.5083122253418</v>
+        <v>9.50831317901611</v>
       </c>
       <c r="H986" t="n">
         <v>19204</v>
@@ -29224,7 +29224,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G995" t="n">
-        <v>10.242546081543</v>
+        <v>10.2425470352173</v>
       </c>
       <c r="H995" t="n">
         <v>110705</v>
@@ -29253,7 +29253,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G996" t="n">
-        <v>10.4261054992676</v>
+        <v>10.4261045455933</v>
       </c>
       <c r="H996" t="n">
         <v>59715</v>
@@ -29311,7 +29311,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G998" t="n">
-        <v>10.2976150512695</v>
+        <v>10.2976140975952</v>
       </c>
       <c r="H998" t="n">
         <v>38169</v>
@@ -29398,7 +29398,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1001" t="n">
-        <v>10.1324110031128</v>
+        <v>10.1324119567871</v>
       </c>
       <c r="H1001" t="n">
         <v>10832</v>
@@ -29427,7 +29427,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1002" t="n">
-        <v>10.0222778320312</v>
+        <v>10.0222768783569</v>
       </c>
       <c r="H1002" t="n">
         <v>3328</v>
@@ -29456,7 +29456,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1003" t="n">
-        <v>10.1324110031128</v>
+        <v>10.1324119567871</v>
       </c>
       <c r="H1003" t="n">
         <v>13007</v>
@@ -29514,7 +29514,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1005" t="n">
-        <v>10.0222778320312</v>
+        <v>10.0222768783569</v>
       </c>
       <c r="H1005" t="n">
         <v>7774</v>
@@ -29572,7 +29572,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G1007" t="n">
-        <v>9.85707473754883</v>
+        <v>9.85707378387451</v>
       </c>
       <c r="H1007" t="n">
         <v>27304</v>
@@ -29601,7 +29601,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1008" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H1008" t="n">
         <v>9037</v>
@@ -29659,7 +29659,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G1010" t="n">
-        <v>10.0222778320312</v>
+        <v>10.0222768783569</v>
       </c>
       <c r="H1010" t="n">
         <v>23276</v>
@@ -29717,7 +29717,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.94885349273682</v>
+        <v>9.9488525390625</v>
       </c>
       <c r="H1012" t="n">
         <v>14824</v>
@@ -29746,7 +29746,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1013" t="n">
-        <v>9.91214275360107</v>
+        <v>9.91214179992676</v>
       </c>
       <c r="H1013" t="n">
         <v>16781</v>
@@ -29833,7 +29833,7 @@
         <v>10.539999961853</v>
       </c>
       <c r="G1016" t="n">
-        <v>9.67351627349854</v>
+        <v>9.67351722717285</v>
       </c>
       <c r="H1016" t="n">
         <v>21532</v>
@@ -29862,7 +29862,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1017" t="n">
-        <v>9.56338214874268</v>
+        <v>9.56338119506836</v>
       </c>
       <c r="H1017" t="n">
         <v>16281</v>
@@ -30036,7 +30036,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1023" t="n">
-        <v>9.56338214874268</v>
+        <v>9.56338119506836</v>
       </c>
       <c r="H1023" t="n">
         <v>17077</v>
@@ -30152,7 +30152,7 @@
         <v>10.4200000762939</v>
       </c>
       <c r="G1027" t="n">
-        <v>9.56338214874268</v>
+        <v>9.56338119506836</v>
       </c>
       <c r="H1027" t="n">
         <v>46429</v>
@@ -30239,7 +30239,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844921112061</v>
       </c>
       <c r="H1030" t="n">
         <v>97562</v>
@@ -30326,7 +30326,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>9.3614673614502</v>
+        <v>9.36146640777588</v>
       </c>
       <c r="H1033" t="n">
         <v>18579</v>
@@ -30355,7 +30355,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G1034" t="n">
-        <v>9.34311294555664</v>
+        <v>9.34311199188232</v>
       </c>
       <c r="H1034" t="n">
         <v>146201</v>
@@ -30413,7 +30413,7 @@
         <v>10</v>
       </c>
       <c r="G1036" t="n">
-        <v>9.1779088973999</v>
+        <v>9.17790985107422</v>
       </c>
       <c r="H1036" t="n">
         <v>63272</v>
@@ -30500,7 +30500,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>9.25133323669434</v>
+        <v>9.2513313293457</v>
       </c>
       <c r="H1039" t="n">
         <v>20536</v>
@@ -30529,7 +30529,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1040" t="n">
-        <v>9.28804492950439</v>
+        <v>9.28804397583008</v>
       </c>
       <c r="H1040" t="n">
         <v>15887</v>
@@ -30558,7 +30558,7 @@
         <v>10</v>
       </c>
       <c r="G1041" t="n">
-        <v>9.1779088973999</v>
+        <v>9.17790985107422</v>
       </c>
       <c r="H1041" t="n">
         <v>52588</v>
@@ -30587,7 +30587,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1042" t="n">
-        <v>9.21461963653564</v>
+        <v>9.21462059020996</v>
       </c>
       <c r="H1042" t="n">
         <v>34966</v>
@@ -30616,7 +30616,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.19626426696777</v>
+        <v>9.19626617431641</v>
       </c>
       <c r="H1043" t="n">
         <v>7574</v>
@@ -30645,7 +30645,7 @@
         <v>10</v>
       </c>
       <c r="G1044" t="n">
-        <v>9.1779088973999</v>
+        <v>9.17790985107422</v>
       </c>
       <c r="H1044" t="n">
         <v>54355</v>
@@ -30674,7 +30674,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>9.25133323669434</v>
+        <v>9.2513313293457</v>
       </c>
       <c r="H1045" t="n">
         <v>20501</v>
@@ -30703,7 +30703,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1046" t="n">
-        <v>9.12284088134766</v>
+        <v>9.12284183502197</v>
       </c>
       <c r="H1046" t="n">
         <v>57268</v>
@@ -30732,7 +30732,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1047" t="n">
-        <v>9.1595516204834</v>
+        <v>9.15955257415771</v>
       </c>
       <c r="H1047" t="n">
         <v>53010</v>
@@ -30819,7 +30819,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1050" t="n">
-        <v>9.47160148620605</v>
+        <v>9.47160243988037</v>
       </c>
       <c r="H1050" t="n">
         <v>28228</v>
@@ -30848,7 +30848,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G1051" t="n">
-        <v>9.41653537750244</v>
+        <v>9.41653442382812</v>
       </c>
       <c r="H1051" t="n">
         <v>24742</v>
@@ -30877,7 +30877,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>9.47160148620605</v>
+        <v>9.47160243988037</v>
       </c>
       <c r="H1052" t="n">
         <v>36025</v>
@@ -30906,7 +30906,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.95763969421387</v>
+        <v>8.95763874053955</v>
       </c>
       <c r="H1053" t="n">
         <v>104412</v>
@@ -30935,7 +30935,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1054" t="n">
-        <v>8.90257167816162</v>
+        <v>8.90257263183594</v>
       </c>
       <c r="H1054" t="n">
         <v>69409</v>
@@ -30964,7 +30964,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1055" t="n">
-        <v>9.06777477264404</v>
+        <v>9.06777381896973</v>
       </c>
       <c r="H1055" t="n">
         <v>19159</v>
@@ -31051,7 +31051,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.55381011962891</v>
+        <v>8.55381107330322</v>
       </c>
       <c r="H1058" t="n">
         <v>39327</v>
@@ -31080,7 +31080,7 @@
         <v>9.25</v>
       </c>
       <c r="G1059" t="n">
-        <v>8.4895658493042</v>
+        <v>8.48956680297852</v>
       </c>
       <c r="H1059" t="n">
         <v>51027</v>
@@ -31138,7 +31138,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.26929664611816</v>
+        <v>8.26929569244385</v>
       </c>
       <c r="H1061" t="n">
         <v>66806</v>
@@ -31196,7 +31196,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1063" t="n">
-        <v>7.95724630355835</v>
+        <v>7.95724678039551</v>
       </c>
       <c r="H1063" t="n">
         <v>59201</v>
@@ -31225,7 +31225,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.75533390045166</v>
+        <v>7.7553334236145</v>
       </c>
       <c r="H1064" t="n">
         <v>54217</v>
@@ -31254,7 +31254,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G1065" t="n">
-        <v>7.8930025100708</v>
+        <v>7.89300203323364</v>
       </c>
       <c r="H1065" t="n">
         <v>40094</v>
@@ -31312,7 +31312,7 @@
         <v>8.5</v>
       </c>
       <c r="G1067" t="n">
-        <v>7.80122184753418</v>
+        <v>7.80122327804565</v>
       </c>
       <c r="H1067" t="n">
         <v>78080</v>
@@ -31341,7 +31341,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G1068" t="n">
-        <v>7.4524621963501</v>
+        <v>7.45246267318726</v>
       </c>
       <c r="H1068" t="n">
         <v>65818</v>
@@ -31399,7 +31399,7 @@
         <v>8.5</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.80122184753418</v>
+        <v>7.80122327804565</v>
       </c>
       <c r="H1070" t="n">
         <v>116366</v>
@@ -31457,7 +31457,7 @@
         <v>8.67000007629395</v>
       </c>
       <c r="G1072" t="n">
-        <v>7.95724630355835</v>
+        <v>7.95724678039551</v>
       </c>
       <c r="H1072" t="n">
         <v>133604</v>
@@ -31486,7 +31486,7 @@
         <v>9.25</v>
       </c>
       <c r="G1073" t="n">
-        <v>8.4895658493042</v>
+        <v>8.48956680297852</v>
       </c>
       <c r="H1073" t="n">
         <v>124900</v>
@@ -31515,7 +31515,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G1074" t="n">
-        <v>8.70065784454346</v>
+        <v>8.70065689086914</v>
       </c>
       <c r="H1074" t="n">
         <v>33804</v>
@@ -31544,7 +31544,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1075" t="n">
-        <v>8.92092800140381</v>
+        <v>8.92092704772949</v>
       </c>
       <c r="H1075" t="n">
         <v>103705</v>
@@ -31602,7 +31602,7 @@
         <v>10.2200002670288</v>
       </c>
       <c r="G1077" t="n">
-        <v>9.3798246383667</v>
+        <v>9.37982368469238</v>
       </c>
       <c r="H1077" t="n">
         <v>116095</v>
@@ -31660,7 +31660,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.02188491821289</v>
+        <v>9.02188396453857</v>
       </c>
       <c r="H1079" t="n">
         <v>54346</v>
@@ -31747,7 +31747,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1082" t="n">
-        <v>9.26968955993652</v>
+        <v>9.26968765258789</v>
       </c>
       <c r="H1082" t="n">
         <v>39878</v>
@@ -31805,7 +31805,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1084" t="n">
-        <v>9.26968955993652</v>
+        <v>9.26968765258789</v>
       </c>
       <c r="H1084" t="n">
         <v>32225</v>
@@ -31921,7 +31921,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G1088" t="n">
-        <v>9.26968955993652</v>
+        <v>9.26968765258789</v>
       </c>
       <c r="H1088" t="n">
         <v>18575</v>
@@ -31950,7 +31950,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G1089" t="n">
-        <v>8.97599601745605</v>
+        <v>8.97599506378174</v>
       </c>
       <c r="H1089" t="n">
         <v>44911</v>
@@ -32008,7 +32008,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G1091" t="n">
-        <v>9.31557750701904</v>
+        <v>9.31557655334473</v>
       </c>
       <c r="H1091" t="n">
         <v>9462</v>
@@ -32066,7 +32066,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.10448551177979</v>
+        <v>9.1044864654541</v>
       </c>
       <c r="H1093" t="n">
         <v>20767</v>
@@ -32124,7 +32124,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.10448551177979</v>
+        <v>9.1044864654541</v>
       </c>
       <c r="H1095" t="n">
         <v>16121</v>
@@ -32211,7 +32211,7 @@
         <v>9.5</v>
       </c>
       <c r="G1098" t="n">
-        <v>8.71901512145996</v>
+        <v>8.71901321411133</v>
       </c>
       <c r="H1098" t="n">
         <v>162659</v>
@@ -32240,7 +32240,7 @@
         <v>9.88000011444092</v>
       </c>
       <c r="G1099" t="n">
-        <v>9.06777477264404</v>
+        <v>9.06777381896973</v>
       </c>
       <c r="H1099" t="n">
         <v>13246</v>
@@ -32298,7 +32298,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.82914924621582</v>
+        <v>8.8291482925415</v>
       </c>
       <c r="H1101" t="n">
         <v>13070</v>
@@ -32327,7 +32327,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G1102" t="n">
-        <v>8.92092800140381</v>
+        <v>8.92092704772949</v>
       </c>
       <c r="H1102" t="n">
         <v>6908</v>
@@ -32414,7 +32414,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G1105" t="n">
-        <v>8.81079292297363</v>
+        <v>8.81079196929932</v>
       </c>
       <c r="H1105" t="n">
         <v>9622</v>
@@ -32472,7 +32472,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1107" t="n">
-        <v>8.90257167816162</v>
+        <v>8.90257263183594</v>
       </c>
       <c r="H1107" t="n">
         <v>3981</v>
@@ -32501,7 +32501,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1108" t="n">
-        <v>8.57216644287109</v>
+        <v>8.57216739654541</v>
       </c>
       <c r="H1108" t="n">
         <v>17767</v>
@@ -32646,7 +32646,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G1113" t="n">
-        <v>8.90257167816162</v>
+        <v>8.90257263183594</v>
       </c>
       <c r="H1113" t="n">
         <v>38309</v>
@@ -32675,7 +32675,7 @@
         <v>9.9399995803833</v>
       </c>
       <c r="G1114" t="n">
-        <v>9.12284088134766</v>
+        <v>9.12284183502197</v>
       </c>
       <c r="H1114" t="n">
         <v>147327</v>
@@ -32791,7 +32791,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G1118" t="n">
-        <v>9.62265968322754</v>
+        <v>9.62265872955322</v>
       </c>
       <c r="H1118" t="n">
         <v>23870</v>
@@ -32849,7 +32849,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1120" t="n">
-        <v>9.90293121337891</v>
+        <v>9.90293216705322</v>
       </c>
       <c r="H1120" t="n">
         <v>28022</v>
@@ -32878,7 +32878,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1121" t="n">
-        <v>9.8562183380127</v>
+        <v>9.85621929168701</v>
       </c>
       <c r="H1121" t="n">
         <v>13948</v>
@@ -33052,7 +33052,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1127" t="n">
-        <v>10.0897798538208</v>
+        <v>10.0897789001465</v>
       </c>
       <c r="H1127" t="n">
         <v>55048</v>
@@ -33081,7 +33081,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1128" t="n">
-        <v>9.8562183380127</v>
+        <v>9.85621929168701</v>
       </c>
       <c r="H1128" t="n">
         <v>62153</v>
@@ -33139,7 +33139,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1130" t="n">
-        <v>9.9496431350708</v>
+        <v>9.94964218139648</v>
       </c>
       <c r="H1130" t="n">
         <v>17077</v>
@@ -33168,7 +33168,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1131" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1131" t="n">
         <v>41503</v>
@@ -33197,7 +33197,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1132" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1132" t="n">
         <v>20171</v>
@@ -33226,7 +33226,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1133" t="n">
-        <v>10.0897798538208</v>
+        <v>10.0897789001465</v>
       </c>
       <c r="H1133" t="n">
         <v>24494</v>
@@ -33371,7 +33371,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1138" t="n">
-        <v>10.0897798538208</v>
+        <v>10.0897789001465</v>
       </c>
       <c r="H1138" t="n">
         <v>27760</v>
@@ -33400,7 +33400,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G1139" t="n">
-        <v>9.8562183380127</v>
+        <v>9.85621929168701</v>
       </c>
       <c r="H1139" t="n">
         <v>49023</v>
@@ -33661,7 +33661,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1148" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1148" t="n">
         <v>30992</v>
@@ -33690,7 +33690,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1149" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1149" t="n">
         <v>20120</v>
@@ -33719,7 +33719,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1150" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1150" t="n">
         <v>8179</v>
@@ -33748,7 +33748,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1151" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1151" t="n">
         <v>6280</v>
@@ -33835,7 +33835,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1154" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1154" t="n">
         <v>2757</v>
@@ -34067,7 +34067,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1162" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1162" t="n">
         <v>2243</v>
@@ -34096,7 +34096,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1163" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1163" t="n">
         <v>9891</v>
@@ -34212,7 +34212,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G1167" t="n">
-        <v>9.90293121337891</v>
+        <v>9.90293216705322</v>
       </c>
       <c r="H1167" t="n">
         <v>65820</v>
@@ -34241,7 +34241,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1168" t="n">
-        <v>9.9496431350708</v>
+        <v>9.94964218139648</v>
       </c>
       <c r="H1168" t="n">
         <v>7485</v>
@@ -34270,7 +34270,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G1169" t="n">
-        <v>9.9496431350708</v>
+        <v>9.94964218139648</v>
       </c>
       <c r="H1169" t="n">
         <v>17178</v>
@@ -34415,7 +34415,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1174" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1174" t="n">
         <v>11795</v>
@@ -34589,7 +34589,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.4167623519897</v>
+        <v>10.4167633056641</v>
       </c>
       <c r="H1180" t="n">
         <v>27377</v>
@@ -34705,7 +34705,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1184" t="n">
-        <v>10.0897798538208</v>
+        <v>10.0897789001465</v>
       </c>
       <c r="H1184" t="n">
         <v>46001</v>
@@ -34734,7 +34734,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1185" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1185" t="n">
         <v>12879</v>
@@ -34763,7 +34763,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1186" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1186" t="n">
         <v>11157</v>
@@ -34792,7 +34792,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1187" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1187" t="n">
         <v>190163</v>
@@ -34821,7 +34821,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G1188" t="n">
-        <v>10.0897798538208</v>
+        <v>10.0897789001465</v>
       </c>
       <c r="H1188" t="n">
         <v>9625</v>
@@ -34879,7 +34879,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>10.1364917755127</v>
+        <v>10.1364908218384</v>
       </c>
       <c r="H1190" t="n">
         <v>3487</v>
@@ -35111,7 +35111,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.1174421310425</v>
+        <v>11.1174411773682</v>
       </c>
       <c r="H1198" t="n">
         <v>103624</v>
@@ -35285,7 +35285,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>10.6970348358154</v>
+        <v>10.6970357894897</v>
       </c>
       <c r="H1204" t="n">
         <v>26462</v>
@@ -35314,7 +35314,7 @@
         <v>11.5</v>
       </c>
       <c r="G1205" t="n">
-        <v>10.743745803833</v>
+        <v>10.7437467575073</v>
       </c>
       <c r="H1205" t="n">
         <v>21545</v>
@@ -35633,7 +35633,7 @@
         <v>11.5</v>
       </c>
       <c r="G1216" t="n">
-        <v>10.743745803833</v>
+        <v>10.7437467575073</v>
       </c>
       <c r="H1216" t="n">
         <v>169797</v>
@@ -35662,7 +35662,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>10.6970348358154</v>
+        <v>10.6970357894897</v>
       </c>
       <c r="H1217" t="n">
         <v>16353</v>
@@ -35691,7 +35691,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.7904586791992</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1218" t="n">
         <v>32050</v>
@@ -35749,7 +35749,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>10.7904586791992</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1220" t="n">
         <v>10357</v>
@@ -35778,7 +35778,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1221" t="n">
-        <v>10.7904586791992</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1221" t="n">
         <v>46127</v>
@@ -35807,7 +35807,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1222" t="n">
-        <v>10.7904586791992</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1222" t="n">
         <v>30407</v>
@@ -35894,7 +35894,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>10.6970348358154</v>
+        <v>10.6970357894897</v>
       </c>
       <c r="H1225" t="n">
         <v>18947</v>
@@ -36126,7 +36126,7 @@
         <v>11.5</v>
       </c>
       <c r="G1233" t="n">
-        <v>10.743745803833</v>
+        <v>10.7437467575073</v>
       </c>
       <c r="H1233" t="n">
         <v>353394</v>
@@ -36155,7 +36155,7 @@
         <v>11.5</v>
       </c>
       <c r="G1234" t="n">
-        <v>10.743745803833</v>
+        <v>10.7437467575073</v>
       </c>
       <c r="H1234" t="n">
         <v>23018</v>
@@ -36184,7 +36184,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>10.7904586791992</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1235" t="n">
         <v>130559</v>
@@ -36271,7 +36271,7 @@
         <v>12.25</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.4444246292114</v>
+        <v>11.4444255828857</v>
       </c>
       <c r="H1238" t="n">
         <v>109803</v>
@@ -36474,7 +36474,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G1245" t="n">
-        <v>11.5845613479614</v>
+        <v>11.5845603942871</v>
       </c>
       <c r="H1245" t="n">
         <v>54904</v>
@@ -36503,7 +36503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.6312732696533</v>
+        <v>11.631272315979</v>
       </c>
       <c r="H1246" t="n">
         <v>74739</v>
@@ -36561,7 +36561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.6312732696533</v>
+        <v>11.631272315979</v>
       </c>
       <c r="H1248" t="n">
         <v>16479</v>
@@ -36909,7 +36909,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.518798828125</v>
+        <v>12.5187997817993</v>
       </c>
       <c r="H1260" t="n">
         <v>19578</v>
@@ -36938,7 +36938,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>12.518798828125</v>
+        <v>12.5187997817993</v>
       </c>
       <c r="H1261" t="n">
         <v>143329</v>
@@ -37141,7 +37141,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.8924951553345</v>
+        <v>12.8924942016602</v>
       </c>
       <c r="H1268" t="n">
         <v>26997</v>
@@ -37228,7 +37228,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1271" t="n">
-        <v>13.3596143722534</v>
+        <v>13.3596153259277</v>
       </c>
       <c r="H1271" t="n">
         <v>108130</v>
@@ -37257,7 +37257,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1272" t="n">
-        <v>13.7333116531372</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1272" t="n">
         <v>66362</v>
@@ -37344,7 +37344,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1275" t="n">
-        <v>13.3596143722534</v>
+        <v>13.3596153259277</v>
       </c>
       <c r="H1275" t="n">
         <v>47009</v>
@@ -37402,7 +37402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>13.7333116531372</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1277" t="n">
         <v>44773</v>
@@ -37431,7 +37431,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.7333116531372</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1278" t="n">
         <v>25963</v>
@@ -37547,7 +37547,7 @@
         <v>14.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>13.7800235748291</v>
+        <v>13.7800226211548</v>
       </c>
       <c r="H1282" t="n">
         <v>46705</v>
@@ -37576,7 +37576,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1283" t="n">
-        <v>13.8734474182129</v>
+        <v>13.8734464645386</v>
       </c>
       <c r="H1283" t="n">
         <v>36622</v>
@@ -37605,7 +37605,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1284" t="n">
-        <v>13.8734474182129</v>
+        <v>13.8734464645386</v>
       </c>
       <c r="H1284" t="n">
         <v>26650</v>
@@ -37692,7 +37692,7 @@
         <v>14.75</v>
       </c>
       <c r="G1287" t="n">
-        <v>13.7800235748291</v>
+        <v>13.7800226211548</v>
       </c>
       <c r="H1287" t="n">
         <v>62941</v>
@@ -37866,7 +37866,7 @@
         <v>15</v>
       </c>
       <c r="G1293" t="n">
-        <v>14.0135812759399</v>
+        <v>14.0135822296143</v>
       </c>
       <c r="H1293" t="n">
         <v>75979</v>
@@ -37953,7 +37953,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1296" t="n">
-        <v>14.1537179946899</v>
+        <v>14.1537189483643</v>
       </c>
       <c r="H1296" t="n">
         <v>64013</v>
@@ -37982,7 +37982,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.107006072998</v>
+        <v>14.1070070266724</v>
       </c>
       <c r="H1297" t="n">
         <v>52067</v>
@@ -38011,7 +38011,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>13.8734474182129</v>
+        <v>13.8734464645386</v>
       </c>
       <c r="H1298" t="n">
         <v>69004</v>
@@ -38040,7 +38040,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1299" t="n">
-        <v>14.1537179946899</v>
+        <v>14.1537189483643</v>
       </c>
       <c r="H1299" t="n">
         <v>54051</v>
@@ -38127,7 +38127,7 @@
         <v>15</v>
       </c>
       <c r="G1302" t="n">
-        <v>14.0135812759399</v>
+        <v>14.0135822296143</v>
       </c>
       <c r="H1302" t="n">
         <v>62910</v>
@@ -38156,7 +38156,7 @@
         <v>15</v>
       </c>
       <c r="G1303" t="n">
-        <v>14.0135812759399</v>
+        <v>14.0135822296143</v>
       </c>
       <c r="H1303" t="n">
         <v>54734</v>
@@ -38301,7 +38301,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G1308" t="n">
-        <v>14.2938537597656</v>
+        <v>14.2938528060913</v>
       </c>
       <c r="H1308" t="n">
         <v>68894</v>
@@ -38475,7 +38475,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>14.107006072998</v>
+        <v>14.1070070266724</v>
       </c>
       <c r="H1314" t="n">
         <v>141761</v>
@@ -38504,7 +38504,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.107006072998</v>
+        <v>14.1070070266724</v>
       </c>
       <c r="H1315" t="n">
         <v>94574</v>
@@ -38533,7 +38533,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G1316" t="n">
-        <v>14.1537179946899</v>
+        <v>14.1537189483643</v>
       </c>
       <c r="H1316" t="n">
         <v>51497</v>
@@ -38678,7 +38678,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1321" t="n">
-        <v>14.5274143218994</v>
+        <v>14.5274133682251</v>
       </c>
       <c r="H1321" t="n">
         <v>61866</v>
@@ -38707,7 +38707,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.6675491333008</v>
+        <v>14.6675500869751</v>
       </c>
       <c r="H1322" t="n">
         <v>27348</v>
@@ -38765,7 +38765,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1324" t="n">
-        <v>14.6675491333008</v>
+        <v>14.6675500869751</v>
       </c>
       <c r="H1324" t="n">
         <v>41138</v>
@@ -38823,7 +38823,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1326" t="n">
-        <v>14.7609729766846</v>
+        <v>14.7609739303589</v>
       </c>
       <c r="H1326" t="n">
         <v>33249</v>
@@ -38881,7 +38881,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G1328" t="n">
-        <v>14.5274143218994</v>
+        <v>14.5274133682251</v>
       </c>
       <c r="H1328" t="n">
         <v>23169</v>
@@ -38968,7 +38968,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>14.7609729766846</v>
+        <v>14.7609739303589</v>
       </c>
       <c r="H1331" t="n">
         <v>50318</v>
@@ -39055,7 +39055,7 @@
         <v>17</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.8820581436157</v>
+        <v>15.8820600509644</v>
       </c>
       <c r="H1334" t="n">
         <v>62603</v>
@@ -39200,7 +39200,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1339" t="n">
-        <v>16.1062774658203</v>
+        <v>16.1062793731689</v>
       </c>
       <c r="H1339" t="n">
         <v>52146</v>
@@ -39229,7 +39229,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2557563781738</v>
+        <v>16.2557544708252</v>
       </c>
       <c r="H1340" t="n">
         <v>57410</v>
@@ -39287,7 +39287,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.2931251525879</v>
+        <v>16.2931270599365</v>
       </c>
       <c r="H1342" t="n">
         <v>34303</v>
@@ -39403,7 +39403,7 @@
         <v>17</v>
       </c>
       <c r="G1346" t="n">
-        <v>15.8820581436157</v>
+        <v>15.8820600509644</v>
       </c>
       <c r="H1346" t="n">
         <v>29061</v>
@@ -39432,7 +39432,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1347" t="n">
-        <v>15.7699508666992</v>
+        <v>15.7699499130249</v>
       </c>
       <c r="H1347" t="n">
         <v>19151</v>
@@ -39461,7 +39461,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>15.6952114105225</v>
+        <v>15.6952095031738</v>
       </c>
       <c r="H1348" t="n">
         <v>50373</v>
@@ -39490,7 +39490,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1349" t="n">
-        <v>15.844690322876</v>
+        <v>15.8446884155273</v>
       </c>
       <c r="H1349" t="n">
         <v>57071</v>
@@ -39519,7 +39519,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1350" t="n">
-        <v>15.6017894744873</v>
+        <v>15.6017904281616</v>
       </c>
       <c r="H1350" t="n">
         <v>36213</v>
@@ -39548,7 +39548,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1351" t="n">
-        <v>15.6017894744873</v>
+        <v>15.6017904281616</v>
       </c>
       <c r="H1351" t="n">
         <v>27700</v>
@@ -39635,7 +39635,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1354" t="n">
-        <v>15.583104133606</v>
+        <v>15.5831031799316</v>
       </c>
       <c r="H1354" t="n">
         <v>28026</v>
@@ -39780,7 +39780,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1359" t="n">
-        <v>15.5457324981689</v>
+        <v>15.5457315444946</v>
       </c>
       <c r="H1359" t="n">
         <v>57086</v>
@@ -39867,7 +39867,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1362" t="n">
-        <v>15.0412454605103</v>
+        <v>15.0412445068359</v>
       </c>
       <c r="H1362" t="n">
         <v>43659</v>
@@ -39925,7 +39925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>15.6952114105225</v>
+        <v>15.6952095031738</v>
       </c>
       <c r="H1364" t="n">
         <v>54661</v>
@@ -39954,7 +39954,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1365" t="n">
-        <v>15.6017894744873</v>
+        <v>15.6017904281616</v>
       </c>
       <c r="H1365" t="n">
         <v>29256</v>
@@ -39983,7 +39983,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1366" t="n">
-        <v>15.6578426361084</v>
+        <v>15.6578416824341</v>
       </c>
       <c r="H1366" t="n">
         <v>27677</v>
@@ -80096,6 +80096,35 @@
         <v>55236</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>58</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>60.0999984741211</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>57.7000007629395</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>59.7999992370605</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>59.7999992370605</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>55850</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/SOL.MI.xlsx
+++ b/data/SOL.MI.xlsx
@@ -427,7 +427,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G2" t="n">
-        <v>7.09495449066162</v>
+        <v>7.09495401382446</v>
       </c>
       <c r="H2" t="n">
         <v>5513</v>
@@ -485,7 +485,7 @@
         <v>8.24499988555908</v>
       </c>
       <c r="G4" t="n">
-        <v>7.13389015197754</v>
+        <v>7.13388967514038</v>
       </c>
       <c r="H4" t="n">
         <v>1896</v>
@@ -514,7 +514,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G5" t="n">
-        <v>7.10793256759644</v>
+        <v>7.10793304443359</v>
       </c>
       <c r="H5" t="n">
         <v>16215</v>
@@ -543,7 +543,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G6" t="n">
-        <v>7.00843143463135</v>
+        <v>7.00843048095703</v>
       </c>
       <c r="H6" t="n">
         <v>12867</v>
@@ -572,7 +572,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G7" t="n">
-        <v>6.85701370239258</v>
+        <v>6.85701417922974</v>
       </c>
       <c r="H7" t="n">
         <v>13353</v>
@@ -601,7 +601,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G8" t="n">
-        <v>7.00843143463135</v>
+        <v>7.00843048095703</v>
       </c>
       <c r="H8" t="n">
         <v>1721</v>
@@ -630,7 +630,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G9" t="n">
-        <v>6.85268831253052</v>
+        <v>6.85268783569336</v>
       </c>
       <c r="H9" t="n">
         <v>18024</v>
@@ -659,7 +659,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G10" t="n">
-        <v>6.8959493637085</v>
+        <v>6.89594984054565</v>
       </c>
       <c r="H10" t="n">
         <v>3804</v>
@@ -717,7 +717,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G12" t="n">
-        <v>6.57581090927124</v>
+        <v>6.5758113861084</v>
       </c>
       <c r="H12" t="n">
         <v>11924</v>
@@ -746,7 +746,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G13" t="n">
-        <v>6.66233539581299</v>
+        <v>6.66233587265015</v>
       </c>
       <c r="H13" t="n">
         <v>30396</v>
@@ -775,7 +775,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G14" t="n">
-        <v>6.25134754180908</v>
+        <v>6.25134611129761</v>
       </c>
       <c r="H14" t="n">
         <v>20146</v>
@@ -804,7 +804,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G15" t="n">
-        <v>6.31623983383179</v>
+        <v>6.31624126434326</v>
       </c>
       <c r="H15" t="n">
         <v>28633</v>
@@ -833,7 +833,7 @@
         <v>7.375</v>
       </c>
       <c r="G16" t="n">
-        <v>6.38113212585449</v>
+        <v>6.38113260269165</v>
       </c>
       <c r="H16" t="n">
         <v>13620</v>
@@ -891,7 +891,7 @@
         <v>7.39499998092651</v>
       </c>
       <c r="G18" t="n">
-        <v>6.3984375</v>
+        <v>6.39843797683716</v>
       </c>
       <c r="H18" t="n">
         <v>3118</v>
@@ -978,7 +978,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G21" t="n">
-        <v>6.31623983383179</v>
+        <v>6.31624126434326</v>
       </c>
       <c r="H21" t="n">
         <v>15596</v>
@@ -1007,7 +1007,7 @@
         <v>7.40999984741211</v>
       </c>
       <c r="G22" t="n">
-        <v>6.41141605377197</v>
+        <v>6.41141510009766</v>
       </c>
       <c r="H22" t="n">
         <v>4042</v>
@@ -1036,7 +1036,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G23" t="n">
-        <v>6.4979395866394</v>
+        <v>6.49794101715088</v>
       </c>
       <c r="H23" t="n">
         <v>8653</v>
@@ -1094,7 +1094,7 @@
         <v>7.46999979019165</v>
       </c>
       <c r="G25" t="n">
-        <v>6.46332979202271</v>
+        <v>6.46333074569702</v>
       </c>
       <c r="H25" t="n">
         <v>5091</v>
@@ -1152,7 +1152,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G27" t="n">
-        <v>6.57581090927124</v>
+        <v>6.5758113861084</v>
       </c>
       <c r="H27" t="n">
         <v>19913</v>
@@ -1181,7 +1181,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G28" t="n">
-        <v>6.57581090927124</v>
+        <v>6.5758113861084</v>
       </c>
       <c r="H28" t="n">
         <v>19874</v>
@@ -1210,7 +1210,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G29" t="n">
-        <v>6.57581090927124</v>
+        <v>6.5758113861084</v>
       </c>
       <c r="H29" t="n">
         <v>15750</v>
@@ -1239,7 +1239,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G30" t="n">
-        <v>6.31623983383179</v>
+        <v>6.31624126434326</v>
       </c>
       <c r="H30" t="n">
         <v>11382</v>
@@ -1268,7 +1268,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G31" t="n">
-        <v>6.60176801681519</v>
+        <v>6.6017689704895</v>
       </c>
       <c r="H31" t="n">
         <v>15575</v>
@@ -1355,7 +1355,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G34" t="n">
-        <v>6.67098712921143</v>
+        <v>6.67098760604858</v>
       </c>
       <c r="H34" t="n">
         <v>7965</v>
@@ -1413,7 +1413,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G36" t="n">
-        <v>6.74020671844482</v>
+        <v>6.74020624160767</v>
       </c>
       <c r="H36" t="n">
         <v>368</v>
@@ -1471,7 +1471,7 @@
         <v>8.03999996185303</v>
       </c>
       <c r="G38" t="n">
-        <v>6.95651626586914</v>
+        <v>6.95651531219482</v>
       </c>
       <c r="H38" t="n">
         <v>19565</v>
@@ -1500,7 +1500,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H39" t="n">
         <v>690</v>
@@ -1529,7 +1529,7 @@
         <v>8.11999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>7.02573585510254</v>
+        <v>7.02573537826538</v>
       </c>
       <c r="H40" t="n">
         <v>7574</v>
@@ -1587,7 +1587,7 @@
         <v>7.98999977111816</v>
       </c>
       <c r="G42" t="n">
-        <v>6.91325426101685</v>
+        <v>6.913254737854</v>
       </c>
       <c r="H42" t="n">
         <v>3640</v>
@@ -1616,7 +1616,7 @@
         <v>8.13000011444092</v>
       </c>
       <c r="G43" t="n">
-        <v>7.03438854217529</v>
+        <v>7.03438806533813</v>
       </c>
       <c r="H43" t="n">
         <v>13506</v>
@@ -1645,7 +1645,7 @@
         <v>7.72499990463257</v>
       </c>
       <c r="G44" t="n">
-        <v>6.6839656829834</v>
+        <v>6.68396663665771</v>
       </c>
       <c r="H44" t="n">
         <v>13599</v>
@@ -1674,7 +1674,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G45" t="n">
-        <v>6.7791428565979</v>
+        <v>6.77914237976074</v>
       </c>
       <c r="H45" t="n">
         <v>2568</v>
@@ -1703,7 +1703,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G46" t="n">
-        <v>6.62772560119629</v>
+        <v>6.62772512435913</v>
       </c>
       <c r="H46" t="n">
         <v>11062</v>
@@ -1732,7 +1732,7 @@
         <v>7.53999996185303</v>
       </c>
       <c r="G47" t="n">
-        <v>6.52389669418335</v>
+        <v>6.52389717102051</v>
       </c>
       <c r="H47" t="n">
         <v>3435</v>
@@ -1761,7 +1761,7 @@
         <v>7.60500001907349</v>
       </c>
       <c r="G48" t="n">
-        <v>6.58013772964478</v>
+        <v>6.58013677597046</v>
       </c>
       <c r="H48" t="n">
         <v>2818</v>
@@ -1790,7 +1790,7 @@
         <v>7.65999984741211</v>
       </c>
       <c r="G49" t="n">
-        <v>6.62772560119629</v>
+        <v>6.62772512435913</v>
       </c>
       <c r="H49" t="n">
         <v>5221</v>
@@ -1848,7 +1848,7 @@
         <v>7.63000011444092</v>
       </c>
       <c r="G51" t="n">
-        <v>6.60176801681519</v>
+        <v>6.6017689704895</v>
       </c>
       <c r="H51" t="n">
         <v>4539</v>
@@ -1935,7 +1935,7 @@
         <v>7.77500009536743</v>
       </c>
       <c r="G54" t="n">
-        <v>6.72722911834717</v>
+        <v>6.72722816467285</v>
       </c>
       <c r="H54" t="n">
         <v>338</v>
@@ -1964,7 +1964,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G55" t="n">
-        <v>6.76183843612671</v>
+        <v>6.76183748245239</v>
       </c>
       <c r="H55" t="n">
         <v>2198</v>
@@ -2022,7 +2022,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G57" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H57" t="n">
         <v>1915</v>
@@ -2080,7 +2080,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G59" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H59" t="n">
         <v>1556</v>
@@ -2109,7 +2109,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G60" t="n">
-        <v>6.74453258514404</v>
+        <v>6.7445330619812</v>
       </c>
       <c r="H60" t="n">
         <v>157</v>
@@ -2138,7 +2138,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G61" t="n">
-        <v>6.66233539581299</v>
+        <v>6.66233587265015</v>
       </c>
       <c r="H61" t="n">
         <v>17259</v>
@@ -2167,7 +2167,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G62" t="n">
-        <v>6.64503049850464</v>
+        <v>6.6450309753418</v>
       </c>
       <c r="H62" t="n">
         <v>11309</v>
@@ -2196,7 +2196,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G63" t="n">
-        <v>6.76616382598877</v>
+        <v>6.76616334915161</v>
       </c>
       <c r="H63" t="n">
         <v>4360</v>
@@ -2225,7 +2225,7 @@
         <v>7.88500022888184</v>
       </c>
       <c r="G64" t="n">
-        <v>6.82240438461304</v>
+        <v>6.82240533828735</v>
       </c>
       <c r="H64" t="n">
         <v>6114</v>
@@ -2312,7 +2312,7 @@
         <v>7.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>6.57581090927124</v>
+        <v>6.5758113861084</v>
       </c>
       <c r="H67" t="n">
         <v>3113</v>
@@ -2341,7 +2341,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G68" t="n">
-        <v>6.4979395866394</v>
+        <v>6.49794101715088</v>
       </c>
       <c r="H68" t="n">
         <v>2771</v>
@@ -2370,7 +2370,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G69" t="n">
-        <v>6.50226640701294</v>
+        <v>6.50226593017578</v>
       </c>
       <c r="H69" t="n">
         <v>4219</v>
@@ -2399,7 +2399,7 @@
         <v>7.41499996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>6.41574144363403</v>
+        <v>6.41574192047119</v>
       </c>
       <c r="H70" t="n">
         <v>459</v>
@@ -2457,7 +2457,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G72" t="n">
-        <v>6.67963933944702</v>
+        <v>6.67964029312134</v>
       </c>
       <c r="H72" t="n">
         <v>30204</v>
@@ -2515,7 +2515,7 @@
         <v>7.96999979019165</v>
       </c>
       <c r="G74" t="n">
-        <v>6.8959493637085</v>
+        <v>6.89594984054565</v>
       </c>
       <c r="H74" t="n">
         <v>16592</v>
@@ -2544,7 +2544,7 @@
         <v>7.92000007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>6.85268831253052</v>
+        <v>6.85268783569336</v>
       </c>
       <c r="H75" t="n">
         <v>405</v>
@@ -2573,7 +2573,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G76" t="n">
-        <v>6.76616382598877</v>
+        <v>6.76616334915161</v>
       </c>
       <c r="H76" t="n">
         <v>302</v>
@@ -2602,7 +2602,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G77" t="n">
-        <v>6.80077362060547</v>
+        <v>6.80077409744263</v>
       </c>
       <c r="H77" t="n">
         <v>12572</v>
@@ -2631,7 +2631,7 @@
         <v>7.85500001907349</v>
       </c>
       <c r="G78" t="n">
-        <v>6.79644775390625</v>
+        <v>6.79644680023193</v>
       </c>
       <c r="H78" t="n">
         <v>8992</v>
@@ -2660,7 +2660,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G79" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H79" t="n">
         <v>850</v>
@@ -2689,7 +2689,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G80" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H80" t="n">
         <v>329</v>
@@ -2718,7 +2718,7 @@
         <v>7.86499977111816</v>
       </c>
       <c r="G81" t="n">
-        <v>6.80509853363037</v>
+        <v>6.805100440979</v>
       </c>
       <c r="H81" t="n">
         <v>6352</v>
@@ -2747,7 +2747,7 @@
         <v>7.73999977111816</v>
       </c>
       <c r="G82" t="n">
-        <v>6.69694471359253</v>
+        <v>6.69694423675537</v>
       </c>
       <c r="H82" t="n">
         <v>10136</v>
@@ -2776,7 +2776,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G83" t="n">
-        <v>6.67963933944702</v>
+        <v>6.67964029312134</v>
       </c>
       <c r="H83" t="n">
         <v>22405</v>
@@ -2805,7 +2805,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G84" t="n">
-        <v>6.66233539581299</v>
+        <v>6.66233587265015</v>
       </c>
       <c r="H84" t="n">
         <v>18991</v>
@@ -2834,7 +2834,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G85" t="n">
-        <v>6.46765661239624</v>
+        <v>6.4676570892334</v>
       </c>
       <c r="H85" t="n">
         <v>12826</v>
@@ -2892,7 +2892,7 @@
         <v>7.5149998664856</v>
       </c>
       <c r="G87" t="n">
-        <v>6.50226640701294</v>
+        <v>6.50226593017578</v>
       </c>
       <c r="H87" t="n">
         <v>4249</v>
@@ -2921,7 +2921,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G88" t="n">
-        <v>6.51524496078491</v>
+        <v>6.51524543762207</v>
       </c>
       <c r="H88" t="n">
         <v>3423</v>
@@ -2950,7 +2950,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G89" t="n">
-        <v>6.51524496078491</v>
+        <v>6.51524543762207</v>
       </c>
       <c r="H89" t="n">
         <v>4113</v>
@@ -2979,7 +2979,7 @@
         <v>7.53000020980835</v>
       </c>
       <c r="G90" t="n">
-        <v>6.51524496078491</v>
+        <v>6.51524543762207</v>
       </c>
       <c r="H90" t="n">
         <v>1713</v>
@@ -3008,7 +3008,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G91" t="n">
-        <v>6.46765661239624</v>
+        <v>6.4676570892334</v>
       </c>
       <c r="H91" t="n">
         <v>4973</v>
@@ -3037,7 +3037,7 @@
         <v>7.65000009536743</v>
       </c>
       <c r="G92" t="n">
-        <v>6.61907339096069</v>
+        <v>6.61907291412354</v>
       </c>
       <c r="H92" t="n">
         <v>9703</v>
@@ -3066,7 +3066,7 @@
         <v>7.7649998664856</v>
       </c>
       <c r="G93" t="n">
-        <v>6.7185754776001</v>
+        <v>6.71857595443726</v>
       </c>
       <c r="H93" t="n">
         <v>12759</v>
@@ -3095,7 +3095,7 @@
         <v>7.71999979019165</v>
       </c>
       <c r="G94" t="n">
-        <v>6.67963933944702</v>
+        <v>6.67964029312134</v>
       </c>
       <c r="H94" t="n">
         <v>634</v>
@@ -3124,7 +3124,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G95" t="n">
-        <v>6.80942583084106</v>
+        <v>6.80942535400391</v>
       </c>
       <c r="H95" t="n">
         <v>1688</v>
@@ -3153,7 +3153,7 @@
         <v>7.86999988555908</v>
       </c>
       <c r="G96" t="n">
-        <v>6.80942583084106</v>
+        <v>6.80942535400391</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G97" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H97" t="n">
         <v>2484</v>
@@ -3240,7 +3240,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G99" t="n">
-        <v>6.79212093353271</v>
+        <v>6.79212045669556</v>
       </c>
       <c r="H99" t="n">
         <v>4098</v>
@@ -3298,7 +3298,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H101" t="n">
         <v>3327</v>
@@ -3327,7 +3327,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G102" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H102" t="n">
         <v>886</v>
@@ -3385,7 +3385,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G104" t="n">
-        <v>6.84923458099365</v>
+        <v>6.84923505783081</v>
       </c>
       <c r="H104" t="n">
         <v>47568</v>
@@ -3414,7 +3414,7 @@
         <v>8.28999996185303</v>
       </c>
       <c r="G105" t="n">
-        <v>7.28417634963989</v>
+        <v>7.28417682647705</v>
       </c>
       <c r="H105" t="n">
         <v>18330</v>
@@ -3443,7 +3443,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G106" t="n">
-        <v>7.16995048522949</v>
+        <v>7.16995000839233</v>
       </c>
       <c r="H106" t="n">
         <v>8878</v>
@@ -3472,7 +3472,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>7.36325740814209</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H107" t="n">
         <v>10304</v>
@@ -3501,7 +3501,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G108" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H108" t="n">
         <v>2205</v>
@@ -3588,7 +3588,7 @@
         <v>8.4350004196167</v>
       </c>
       <c r="G111" t="n">
-        <v>7.41158390045166</v>
+        <v>7.41158437728882</v>
       </c>
       <c r="H111" t="n">
         <v>14073</v>
@@ -3617,7 +3617,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G112" t="n">
-        <v>7.34568357467651</v>
+        <v>7.34568309783936</v>
       </c>
       <c r="H112" t="n">
         <v>1577</v>
@@ -3646,7 +3646,7 @@
         <v>8.40999984741211</v>
       </c>
       <c r="G113" t="n">
-        <v>7.3896164894104</v>
+        <v>7.38961744308472</v>
       </c>
       <c r="H113" t="n">
         <v>1885</v>
@@ -3791,7 +3791,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G118" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H118" t="n">
         <v>16702</v>
@@ -3820,7 +3820,7 @@
         <v>8.14000034332275</v>
       </c>
       <c r="G119" t="n">
-        <v>7.15237665176392</v>
+        <v>7.1523756980896</v>
       </c>
       <c r="H119" t="n">
         <v>48342</v>
@@ -3907,7 +3907,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G122" t="n">
-        <v>7.51263093948364</v>
+        <v>7.51263046264648</v>
       </c>
       <c r="H122" t="n">
         <v>7693</v>
@@ -3936,7 +3936,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G123" t="n">
-        <v>7.63564348220825</v>
+        <v>7.63564443588257</v>
       </c>
       <c r="H123" t="n">
         <v>27887</v>
@@ -3965,7 +3965,7 @@
         <v>8.6899995803833</v>
       </c>
       <c r="G124" t="n">
-        <v>7.63564348220825</v>
+        <v>7.63564443588257</v>
       </c>
       <c r="H124" t="n">
         <v>10411</v>
@@ -3994,7 +3994,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G125" t="n">
-        <v>7.64443159103394</v>
+        <v>7.64443063735962</v>
       </c>
       <c r="H125" t="n">
         <v>11739</v>
@@ -4023,7 +4023,7 @@
         <v>8.71000003814697</v>
       </c>
       <c r="G126" t="n">
-        <v>7.65321731567383</v>
+        <v>7.65321683883667</v>
       </c>
       <c r="H126" t="n">
         <v>6833</v>
@@ -4052,7 +4052,7 @@
         <v>8.64999961853027</v>
       </c>
       <c r="G127" t="n">
-        <v>7.60049676895142</v>
+        <v>7.60049772262573</v>
       </c>
       <c r="H127" t="n">
         <v>20863</v>
@@ -4110,7 +4110,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G129" t="n">
-        <v>7.55656433105469</v>
+        <v>7.55656480789185</v>
       </c>
       <c r="H129" t="n">
         <v>54591</v>
@@ -4139,7 +4139,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G130" t="n">
-        <v>7.24024295806885</v>
+        <v>7.24024343490601</v>
       </c>
       <c r="H130" t="n">
         <v>12512</v>
@@ -4168,7 +4168,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G131" t="n">
-        <v>6.94149494171143</v>
+        <v>6.94149541854858</v>
       </c>
       <c r="H131" t="n">
         <v>10710</v>
@@ -4226,7 +4226,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G133" t="n">
-        <v>7.49505805969238</v>
+        <v>7.49505758285522</v>
       </c>
       <c r="H133" t="n">
         <v>14238</v>
@@ -4284,7 +4284,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G135" t="n">
-        <v>7.45112323760986</v>
+        <v>7.45112371444702</v>
       </c>
       <c r="H135" t="n">
         <v>32534</v>
@@ -4313,7 +4313,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G136" t="n">
-        <v>7.3676495552063</v>
+        <v>7.36765003204346</v>
       </c>
       <c r="H136" t="n">
         <v>8303</v>
@@ -4400,7 +4400,7 @@
         <v>8.5</v>
       </c>
       <c r="G139" t="n">
-        <v>7.4686975479126</v>
+        <v>7.46869611740112</v>
       </c>
       <c r="H139" t="n">
         <v>5308</v>
@@ -4429,7 +4429,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G140" t="n">
-        <v>7.48627138137817</v>
+        <v>7.48627185821533</v>
       </c>
       <c r="H140" t="n">
         <v>3111</v>
@@ -4487,7 +4487,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G142" t="n">
-        <v>7.16116237640381</v>
+        <v>7.16116142272949</v>
       </c>
       <c r="H142" t="n">
         <v>22169</v>
@@ -4516,7 +4516,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G143" t="n">
-        <v>7.16995048522949</v>
+        <v>7.16995000839233</v>
       </c>
       <c r="H143" t="n">
         <v>18680</v>
@@ -4545,7 +4545,7 @@
         <v>7.89499998092651</v>
       </c>
       <c r="G144" t="n">
-        <v>6.9371018409729</v>
+        <v>6.93710231781006</v>
       </c>
       <c r="H144" t="n">
         <v>13893</v>
@@ -4661,7 +4661,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G148" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H148" t="n">
         <v>3800</v>
@@ -4690,7 +4690,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G149" t="n">
-        <v>6.95467472076416</v>
+        <v>6.95467519760132</v>
       </c>
       <c r="H149" t="n">
         <v>16736</v>
@@ -4719,7 +4719,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G150" t="n">
-        <v>6.95467472076416</v>
+        <v>6.95467519760132</v>
       </c>
       <c r="H150" t="n">
         <v>3409</v>
@@ -4748,7 +4748,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G151" t="n">
-        <v>7.16116237640381</v>
+        <v>7.16116142272949</v>
       </c>
       <c r="H151" t="n">
         <v>8656</v>
@@ -4777,7 +4777,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G152" t="n">
-        <v>7.16116237640381</v>
+        <v>7.16116142272949</v>
       </c>
       <c r="H152" t="n">
         <v>3978</v>
@@ -4806,7 +4806,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G153" t="n">
-        <v>7.16116237640381</v>
+        <v>7.16116142272949</v>
       </c>
       <c r="H153" t="n">
         <v>5138</v>
@@ -4835,7 +4835,7 @@
         <v>8.21000003814697</v>
       </c>
       <c r="G154" t="n">
-        <v>7.21388292312622</v>
+        <v>7.21388339996338</v>
       </c>
       <c r="H154" t="n">
         <v>4722</v>
@@ -4893,7 +4893,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G156" t="n">
-        <v>7.28857040405273</v>
+        <v>7.28856992721558</v>
       </c>
       <c r="H156" t="n">
         <v>38786</v>
@@ -4951,7 +4951,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G158" t="n">
-        <v>7.40718984603882</v>
+        <v>7.40718936920166</v>
       </c>
       <c r="H158" t="n">
         <v>4438</v>
@@ -4980,7 +4980,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G159" t="n">
-        <v>7.36325740814209</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H159" t="n">
         <v>8082</v>
@@ -5009,7 +5009,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G160" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H160" t="n">
         <v>6187</v>
@@ -5038,7 +5038,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G161" t="n">
-        <v>7.36325740814209</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H161" t="n">
         <v>1145</v>
@@ -5067,7 +5067,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G162" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H162" t="n">
         <v>4942</v>
@@ -5096,7 +5096,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G163" t="n">
-        <v>7.40718984603882</v>
+        <v>7.40718936920166</v>
       </c>
       <c r="H163" t="n">
         <v>11925</v>
@@ -5125,7 +5125,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G164" t="n">
-        <v>7.45991039276123</v>
+        <v>7.45990991592407</v>
       </c>
       <c r="H164" t="n">
         <v>1298</v>
@@ -5154,7 +5154,7 @@
         <v>8.48999977111816</v>
       </c>
       <c r="G165" t="n">
-        <v>7.45991039276123</v>
+        <v>7.45990991592407</v>
       </c>
       <c r="H165" t="n">
         <v>2126</v>
@@ -5183,7 +5183,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G166" t="n">
-        <v>7.3368968963623</v>
+        <v>7.33689641952515</v>
       </c>
       <c r="H166" t="n">
         <v>9454</v>
@@ -5212,7 +5212,7 @@
         <v>8.42000007629395</v>
       </c>
       <c r="G167" t="n">
-        <v>7.39840364456177</v>
+        <v>7.39840459823608</v>
       </c>
       <c r="H167" t="n">
         <v>2349</v>
@@ -5241,7 +5241,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G168" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H168" t="n">
         <v>8638</v>
@@ -5270,7 +5270,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G169" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H169" t="n">
         <v>1652</v>
@@ -5328,7 +5328,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G171" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H171" t="n">
         <v>6170</v>
@@ -5386,7 +5386,7 @@
         <v>8.27999973297119</v>
       </c>
       <c r="G173" t="n">
-        <v>7.27539014816284</v>
+        <v>7.27539110183716</v>
       </c>
       <c r="H173" t="n">
         <v>1597</v>
@@ -5415,7 +5415,7 @@
         <v>8.35499954223633</v>
       </c>
       <c r="G174" t="n">
-        <v>7.3412880897522</v>
+        <v>7.34128856658936</v>
       </c>
       <c r="H174" t="n">
         <v>1536</v>
@@ -5473,7 +5473,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G176" t="n">
-        <v>7.22266912460327</v>
+        <v>7.22267007827759</v>
       </c>
       <c r="H176" t="n">
         <v>11254</v>
@@ -5502,7 +5502,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G177" t="n">
-        <v>7.1963095664978</v>
+        <v>7.19630908966064</v>
       </c>
       <c r="H177" t="n">
         <v>2108</v>
@@ -5531,7 +5531,7 @@
         <v>8.09000015258789</v>
       </c>
       <c r="G178" t="n">
-        <v>7.10844326019287</v>
+        <v>7.10844230651855</v>
       </c>
       <c r="H178" t="n">
         <v>6045</v>
@@ -5589,7 +5589,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G180" t="n">
-        <v>6.82726764678955</v>
+        <v>6.82726716995239</v>
       </c>
       <c r="H180" t="n">
         <v>23452</v>
@@ -5676,7 +5676,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G183" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H183" t="n">
         <v>14070</v>
@@ -5705,7 +5705,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G184" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605527877808</v>
       </c>
       <c r="H184" t="n">
         <v>7690</v>
@@ -5763,7 +5763,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G186" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H186" t="n">
         <v>39341</v>
@@ -5792,7 +5792,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G187" t="n">
-        <v>6.90634822845459</v>
+        <v>6.90634870529175</v>
       </c>
       <c r="H187" t="n">
         <v>9815</v>
@@ -5821,7 +5821,7 @@
         <v>7.74499988555908</v>
       </c>
       <c r="G188" t="n">
-        <v>6.80530118942261</v>
+        <v>6.80530071258545</v>
       </c>
       <c r="H188" t="n">
         <v>3149</v>
@@ -5908,7 +5908,7 @@
         <v>7.71000003814697</v>
       </c>
       <c r="G191" t="n">
-        <v>6.77454710006714</v>
+        <v>6.7745475769043</v>
       </c>
       <c r="H191" t="n">
         <v>1443</v>
@@ -5937,7 +5937,7 @@
         <v>7.55000019073486</v>
       </c>
       <c r="G192" t="n">
-        <v>6.63396072387695</v>
+        <v>6.63396024703979</v>
       </c>
       <c r="H192" t="n">
         <v>2140</v>
@@ -5995,7 +5995,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G194" t="n">
-        <v>6.85362815856934</v>
+        <v>6.85362863540649</v>
       </c>
       <c r="H194" t="n">
         <v>3730</v>
@@ -6024,7 +6024,7 @@
         <v>7.90000009536743</v>
       </c>
       <c r="G195" t="n">
-        <v>6.94149494171143</v>
+        <v>6.94149541854858</v>
       </c>
       <c r="H195" t="n">
         <v>4152</v>
@@ -6053,7 +6053,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G196" t="n">
-        <v>6.96346092224121</v>
+        <v>6.96346187591553</v>
       </c>
       <c r="H196" t="n">
         <v>19913</v>
@@ -6082,7 +6082,7 @@
         <v>7.91499996185303</v>
       </c>
       <c r="G197" t="n">
-        <v>6.95467472076416</v>
+        <v>6.95467519760132</v>
       </c>
       <c r="H197" t="n">
         <v>4610</v>
@@ -6111,7 +6111,7 @@
         <v>7.78999996185303</v>
       </c>
       <c r="G198" t="n">
-        <v>6.84484100341797</v>
+        <v>6.84484052658081</v>
       </c>
       <c r="H198" t="n">
         <v>3868</v>
@@ -6198,7 +6198,7 @@
         <v>7.76000022888184</v>
       </c>
       <c r="G201" t="n">
-        <v>6.81848096847534</v>
+        <v>6.8184814453125</v>
       </c>
       <c r="H201" t="n">
         <v>8692</v>
@@ -6227,7 +6227,7 @@
         <v>7.75</v>
       </c>
       <c r="G202" t="n">
-        <v>6.80969381332397</v>
+        <v>6.80969429016113</v>
       </c>
       <c r="H202" t="n">
         <v>896</v>
@@ -6256,7 +6256,7 @@
         <v>7.8600001335144</v>
       </c>
       <c r="G203" t="n">
-        <v>6.90634822845459</v>
+        <v>6.90634870529175</v>
       </c>
       <c r="H203" t="n">
         <v>4470</v>
@@ -6285,7 +6285,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G204" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605527877808</v>
       </c>
       <c r="H204" t="n">
         <v>10055</v>
@@ -6314,7 +6314,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G205" t="n">
-        <v>6.87120199203491</v>
+        <v>6.87120246887207</v>
       </c>
       <c r="H205" t="n">
         <v>10123</v>
@@ -6343,7 +6343,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G206" t="n">
-        <v>6.87120199203491</v>
+        <v>6.87120246887207</v>
       </c>
       <c r="H206" t="n">
         <v>20447</v>
@@ -6401,7 +6401,7 @@
         <v>7.79500007629395</v>
       </c>
       <c r="G208" t="n">
-        <v>6.84923458099365</v>
+        <v>6.84923505783081</v>
       </c>
       <c r="H208" t="n">
         <v>6959</v>
@@ -6430,7 +6430,7 @@
         <v>7.78000020980835</v>
       </c>
       <c r="G209" t="n">
-        <v>6.83605480194092</v>
+        <v>6.83605527877808</v>
       </c>
       <c r="H209" t="n">
         <v>1774</v>
@@ -6459,7 +6459,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G210" t="n">
-        <v>6.85362815856934</v>
+        <v>6.85362863540649</v>
       </c>
       <c r="H210" t="n">
         <v>3875</v>
@@ -6517,7 +6517,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G212" t="n">
-        <v>6.95028209686279</v>
+        <v>6.95028114318848</v>
       </c>
       <c r="H212" t="n">
         <v>240</v>
@@ -6575,7 +6575,7 @@
         <v>7.81500005722046</v>
       </c>
       <c r="G214" t="n">
-        <v>6.86680936813354</v>
+        <v>6.86680793762207</v>
       </c>
       <c r="H214" t="n">
         <v>2631</v>
@@ -6604,7 +6604,7 @@
         <v>7.83500003814697</v>
       </c>
       <c r="G215" t="n">
-        <v>6.88438177108765</v>
+        <v>6.88438129425049</v>
       </c>
       <c r="H215" t="n">
         <v>288</v>
@@ -6720,7 +6720,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G219" t="n">
-        <v>6.87120199203491</v>
+        <v>6.87120246887207</v>
       </c>
       <c r="H219" t="n">
         <v>9141</v>
@@ -6894,7 +6894,7 @@
         <v>7.65500020980835</v>
       </c>
       <c r="G225" t="n">
-        <v>6.72622203826904</v>
+        <v>6.72622108459473</v>
       </c>
       <c r="H225" t="n">
         <v>353</v>
@@ -6923,7 +6923,7 @@
         <v>7.51000022888184</v>
       </c>
       <c r="G226" t="n">
-        <v>6.59881353378296</v>
+        <v>6.59881401062012</v>
       </c>
       <c r="H226" t="n">
         <v>16592</v>
@@ -6981,7 +6981,7 @@
         <v>7.19500017166138</v>
       </c>
       <c r="G228" t="n">
-        <v>6.32203245162964</v>
+        <v>6.32203340530396</v>
       </c>
       <c r="H228" t="n">
         <v>6999</v>
@@ -7097,7 +7097,7 @@
         <v>7.32000017166138</v>
       </c>
       <c r="G232" t="n">
-        <v>6.43186712265015</v>
+        <v>6.43186616897583</v>
       </c>
       <c r="H232" t="n">
         <v>7017</v>
@@ -7155,7 +7155,7 @@
         <v>7.3899998664856</v>
       </c>
       <c r="G234" t="n">
-        <v>6.49337291717529</v>
+        <v>6.49337339401245</v>
       </c>
       <c r="H234" t="n">
         <v>1679</v>
@@ -7184,7 +7184,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G235" t="n">
-        <v>6.41429328918457</v>
+        <v>6.41429281234741</v>
       </c>
       <c r="H235" t="n">
         <v>7879</v>
@@ -7213,7 +7213,7 @@
         <v>7.30000019073486</v>
       </c>
       <c r="G236" t="n">
-        <v>6.41429328918457</v>
+        <v>6.41429281234741</v>
       </c>
       <c r="H236" t="n">
         <v>4615</v>
@@ -7242,7 +7242,7 @@
         <v>7.05000019073486</v>
       </c>
       <c r="G237" t="n">
-        <v>6.19462585449219</v>
+        <v>6.19462537765503</v>
       </c>
       <c r="H237" t="n">
         <v>52499</v>
@@ -7300,7 +7300,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G239" t="n">
-        <v>6.17705154418945</v>
+        <v>6.17705249786377</v>
       </c>
       <c r="H239" t="n">
         <v>8669</v>
@@ -7358,7 +7358,7 @@
         <v>7.50500011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>6.59441995620728</v>
+        <v>6.59442043304443</v>
       </c>
       <c r="H241" t="n">
         <v>17531</v>
@@ -7445,7 +7445,7 @@
         <v>7.92500019073486</v>
       </c>
       <c r="G244" t="n">
-        <v>6.96346092224121</v>
+        <v>6.96346187591553</v>
       </c>
       <c r="H244" t="n">
         <v>21249</v>
@@ -7474,7 +7474,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G245" t="n">
-        <v>6.98542833328247</v>
+        <v>6.98542785644531</v>
       </c>
       <c r="H245" t="n">
         <v>12507</v>
@@ -7532,7 +7532,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G247" t="n">
-        <v>6.82726764678955</v>
+        <v>6.82726716995239</v>
       </c>
       <c r="H247" t="n">
         <v>4566</v>
@@ -7648,7 +7648,7 @@
         <v>7.57000017166138</v>
       </c>
       <c r="G251" t="n">
-        <v>6.65153455734253</v>
+        <v>6.65153408050537</v>
       </c>
       <c r="H251" t="n">
         <v>9506</v>
@@ -7677,7 +7677,7 @@
         <v>7.57499980926514</v>
       </c>
       <c r="G252" t="n">
-        <v>6.6559271812439</v>
+        <v>6.65592670440674</v>
       </c>
       <c r="H252" t="n">
         <v>2025</v>
@@ -7735,7 +7735,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G254" t="n">
-        <v>6.53291320800781</v>
+        <v>6.53291368484497</v>
       </c>
       <c r="H254" t="n">
         <v>10512</v>
@@ -7764,7 +7764,7 @@
         <v>7.43499994277954</v>
       </c>
       <c r="G255" t="n">
-        <v>6.53291320800781</v>
+        <v>6.53291368484497</v>
       </c>
       <c r="H255" t="n">
         <v>17323</v>
@@ -7851,7 +7851,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G258" t="n">
-        <v>6.89756107330322</v>
+        <v>6.89756155014038</v>
       </c>
       <c r="H258" t="n">
         <v>15659</v>
@@ -7880,7 +7880,7 @@
         <v>8.03499984741211</v>
       </c>
       <c r="G259" t="n">
-        <v>7.06011533737183</v>
+        <v>7.06011581420898</v>
       </c>
       <c r="H259" t="n">
         <v>43150</v>
@@ -7909,7 +7909,7 @@
         <v>8.14999961853027</v>
       </c>
       <c r="G260" t="n">
-        <v>7.16116237640381</v>
+        <v>7.16116142272949</v>
       </c>
       <c r="H260" t="n">
         <v>9680</v>
@@ -7967,7 +7967,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G262" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H262" t="n">
         <v>2360</v>
@@ -8054,7 +8054,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G265" t="n">
-        <v>7.1963095664978</v>
+        <v>7.19630908966064</v>
       </c>
       <c r="H265" t="n">
         <v>7870</v>
@@ -8083,7 +8083,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G266" t="n">
-        <v>7.1963095664978</v>
+        <v>7.19630908966064</v>
       </c>
       <c r="H266" t="n">
         <v>2986</v>
@@ -8112,7 +8112,7 @@
         <v>8.1899995803833</v>
       </c>
       <c r="G267" t="n">
-        <v>7.1963095664978</v>
+        <v>7.19630908966064</v>
       </c>
       <c r="H267" t="n">
         <v>3709</v>
@@ -8257,7 +8257,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G272" t="n">
-        <v>7.07329559326172</v>
+        <v>7.07329607009888</v>
       </c>
       <c r="H272" t="n">
         <v>4062</v>
@@ -8286,7 +8286,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G273" t="n">
-        <v>7.07329559326172</v>
+        <v>7.07329607009888</v>
       </c>
       <c r="H273" t="n">
         <v>4804</v>
@@ -8315,7 +8315,7 @@
         <v>8.125</v>
       </c>
       <c r="G274" t="n">
-        <v>7.13919544219971</v>
+        <v>7.13919591903687</v>
       </c>
       <c r="H274" t="n">
         <v>4849</v>
@@ -8344,7 +8344,7 @@
         <v>8.05000019073486</v>
       </c>
       <c r="G275" t="n">
-        <v>7.07329559326172</v>
+        <v>7.07329607009888</v>
       </c>
       <c r="H275" t="n">
         <v>7892</v>
@@ -8402,7 +8402,7 @@
         <v>8.15999984741211</v>
       </c>
       <c r="G277" t="n">
-        <v>7.16995048522949</v>
+        <v>7.16995000839233</v>
       </c>
       <c r="H277" t="n">
         <v>7983</v>
@@ -8460,7 +8460,7 @@
         <v>8.35000038146973</v>
       </c>
       <c r="G279" t="n">
-        <v>7.3368968963623</v>
+        <v>7.33689641952515</v>
       </c>
       <c r="H279" t="n">
         <v>7090</v>
@@ -8489,7 +8489,7 @@
         <v>8.39999961853027</v>
       </c>
       <c r="G280" t="n">
-        <v>7.38082981109619</v>
+        <v>7.38082933425903</v>
       </c>
       <c r="H280" t="n">
         <v>15652</v>
@@ -8518,7 +8518,7 @@
         <v>8.36999988555908</v>
       </c>
       <c r="G281" t="n">
-        <v>7.35446929931641</v>
+        <v>7.35447025299072</v>
       </c>
       <c r="H281" t="n">
         <v>3123</v>
@@ -8547,7 +8547,7 @@
         <v>8.38500022888184</v>
       </c>
       <c r="G282" t="n">
-        <v>7.3676495552063</v>
+        <v>7.36765003204346</v>
       </c>
       <c r="H282" t="n">
         <v>692</v>
@@ -8576,7 +8576,7 @@
         <v>8.43000030517578</v>
       </c>
       <c r="G283" t="n">
-        <v>7.40718984603882</v>
+        <v>7.40718936920166</v>
       </c>
       <c r="H283" t="n">
         <v>7273</v>
@@ -8605,7 +8605,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G284" t="n">
-        <v>7.42476463317871</v>
+        <v>7.42476320266724</v>
       </c>
       <c r="H284" t="n">
         <v>2943</v>
@@ -8634,7 +8634,7 @@
         <v>8.55000019073486</v>
       </c>
       <c r="G285" t="n">
-        <v>7.51263093948364</v>
+        <v>7.51263046264648</v>
       </c>
       <c r="H285" t="n">
         <v>9255</v>
@@ -8663,7 +8663,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G286" t="n">
-        <v>7.42476463317871</v>
+        <v>7.42476320266724</v>
       </c>
       <c r="H286" t="n">
         <v>4018</v>
@@ -8692,7 +8692,7 @@
         <v>8.52999973297119</v>
       </c>
       <c r="G287" t="n">
-        <v>7.49505805969238</v>
+        <v>7.49505758285522</v>
       </c>
       <c r="H287" t="n">
         <v>8846</v>
@@ -8750,7 +8750,7 @@
         <v>8.06999969482422</v>
       </c>
       <c r="G289" t="n">
-        <v>7.09086894989014</v>
+        <v>7.09086847305298</v>
       </c>
       <c r="H289" t="n">
         <v>16710</v>
@@ -8779,7 +8779,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G290" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H290" t="n">
         <v>31344</v>
@@ -8808,7 +8808,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G291" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H291" t="n">
         <v>14166</v>
@@ -8837,7 +8837,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G292" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H292" t="n">
         <v>12124</v>
@@ -8895,7 +8895,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G294" t="n">
-        <v>7.42476463317871</v>
+        <v>7.42476320266724</v>
       </c>
       <c r="H294" t="n">
         <v>7818</v>
@@ -8924,7 +8924,7 @@
         <v>8.29500007629395</v>
       </c>
       <c r="G295" t="n">
-        <v>7.28857040405273</v>
+        <v>7.28856992721558</v>
       </c>
       <c r="H295" t="n">
         <v>18039</v>
@@ -8953,7 +8953,7 @@
         <v>8.21500015258789</v>
       </c>
       <c r="G296" t="n">
-        <v>7.21827554702759</v>
+        <v>7.21827602386475</v>
       </c>
       <c r="H296" t="n">
         <v>21519</v>
@@ -8982,7 +8982,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G297" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H297" t="n">
         <v>3447</v>
@@ -9011,7 +9011,7 @@
         <v>8.10499954223633</v>
       </c>
       <c r="G298" t="n">
-        <v>7.12162160873413</v>
+        <v>7.12162208557129</v>
       </c>
       <c r="H298" t="n">
         <v>587</v>
@@ -9098,7 +9098,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G301" t="n">
-        <v>6.99421501159668</v>
+        <v>6.994215965271</v>
       </c>
       <c r="H301" t="n">
         <v>29954</v>
@@ -9127,7 +9127,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G302" t="n">
-        <v>6.99421501159668</v>
+        <v>6.994215965271</v>
       </c>
       <c r="H302" t="n">
         <v>10238</v>
@@ -9156,7 +9156,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G303" t="n">
-        <v>7.11722946166992</v>
+        <v>7.11722993850708</v>
       </c>
       <c r="H303" t="n">
         <v>7511</v>
@@ -9185,7 +9185,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G304" t="n">
-        <v>7.17873620986938</v>
+        <v>7.17873668670654</v>
       </c>
       <c r="H304" t="n">
         <v>4105</v>
@@ -9214,7 +9214,7 @@
         <v>8.17000007629395</v>
       </c>
       <c r="G305" t="n">
-        <v>7.17873620986938</v>
+        <v>7.17873668670654</v>
       </c>
       <c r="H305" t="n">
         <v>13454</v>
@@ -9388,7 +9388,7 @@
         <v>8.39000034332275</v>
       </c>
       <c r="G311" t="n">
-        <v>7.3720440864563</v>
+        <v>7.37204313278198</v>
       </c>
       <c r="H311" t="n">
         <v>29965</v>
@@ -9417,7 +9417,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G312" t="n">
-        <v>7.36325740814209</v>
+        <v>7.36325645446777</v>
       </c>
       <c r="H312" t="n">
         <v>22522</v>
@@ -9446,7 +9446,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G313" t="n">
-        <v>7.42476463317871</v>
+        <v>7.42476320266724</v>
       </c>
       <c r="H313" t="n">
         <v>20571</v>
@@ -9475,7 +9475,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G314" t="n">
-        <v>7.45112323760986</v>
+        <v>7.45112371444702</v>
       </c>
       <c r="H314" t="n">
         <v>31376</v>
@@ -9504,7 +9504,7 @@
         <v>8.85000038146973</v>
       </c>
       <c r="G315" t="n">
-        <v>7.7762336730957</v>
+        <v>7.77623224258423</v>
       </c>
       <c r="H315" t="n">
         <v>29110</v>
@@ -9533,7 +9533,7 @@
         <v>8.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>7.7674446105957</v>
+        <v>7.76744651794434</v>
       </c>
       <c r="H316" t="n">
         <v>17411</v>
@@ -9649,7 +9649,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G320" t="n">
-        <v>8.96243762969971</v>
+        <v>8.96243572235107</v>
       </c>
       <c r="H320" t="n">
         <v>105159</v>
@@ -9678,7 +9678,7 @@
         <v>9.63500022888184</v>
       </c>
       <c r="G321" t="n">
-        <v>8.46598815917969</v>
+        <v>8.465989112854</v>
       </c>
       <c r="H321" t="n">
         <v>76746</v>
@@ -9707,7 +9707,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G322" t="n">
-        <v>8.43523406982422</v>
+        <v>8.43523502349854</v>
       </c>
       <c r="H322" t="n">
         <v>38737</v>
@@ -9736,7 +9736,7 @@
         <v>9.32999992370605</v>
       </c>
       <c r="G323" t="n">
-        <v>8.19799423217773</v>
+        <v>8.1979923248291</v>
       </c>
       <c r="H323" t="n">
         <v>17848</v>
@@ -9765,7 +9765,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G324" t="n">
-        <v>8.85699653625488</v>
+        <v>8.8569974899292</v>
       </c>
       <c r="H324" t="n">
         <v>44628</v>
@@ -9794,7 +9794,7 @@
         <v>9.69999980926514</v>
       </c>
       <c r="G325" t="n">
-        <v>8.52310276031494</v>
+        <v>8.52310085296631</v>
       </c>
       <c r="H325" t="n">
         <v>52944</v>
@@ -9823,7 +9823,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G326" t="n">
-        <v>8.90971755981445</v>
+        <v>8.90971660614014</v>
       </c>
       <c r="H326" t="n">
         <v>66582</v>
@@ -9852,7 +9852,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G327" t="n">
-        <v>8.69883632659912</v>
+        <v>8.6988353729248</v>
       </c>
       <c r="H327" t="n">
         <v>32280</v>
@@ -9881,7 +9881,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G328" t="n">
-        <v>8.80427742004395</v>
+        <v>8.80427646636963</v>
       </c>
       <c r="H328" t="n">
         <v>150406</v>
@@ -9910,7 +9910,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G329" t="n">
-        <v>9.48963737487793</v>
+        <v>9.48963928222656</v>
       </c>
       <c r="H329" t="n">
         <v>89182</v>
@@ -9939,7 +9939,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G330" t="n">
-        <v>9.18210411071777</v>
+        <v>9.18210506439209</v>
       </c>
       <c r="H330" t="n">
         <v>36798</v>
@@ -9968,7 +9968,7 @@
         <v>10.1899995803833</v>
       </c>
       <c r="G331" t="n">
-        <v>8.95364952087402</v>
+        <v>8.95364856719971</v>
       </c>
       <c r="H331" t="n">
         <v>17183</v>
@@ -9997,7 +9997,7 @@
         <v>10</v>
       </c>
       <c r="G332" t="n">
-        <v>8.78670310974121</v>
+        <v>8.78670215606689</v>
       </c>
       <c r="H332" t="n">
         <v>34355</v>
@@ -10055,7 +10055,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G334" t="n">
-        <v>8.69883632659912</v>
+        <v>8.6988353729248</v>
       </c>
       <c r="H334" t="n">
         <v>20723</v>
@@ -10142,7 +10142,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G337" t="n">
-        <v>8.8306360244751</v>
+        <v>8.83063411712646</v>
       </c>
       <c r="H337" t="n">
         <v>12422</v>
@@ -10171,7 +10171,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G338" t="n">
-        <v>8.74277019500732</v>
+        <v>8.74276828765869</v>
       </c>
       <c r="H338" t="n">
         <v>19588</v>
@@ -10200,7 +10200,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G339" t="n">
-        <v>8.74277019500732</v>
+        <v>8.74276828765869</v>
       </c>
       <c r="H339" t="n">
         <v>52366</v>
@@ -10229,7 +10229,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G340" t="n">
-        <v>8.69883632659912</v>
+        <v>8.6988353729248</v>
       </c>
       <c r="H340" t="n">
         <v>23777</v>
@@ -10316,7 +10316,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G343" t="n">
-        <v>8.69883632659912</v>
+        <v>8.6988353729248</v>
       </c>
       <c r="H343" t="n">
         <v>12882</v>
@@ -10374,7 +10374,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G345" t="n">
-        <v>8.71640872955322</v>
+        <v>8.71640968322754</v>
       </c>
       <c r="H345" t="n">
         <v>27443</v>
@@ -10403,7 +10403,7 @@
         <v>9.94999980926514</v>
       </c>
       <c r="G346" t="n">
-        <v>8.74277019500732</v>
+        <v>8.74276828765869</v>
       </c>
       <c r="H346" t="n">
         <v>38460</v>
@@ -10432,7 +10432,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G347" t="n">
-        <v>8.6109676361084</v>
+        <v>8.61096954345703</v>
       </c>
       <c r="H347" t="n">
         <v>25037</v>
@@ -10461,7 +10461,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G348" t="n">
-        <v>8.69883632659912</v>
+        <v>8.6988353729248</v>
       </c>
       <c r="H348" t="n">
         <v>32004</v>
@@ -10490,7 +10490,7 @@
         <v>9.89000034332275</v>
       </c>
       <c r="G349" t="n">
-        <v>8.69004917144775</v>
+        <v>8.69004821777344</v>
       </c>
       <c r="H349" t="n">
         <v>16975</v>
@@ -10548,7 +10548,7 @@
         <v>10.2799997329712</v>
       </c>
       <c r="G351" t="n">
-        <v>9.03272914886475</v>
+        <v>9.03273010253906</v>
       </c>
       <c r="H351" t="n">
         <v>40243</v>
@@ -10577,7 +10577,7 @@
         <v>9.96500015258789</v>
       </c>
       <c r="G352" t="n">
-        <v>8.75595092773438</v>
+        <v>8.75594997406006</v>
       </c>
       <c r="H352" t="n">
         <v>14372</v>
@@ -10606,7 +10606,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G353" t="n">
-        <v>8.87457180023193</v>
+        <v>8.87457084655762</v>
       </c>
       <c r="H353" t="n">
         <v>7452</v>
@@ -10635,7 +10635,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G354" t="n">
-        <v>9.13816928863525</v>
+        <v>9.13817119598389</v>
       </c>
       <c r="H354" t="n">
         <v>25592</v>
@@ -10664,7 +10664,7 @@
         <v>10.5</v>
       </c>
       <c r="G355" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H355" t="n">
         <v>13733</v>
@@ -10722,7 +10722,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H357" t="n">
         <v>14724</v>
@@ -10751,7 +10751,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G358" t="n">
-        <v>9.25407028198242</v>
+        <v>9.25407123565674</v>
       </c>
       <c r="H358" t="n">
         <v>22212</v>
@@ -10780,7 +10780,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>9.3164758682251</v>
+        <v>9.31647682189941</v>
       </c>
       <c r="H359" t="n">
         <v>19465</v>
@@ -10867,7 +10867,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G362" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H362" t="n">
         <v>9456</v>
@@ -10896,7 +10896,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G363" t="n">
-        <v>9.48586845397949</v>
+        <v>9.48586750030518</v>
       </c>
       <c r="H363" t="n">
         <v>14772</v>
@@ -10925,7 +10925,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G364" t="n">
-        <v>9.60176658630371</v>
+        <v>9.60176467895508</v>
       </c>
       <c r="H364" t="n">
         <v>7605</v>
@@ -10954,7 +10954,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G365" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H365" t="n">
         <v>19352</v>
@@ -10983,7 +10983,7 @@
         <v>11.710000038147</v>
       </c>
       <c r="G366" t="n">
-        <v>10.4398031234741</v>
+        <v>10.4398021697998</v>
       </c>
       <c r="H366" t="n">
         <v>68065</v>
@@ -11041,7 +11041,7 @@
         <v>11</v>
       </c>
       <c r="G368" t="n">
-        <v>9.80681705474854</v>
+        <v>9.80681610107422</v>
       </c>
       <c r="H368" t="n">
         <v>22352</v>
@@ -11070,7 +11070,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G369" t="n">
-        <v>9.67308902740479</v>
+        <v>9.67308807373047</v>
       </c>
       <c r="H369" t="n">
         <v>20493</v>
@@ -11157,7 +11157,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G372" t="n">
-        <v>9.46803665161133</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H372" t="n">
         <v>20681</v>
@@ -11186,7 +11186,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G373" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H373" t="n">
         <v>4636792</v>
@@ -11302,7 +11302,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G377" t="n">
-        <v>9.41454601287842</v>
+        <v>9.4145450592041</v>
       </c>
       <c r="H377" t="n">
         <v>29660</v>
@@ -11331,7 +11331,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G378" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H378" t="n">
         <v>18961</v>
@@ -11360,7 +11360,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G379" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H379" t="n">
         <v>28104</v>
@@ -11447,7 +11447,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H382" t="n">
         <v>36617</v>
@@ -11505,7 +11505,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G384" t="n">
-        <v>9.47695159912109</v>
+        <v>9.47695064544678</v>
       </c>
       <c r="H384" t="n">
         <v>21670</v>
@@ -11563,7 +11563,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G386" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H386" t="n">
         <v>5155</v>
@@ -11592,7 +11592,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G387" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H387" t="n">
         <v>15072</v>
@@ -11621,7 +11621,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G388" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H388" t="n">
         <v>32983</v>
@@ -11650,7 +11650,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G389" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H389" t="n">
         <v>14464</v>
@@ -11679,7 +11679,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G390" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H390" t="n">
         <v>9256</v>
@@ -11708,7 +11708,7 @@
         <v>10.5</v>
       </c>
       <c r="G391" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H391" t="n">
         <v>7500</v>
@@ -11766,7 +11766,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H393" t="n">
         <v>11623</v>
@@ -11795,7 +11795,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G394" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H394" t="n">
         <v>12609</v>
@@ -11824,7 +11824,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G395" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H395" t="n">
         <v>13222</v>
@@ -11882,7 +11882,7 @@
         <v>10.5</v>
       </c>
       <c r="G397" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H397" t="n">
         <v>13753</v>
@@ -11911,7 +11911,7 @@
         <v>10.5</v>
       </c>
       <c r="G398" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H398" t="n">
         <v>7506</v>
@@ -11969,7 +11969,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G400" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H400" t="n">
         <v>11923</v>
@@ -11998,7 +11998,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G401" t="n">
-        <v>9.23623657226562</v>
+        <v>9.23623752593994</v>
       </c>
       <c r="H401" t="n">
         <v>7394</v>
@@ -12027,7 +12027,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G402" t="n">
-        <v>9.20949172973633</v>
+        <v>9.20949268341064</v>
       </c>
       <c r="H402" t="n">
         <v>4211</v>
@@ -12056,7 +12056,7 @@
         <v>10.2600002288818</v>
       </c>
       <c r="G403" t="n">
-        <v>9.14708614349365</v>
+        <v>9.14708709716797</v>
       </c>
       <c r="H403" t="n">
         <v>10030</v>
@@ -12085,7 +12085,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>9.09359455108643</v>
+        <v>9.09359359741211</v>
       </c>
       <c r="H404" t="n">
         <v>8156</v>
@@ -12114,7 +12114,7 @@
         <v>10.25</v>
       </c>
       <c r="G405" t="n">
-        <v>9.13816928863525</v>
+        <v>9.13817024230957</v>
       </c>
       <c r="H405" t="n">
         <v>12431</v>
@@ -12143,7 +12143,7 @@
         <v>10.25</v>
       </c>
       <c r="G406" t="n">
-        <v>9.13816928863525</v>
+        <v>9.13817024230957</v>
       </c>
       <c r="H406" t="n">
         <v>5490</v>
@@ -12201,7 +12201,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G408" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H408" t="n">
         <v>22288</v>
@@ -12259,7 +12259,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G410" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H410" t="n">
         <v>19678</v>
@@ -12288,7 +12288,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G411" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H411" t="n">
         <v>28264</v>
@@ -12317,7 +12317,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G412" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H412" t="n">
         <v>16884</v>
@@ -12346,7 +12346,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G413" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H413" t="n">
         <v>23611</v>
@@ -12375,7 +12375,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G414" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H414" t="n">
         <v>7177</v>
@@ -12404,7 +12404,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G415" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H415" t="n">
         <v>6659</v>
@@ -12462,7 +12462,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G417" t="n">
-        <v>9.46803665161133</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H417" t="n">
         <v>1987</v>
@@ -12520,7 +12520,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G419" t="n">
-        <v>9.41454601287842</v>
+        <v>9.4145450592041</v>
       </c>
       <c r="H419" t="n">
         <v>11130</v>
@@ -12549,7 +12549,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G420" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H420" t="n">
         <v>5897</v>
@@ -12578,7 +12578,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G421" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H421" t="n">
         <v>13775</v>
@@ -12607,7 +12607,7 @@
         <v>10.5</v>
       </c>
       <c r="G422" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H422" t="n">
         <v>9242</v>
@@ -12636,7 +12636,7 @@
         <v>10.5</v>
       </c>
       <c r="G423" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H423" t="n">
         <v>4076</v>
@@ -12665,7 +12665,7 @@
         <v>10.5</v>
       </c>
       <c r="G424" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H424" t="n">
         <v>845</v>
@@ -12694,7 +12694,7 @@
         <v>10.5</v>
       </c>
       <c r="G425" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H425" t="n">
         <v>5285</v>
@@ -12723,7 +12723,7 @@
         <v>10.5</v>
       </c>
       <c r="G426" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H426" t="n">
         <v>1963</v>
@@ -12752,7 +12752,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G427" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H427" t="n">
         <v>3597</v>
@@ -12781,7 +12781,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G428" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H428" t="n">
         <v>4642</v>
@@ -12810,7 +12810,7 @@
         <v>10.5</v>
       </c>
       <c r="G429" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H429" t="n">
         <v>1070</v>
@@ -12868,7 +12868,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G431" t="n">
-        <v>9.52152824401855</v>
+        <v>9.52152729034424</v>
       </c>
       <c r="H431" t="n">
         <v>5497</v>
@@ -12897,7 +12897,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G432" t="n">
-        <v>9.592848777771</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H432" t="n">
         <v>6357</v>
@@ -12926,7 +12926,7 @@
         <v>10.8100004196167</v>
       </c>
       <c r="G433" t="n">
-        <v>9.63742733001709</v>
+        <v>9.63742828369141</v>
       </c>
       <c r="H433" t="n">
         <v>3228</v>
@@ -12955,7 +12955,7 @@
         <v>10.6800003051758</v>
       </c>
       <c r="G434" t="n">
-        <v>9.52152824401855</v>
+        <v>9.52152729034424</v>
       </c>
       <c r="H434" t="n">
         <v>9019</v>
@@ -12984,7 +12984,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G435" t="n">
-        <v>9.41454601287842</v>
+        <v>9.4145450592041</v>
       </c>
       <c r="H435" t="n">
         <v>16590</v>
@@ -13013,7 +13013,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G436" t="n">
-        <v>9.25407028198242</v>
+        <v>9.25407123565674</v>
       </c>
       <c r="H436" t="n">
         <v>33174</v>
@@ -13042,7 +13042,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G437" t="n">
-        <v>9.25407028198242</v>
+        <v>9.25407123565674</v>
       </c>
       <c r="H437" t="n">
         <v>23876</v>
@@ -13071,7 +13071,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G438" t="n">
-        <v>9.46803665161133</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H438" t="n">
         <v>32980</v>
@@ -13100,7 +13100,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G439" t="n">
-        <v>9.592848777771</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H439" t="n">
         <v>11645</v>
@@ -13129,7 +13129,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G440" t="n">
-        <v>9.46803665161133</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H440" t="n">
         <v>12649</v>
@@ -13158,7 +13158,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G441" t="n">
-        <v>9.48586845397949</v>
+        <v>9.48586750030518</v>
       </c>
       <c r="H441" t="n">
         <v>13922</v>
@@ -13187,7 +13187,7 @@
         <v>10.5</v>
       </c>
       <c r="G442" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H442" t="n">
         <v>30432</v>
@@ -13216,7 +13216,7 @@
         <v>10.4700002670288</v>
       </c>
       <c r="G443" t="n">
-        <v>9.33430671691895</v>
+        <v>9.33430767059326</v>
       </c>
       <c r="H443" t="n">
         <v>7591</v>
@@ -13245,7 +13245,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G444" t="n">
-        <v>9.3164758682251</v>
+        <v>9.31647682189941</v>
       </c>
       <c r="H444" t="n">
         <v>10731</v>
@@ -13274,7 +13274,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G445" t="n">
-        <v>9.3164758682251</v>
+        <v>9.31647682189941</v>
       </c>
       <c r="H445" t="n">
         <v>9453</v>
@@ -13332,7 +13332,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G447" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H447" t="n">
         <v>9429</v>
@@ -13361,7 +13361,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H448" t="n">
         <v>28520</v>
@@ -13390,7 +13390,7 @@
         <v>10.5</v>
       </c>
       <c r="G449" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H449" t="n">
         <v>12077</v>
@@ -13477,7 +13477,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G452" t="n">
-        <v>9.3164758682251</v>
+        <v>9.31647682189941</v>
       </c>
       <c r="H452" t="n">
         <v>9724</v>
@@ -13506,7 +13506,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G453" t="n">
-        <v>9.23623657226562</v>
+        <v>9.23623752593994</v>
       </c>
       <c r="H453" t="n">
         <v>4892</v>
@@ -13651,7 +13651,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G458" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H458" t="n">
         <v>39732</v>
@@ -13709,7 +13709,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G460" t="n">
-        <v>9.23623657226562</v>
+        <v>9.23623752593994</v>
       </c>
       <c r="H460" t="n">
         <v>27107</v>
@@ -13767,7 +13767,7 @@
         <v>10.3199996948242</v>
       </c>
       <c r="G462" t="n">
-        <v>9.20057773590088</v>
+        <v>9.20057678222656</v>
       </c>
       <c r="H462" t="n">
         <v>3846</v>
@@ -13796,7 +13796,7 @@
         <v>10.5</v>
       </c>
       <c r="G463" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H463" t="n">
         <v>10385</v>
@@ -13883,7 +13883,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G466" t="n">
-        <v>9.21840667724609</v>
+        <v>9.21840858459473</v>
       </c>
       <c r="H466" t="n">
         <v>19152</v>
@@ -13912,7 +13912,7 @@
         <v>10.3299999237061</v>
       </c>
       <c r="G467" t="n">
-        <v>9.20949172973633</v>
+        <v>9.20949268341064</v>
       </c>
       <c r="H467" t="n">
         <v>10971</v>
@@ -13941,7 +13941,7 @@
         <v>10.4300003051758</v>
       </c>
       <c r="G468" t="n">
-        <v>9.29864597320557</v>
+        <v>9.29864501953125</v>
       </c>
       <c r="H468" t="n">
         <v>6059</v>
@@ -13970,7 +13970,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H469" t="n">
         <v>21920</v>
@@ -13999,7 +13999,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G470" t="n">
-        <v>9.22732448577881</v>
+        <v>9.22732353210449</v>
       </c>
       <c r="H470" t="n">
         <v>4876</v>
@@ -14028,7 +14028,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G471" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H471" t="n">
         <v>11273</v>
@@ -14057,7 +14057,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G472" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H472" t="n">
         <v>7887</v>
@@ -14086,7 +14086,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G473" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H473" t="n">
         <v>4137</v>
@@ -14115,7 +14115,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G474" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H474" t="n">
         <v>104971</v>
@@ -14173,7 +14173,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G476" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H476" t="n">
         <v>30305</v>
@@ -14202,7 +14202,7 @@
         <v>10.5</v>
       </c>
       <c r="G477" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H477" t="n">
         <v>8518</v>
@@ -14231,7 +14231,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G478" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H478" t="n">
         <v>5316</v>
@@ -14289,7 +14289,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G480" t="n">
-        <v>9.4056282043457</v>
+        <v>9.40562915802002</v>
       </c>
       <c r="H480" t="n">
         <v>9052</v>
@@ -14318,7 +14318,7 @@
         <v>10.25</v>
       </c>
       <c r="G481" t="n">
-        <v>9.13816928863525</v>
+        <v>9.13817024230957</v>
       </c>
       <c r="H481" t="n">
         <v>16931</v>
@@ -14434,7 +14434,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G485" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H485" t="n">
         <v>23241</v>
@@ -14463,7 +14463,7 @@
         <v>10.75</v>
       </c>
       <c r="G486" t="n">
-        <v>9.58393478393555</v>
+        <v>9.58393573760986</v>
       </c>
       <c r="H486" t="n">
         <v>15348</v>
@@ -14492,7 +14492,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G487" t="n">
-        <v>9.67308902740479</v>
+        <v>9.67308807373047</v>
       </c>
       <c r="H487" t="n">
         <v>57982</v>
@@ -14521,7 +14521,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G488" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H488" t="n">
         <v>17941</v>
@@ -14579,7 +14579,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G490" t="n">
-        <v>9.64634132385254</v>
+        <v>9.64634227752686</v>
       </c>
       <c r="H490" t="n">
         <v>21920</v>
@@ -14608,7 +14608,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G491" t="n">
-        <v>9.73549461364746</v>
+        <v>9.73549365997314</v>
       </c>
       <c r="H491" t="n">
         <v>4719</v>
@@ -14666,7 +14666,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G493" t="n">
-        <v>9.30755996704102</v>
+        <v>9.30756092071533</v>
       </c>
       <c r="H493" t="n">
         <v>15192</v>
@@ -14695,7 +14695,7 @@
         <v>10.7700004577637</v>
       </c>
       <c r="G494" t="n">
-        <v>9.60176658630371</v>
+        <v>9.60176467895508</v>
       </c>
       <c r="H494" t="n">
         <v>12114</v>
@@ -14724,7 +14724,7 @@
         <v>11.0299997329712</v>
       </c>
       <c r="G495" t="n">
-        <v>9.83356189727783</v>
+        <v>9.83356285095215</v>
       </c>
       <c r="H495" t="n">
         <v>11597</v>
@@ -14753,7 +14753,7 @@
         <v>10.9300003051758</v>
       </c>
       <c r="G496" t="n">
-        <v>9.74441051483154</v>
+        <v>9.74441146850586</v>
       </c>
       <c r="H496" t="n">
         <v>8197</v>
@@ -14811,7 +14811,7 @@
         <v>10.8900003433228</v>
       </c>
       <c r="G498" t="n">
-        <v>9.70875072479248</v>
+        <v>9.70874977111816</v>
       </c>
       <c r="H498" t="n">
         <v>483</v>
@@ -14869,7 +14869,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G500" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H500" t="n">
         <v>3490</v>
@@ -14898,7 +14898,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G501" t="n">
-        <v>9.3164758682251</v>
+        <v>9.31647682189941</v>
       </c>
       <c r="H501" t="n">
         <v>4612</v>
@@ -14927,7 +14927,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G502" t="n">
-        <v>9.09359455108643</v>
+        <v>9.09359359741211</v>
       </c>
       <c r="H502" t="n">
         <v>24207</v>
@@ -14956,7 +14956,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G503" t="n">
-        <v>9.04901599884033</v>
+        <v>9.04901695251465</v>
       </c>
       <c r="H503" t="n">
         <v>23316</v>
@@ -14985,7 +14985,7 @@
         <v>10.1099996566772</v>
       </c>
       <c r="G504" t="n">
-        <v>9.01335716247559</v>
+        <v>9.01335620880127</v>
       </c>
       <c r="H504" t="n">
         <v>33740</v>
@@ -15072,7 +15072,7 @@
         <v>10.2299995422363</v>
       </c>
       <c r="G507" t="n">
-        <v>9.12033843994141</v>
+        <v>9.12034034729004</v>
       </c>
       <c r="H507" t="n">
         <v>17954</v>
@@ -15130,7 +15130,7 @@
         <v>10.2700004577637</v>
       </c>
       <c r="G509" t="n">
-        <v>9.15600204467773</v>
+        <v>9.15600109100342</v>
       </c>
       <c r="H509" t="n">
         <v>1553</v>
@@ -15159,7 +15159,7 @@
         <v>10.5</v>
       </c>
       <c r="G510" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H510" t="n">
         <v>20934</v>
@@ -15188,7 +15188,7 @@
         <v>10.6300001144409</v>
       </c>
       <c r="G511" t="n">
-        <v>9.47695159912109</v>
+        <v>9.47695064544678</v>
       </c>
       <c r="H511" t="n">
         <v>5177</v>
@@ -15217,7 +15217,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G512" t="n">
-        <v>9.34322166442871</v>
+        <v>9.34322071075439</v>
       </c>
       <c r="H512" t="n">
         <v>2193</v>
@@ -15246,7 +15246,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G513" t="n">
-        <v>9.3253927230835</v>
+        <v>9.32539176940918</v>
       </c>
       <c r="H513" t="n">
         <v>9657</v>
@@ -15275,7 +15275,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G514" t="n">
-        <v>9.30755996704102</v>
+        <v>9.30756092071533</v>
       </c>
       <c r="H514" t="n">
         <v>32641</v>
@@ -15304,7 +15304,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G515" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H515" t="n">
         <v>12058</v>
@@ -15362,7 +15362,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G517" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H517" t="n">
         <v>26556</v>
@@ -15420,7 +15420,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G519" t="n">
-        <v>9.00444316864014</v>
+        <v>9.00444221496582</v>
       </c>
       <c r="H519" t="n">
         <v>57663</v>
@@ -15449,7 +15449,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G520" t="n">
-        <v>9.09359455108643</v>
+        <v>9.09359359741211</v>
       </c>
       <c r="H520" t="n">
         <v>7970</v>
@@ -15507,7 +15507,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G522" t="n">
-        <v>9.21840667724609</v>
+        <v>9.21840858459473</v>
       </c>
       <c r="H522" t="n">
         <v>8334</v>
@@ -15536,7 +15536,7 @@
         <v>10.5</v>
       </c>
       <c r="G523" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H523" t="n">
         <v>8693</v>
@@ -15565,7 +15565,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G524" t="n">
-        <v>9.41454601287842</v>
+        <v>9.4145450592041</v>
       </c>
       <c r="H524" t="n">
         <v>5293</v>
@@ -15594,7 +15594,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G525" t="n">
-        <v>9.5393590927124</v>
+        <v>9.53935813903809</v>
       </c>
       <c r="H525" t="n">
         <v>7037</v>
@@ -15623,7 +15623,7 @@
         <v>10.6599998474121</v>
       </c>
       <c r="G526" t="n">
-        <v>9.50369739532471</v>
+        <v>9.50369834899902</v>
       </c>
       <c r="H526" t="n">
         <v>11318</v>
@@ -15652,7 +15652,7 @@
         <v>10.7600002288818</v>
       </c>
       <c r="G527" t="n">
-        <v>9.592848777771</v>
+        <v>9.59284973144531</v>
       </c>
       <c r="H527" t="n">
         <v>15071</v>
@@ -15710,7 +15710,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G529" t="n">
-        <v>9.61068153381348</v>
+        <v>9.61068058013916</v>
       </c>
       <c r="H529" t="n">
         <v>7263</v>
@@ -15739,7 +15739,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G530" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H530" t="n">
         <v>80</v>
@@ -15768,7 +15768,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G531" t="n">
-        <v>9.64634132385254</v>
+        <v>9.64634227752686</v>
       </c>
       <c r="H531" t="n">
         <v>6447</v>
@@ -15855,7 +15855,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G534" t="n">
-        <v>9.23623657226562</v>
+        <v>9.23623752593994</v>
       </c>
       <c r="H534" t="n">
         <v>2616</v>
@@ -15884,7 +15884,7 @@
         <v>10.5</v>
       </c>
       <c r="G535" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H535" t="n">
         <v>14368</v>
@@ -16000,7 +16000,7 @@
         <v>10.5</v>
       </c>
       <c r="G539" t="n">
-        <v>9.36105251312256</v>
+        <v>9.36105346679688</v>
       </c>
       <c r="H539" t="n">
         <v>7725</v>
@@ -16029,7 +16029,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G540" t="n">
-        <v>9.23623657226562</v>
+        <v>9.23623752593994</v>
       </c>
       <c r="H540" t="n">
         <v>10611</v>
@@ -16058,7 +16058,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G541" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H541" t="n">
         <v>14882</v>
@@ -16087,7 +16087,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G542" t="n">
-        <v>8.98661041259766</v>
+        <v>8.98661136627197</v>
       </c>
       <c r="H542" t="n">
         <v>20475</v>
@@ -16116,7 +16116,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G543" t="n">
-        <v>9.34322166442871</v>
+        <v>9.34322071075439</v>
       </c>
       <c r="H543" t="n">
         <v>24708</v>
@@ -16145,7 +16145,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G544" t="n">
-        <v>9.27189922332764</v>
+        <v>9.27190017700195</v>
       </c>
       <c r="H544" t="n">
         <v>27874</v>
@@ -16203,7 +16203,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G546" t="n">
-        <v>8.98661041259766</v>
+        <v>8.98661136627197</v>
       </c>
       <c r="H546" t="n">
         <v>8062</v>
@@ -16261,7 +16261,7 @@
         <v>10.1400003433228</v>
       </c>
       <c r="G548" t="n">
-        <v>9.04010391235352</v>
+        <v>9.0401029586792</v>
       </c>
       <c r="H548" t="n">
         <v>36378</v>
@@ -16319,7 +16319,7 @@
         <v>10.460000038147</v>
       </c>
       <c r="G550" t="n">
-        <v>9.3253927230835</v>
+        <v>9.32539176940918</v>
       </c>
       <c r="H550" t="n">
         <v>6723</v>
@@ -16377,7 +16377,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G552" t="n">
-        <v>9.21840667724609</v>
+        <v>9.21840858459473</v>
       </c>
       <c r="H552" t="n">
         <v>13956</v>
@@ -16406,7 +16406,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G553" t="n">
-        <v>9.34322166442871</v>
+        <v>9.34322071075439</v>
       </c>
       <c r="H553" t="n">
         <v>26292</v>
@@ -16435,7 +16435,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G554" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H554" t="n">
         <v>100659</v>
@@ -16464,7 +16464,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G555" t="n">
-        <v>9.78898620605469</v>
+        <v>9.788987159729</v>
       </c>
       <c r="H555" t="n">
         <v>23195</v>
@@ -16493,7 +16493,7 @@
         <v>11</v>
       </c>
       <c r="G556" t="n">
-        <v>9.80681705474854</v>
+        <v>9.80681610107422</v>
       </c>
       <c r="H556" t="n">
         <v>59233</v>
@@ -16522,7 +16522,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G557" t="n">
-        <v>9.87813949584961</v>
+        <v>9.87813854217529</v>
       </c>
       <c r="H557" t="n">
         <v>40540</v>
@@ -16551,7 +16551,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G558" t="n">
-        <v>10.43088722229</v>
+        <v>10.4308881759644</v>
       </c>
       <c r="H558" t="n">
         <v>215011</v>
@@ -16609,7 +16609,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G560" t="n">
-        <v>10.4665498733521</v>
+        <v>10.4665489196777</v>
       </c>
       <c r="H560" t="n">
         <v>39068</v>
@@ -16696,7 +16696,7 @@
         <v>12</v>
       </c>
       <c r="G563" t="n">
-        <v>10.6983461380005</v>
+        <v>10.6983470916748</v>
       </c>
       <c r="H563" t="n">
         <v>86941</v>
@@ -16725,7 +16725,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G564" t="n">
-        <v>10.6270236968994</v>
+        <v>10.6270227432251</v>
       </c>
       <c r="H564" t="n">
         <v>38930</v>
@@ -16754,7 +16754,7 @@
         <v>11.8599996566772</v>
       </c>
       <c r="G565" t="n">
-        <v>10.5735311508179</v>
+        <v>10.5735321044922</v>
       </c>
       <c r="H565" t="n">
         <v>259538</v>
@@ -16841,7 +16841,7 @@
         <v>11.5</v>
       </c>
       <c r="G568" t="n">
-        <v>10.2525825500488</v>
+        <v>10.2525806427002</v>
       </c>
       <c r="H568" t="n">
         <v>20094</v>
@@ -16870,7 +16870,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G569" t="n">
-        <v>10.0921068191528</v>
+        <v>10.0921058654785</v>
       </c>
       <c r="H569" t="n">
         <v>16994</v>
@@ -16928,7 +16928,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G571" t="n">
-        <v>10.0564451217651</v>
+        <v>10.0564441680908</v>
       </c>
       <c r="H571" t="n">
         <v>7153</v>
@@ -17015,7 +17015,7 @@
         <v>11</v>
       </c>
       <c r="G574" t="n">
-        <v>9.80681705474854</v>
+        <v>9.80681610107422</v>
       </c>
       <c r="H574" t="n">
         <v>15974</v>
@@ -17044,7 +17044,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G575" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H575" t="n">
         <v>16571</v>
@@ -17102,7 +17102,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G577" t="n">
-        <v>9.55718994140625</v>
+        <v>9.55718898773193</v>
       </c>
       <c r="H577" t="n">
         <v>28213</v>
@@ -17131,7 +17131,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G578" t="n">
-        <v>9.62851142883301</v>
+        <v>9.62851238250732</v>
       </c>
       <c r="H578" t="n">
         <v>25531</v>
@@ -17160,7 +17160,7 @@
         <v>10.5600004196167</v>
       </c>
       <c r="G579" t="n">
-        <v>9.41454601287842</v>
+        <v>9.4145450592041</v>
       </c>
       <c r="H579" t="n">
         <v>26470</v>
@@ -17189,7 +17189,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G580" t="n">
-        <v>9.73549461364746</v>
+        <v>9.73549365997314</v>
       </c>
       <c r="H580" t="n">
         <v>29642</v>
@@ -17218,7 +17218,7 @@
         <v>11.1400003433228</v>
       </c>
       <c r="G581" t="n">
-        <v>9.93163204193115</v>
+        <v>9.93163108825684</v>
       </c>
       <c r="H581" t="n">
         <v>10411</v>
@@ -17247,7 +17247,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G582" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H582" t="n">
         <v>5977</v>
@@ -17276,7 +17276,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G583" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H583" t="n">
         <v>13183</v>
@@ -17305,7 +17305,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G584" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H584" t="n">
         <v>18893</v>
@@ -17334,7 +17334,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G585" t="n">
-        <v>9.77115631103516</v>
+        <v>9.77115535736084</v>
       </c>
       <c r="H585" t="n">
         <v>204901</v>
@@ -17363,7 +17363,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G586" t="n">
-        <v>9.73549461364746</v>
+        <v>9.73549365997314</v>
       </c>
       <c r="H586" t="n">
         <v>10236</v>
@@ -17392,7 +17392,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G587" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H587" t="n">
         <v>8488</v>
@@ -17421,7 +17421,7 @@
         <v>11.3199996948242</v>
       </c>
       <c r="G588" t="n">
-        <v>10.0921068191528</v>
+        <v>10.0921058654785</v>
       </c>
       <c r="H588" t="n">
         <v>13867</v>
@@ -17479,7 +17479,7 @@
         <v>11.5</v>
       </c>
       <c r="G590" t="n">
-        <v>10.2525825500488</v>
+        <v>10.2525806427002</v>
       </c>
       <c r="H590" t="n">
         <v>37831</v>
@@ -17537,7 +17537,7 @@
         <v>11.5</v>
       </c>
       <c r="G592" t="n">
-        <v>10.2525825500488</v>
+        <v>10.2525806427002</v>
       </c>
       <c r="H592" t="n">
         <v>11528</v>
@@ -17595,7 +17595,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G594" t="n">
-        <v>10.1455984115601</v>
+        <v>10.1455993652344</v>
       </c>
       <c r="H594" t="n">
         <v>6655</v>
@@ -17624,7 +17624,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G595" t="n">
-        <v>10.1634292602539</v>
+        <v>10.1634283065796</v>
       </c>
       <c r="H595" t="n">
         <v>2549</v>
@@ -17682,7 +17682,7 @@
         <v>11.9799995422363</v>
       </c>
       <c r="G597" t="n">
-        <v>10.680513381958</v>
+        <v>10.6805143356323</v>
       </c>
       <c r="H597" t="n">
         <v>27249</v>
@@ -17711,7 +17711,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>10.43088722229</v>
+        <v>10.4308881759644</v>
       </c>
       <c r="H598" t="n">
         <v>11050</v>
@@ -17740,7 +17740,7 @@
         <v>11.4200000762939</v>
       </c>
       <c r="G599" t="n">
-        <v>10.1812610626221</v>
+        <v>10.1812591552734</v>
       </c>
       <c r="H599" t="n">
         <v>5857</v>
@@ -17769,7 +17769,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G600" t="n">
-        <v>9.84247875213623</v>
+        <v>9.8424768447876</v>
       </c>
       <c r="H600" t="n">
         <v>44414</v>
@@ -17798,7 +17798,7 @@
         <v>10.6199998855591</v>
       </c>
       <c r="G601" t="n">
-        <v>9.46803665161133</v>
+        <v>9.46803569793701</v>
       </c>
       <c r="H601" t="n">
         <v>52636</v>
@@ -17827,7 +17827,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G602" t="n">
-        <v>9.45020580291748</v>
+        <v>9.45020484924316</v>
       </c>
       <c r="H602" t="n">
         <v>26850</v>
@@ -17856,7 +17856,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G603" t="n">
-        <v>9.73549461364746</v>
+        <v>9.73549365997314</v>
       </c>
       <c r="H603" t="n">
         <v>66416</v>
@@ -17885,7 +17885,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G604" t="n">
-        <v>9.84247875213623</v>
+        <v>9.8424768447876</v>
       </c>
       <c r="H604" t="n">
         <v>12773</v>
@@ -17943,7 +17943,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G606" t="n">
-        <v>9.82464981079102</v>
+        <v>9.8246488571167</v>
       </c>
       <c r="H606" t="n">
         <v>36151</v>
@@ -17972,7 +17972,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G607" t="n">
-        <v>9.7176628112793</v>
+        <v>9.71766376495361</v>
       </c>
       <c r="H607" t="n">
         <v>78946</v>
@@ -18059,7 +18059,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G610" t="n">
-        <v>9.79902172088623</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H610" t="n">
         <v>20207</v>
@@ -18088,7 +18088,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G611" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882911682129</v>
       </c>
       <c r="H611" t="n">
         <v>17961</v>
@@ -18117,7 +18117,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G612" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H612" t="n">
         <v>13121</v>
@@ -18175,7 +18175,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G614" t="n">
-        <v>9.40127468109131</v>
+        <v>9.40127563476562</v>
       </c>
       <c r="H614" t="n">
         <v>32400</v>
@@ -18204,7 +18204,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G615" t="n">
-        <v>9.69054412841797</v>
+        <v>9.69054508209229</v>
       </c>
       <c r="H615" t="n">
         <v>28069</v>
@@ -18262,7 +18262,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G617" t="n">
-        <v>9.69054412841797</v>
+        <v>9.69054508209229</v>
       </c>
       <c r="H617" t="n">
         <v>18097</v>
@@ -18291,7 +18291,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G618" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H618" t="n">
         <v>6484</v>
@@ -18378,7 +18378,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G621" t="n">
-        <v>10.3052444458008</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H621" t="n">
         <v>12133</v>
@@ -18465,7 +18465,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G624" t="n">
-        <v>10.6125917434692</v>
+        <v>10.6125926971436</v>
       </c>
       <c r="H624" t="n">
         <v>15870</v>
@@ -18494,7 +18494,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G625" t="n">
-        <v>10.5402765274048</v>
+        <v>10.5402755737305</v>
       </c>
       <c r="H625" t="n">
         <v>17727</v>
@@ -18610,7 +18610,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>10.3052444458008</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H629" t="n">
         <v>7309</v>
@@ -18639,7 +18639,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G630" t="n">
-        <v>10.1425294876099</v>
+        <v>10.1425304412842</v>
       </c>
       <c r="H630" t="n">
         <v>7952</v>
@@ -18755,7 +18755,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G634" t="n">
-        <v>10.2690839767456</v>
+        <v>10.2690849304199</v>
       </c>
       <c r="H634" t="n">
         <v>6424</v>
@@ -18784,7 +18784,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G635" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H635" t="n">
         <v>15922</v>
@@ -18842,7 +18842,7 @@
         <v>10.5</v>
       </c>
       <c r="G637" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H637" t="n">
         <v>32207</v>
@@ -18871,7 +18871,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G638" t="n">
-        <v>9.34703826904297</v>
+        <v>9.34703731536865</v>
       </c>
       <c r="H638" t="n">
         <v>45306</v>
@@ -18929,7 +18929,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G640" t="n">
-        <v>9.47359180450439</v>
+        <v>9.47359085083008</v>
       </c>
       <c r="H640" t="n">
         <v>12764</v>
@@ -18987,7 +18987,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G642" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H642" t="n">
         <v>20148</v>
@@ -19016,7 +19016,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G643" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882911682129</v>
       </c>
       <c r="H643" t="n">
         <v>12748</v>
@@ -19045,7 +19045,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G644" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882911682129</v>
       </c>
       <c r="H644" t="n">
         <v>21220</v>
@@ -19074,7 +19074,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G645" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H645" t="n">
         <v>2324</v>
@@ -19161,7 +19161,7 @@
         <v>11</v>
       </c>
       <c r="G648" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H648" t="n">
         <v>13457</v>
@@ -19219,7 +19219,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G650" t="n">
-        <v>10.1244506835938</v>
+        <v>10.1244497299194</v>
       </c>
       <c r="H650" t="n">
         <v>74885</v>
@@ -19335,7 +19335,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G654" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H654" t="n">
         <v>4117</v>
@@ -19364,7 +19364,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G655" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87133884429932</v>
       </c>
       <c r="H655" t="n">
         <v>1822</v>
@@ -19393,7 +19393,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H656" t="n">
         <v>7599</v>
@@ -19422,7 +19422,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G657" t="n">
-        <v>9.79902172088623</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H657" t="n">
         <v>3469</v>
@@ -19509,7 +19509,7 @@
         <v>11</v>
       </c>
       <c r="G660" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H660" t="n">
         <v>6088</v>
@@ -19567,7 +19567,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H662" t="n">
         <v>7902</v>
@@ -19596,7 +19596,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G663" t="n">
-        <v>9.7086238861084</v>
+        <v>9.70862483978271</v>
       </c>
       <c r="H663" t="n">
         <v>13483</v>
@@ -19654,7 +19654,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G665" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H665" t="n">
         <v>2732</v>
@@ -19683,7 +19683,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G666" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H666" t="n">
         <v>1481</v>
@@ -19799,7 +19799,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G670" t="n">
-        <v>9.3831958770752</v>
+        <v>9.38319778442383</v>
       </c>
       <c r="H670" t="n">
         <v>28506</v>
@@ -19828,7 +19828,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G671" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H671" t="n">
         <v>11434</v>
@@ -19857,7 +19857,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G672" t="n">
-        <v>9.43743228912354</v>
+        <v>9.43743324279785</v>
       </c>
       <c r="H672" t="n">
         <v>8929</v>
@@ -19886,7 +19886,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G673" t="n">
-        <v>9.36511611938477</v>
+        <v>9.36511516571045</v>
       </c>
       <c r="H673" t="n">
         <v>1943</v>
@@ -19915,7 +19915,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G674" t="n">
-        <v>9.43743228912354</v>
+        <v>9.43743324279785</v>
       </c>
       <c r="H674" t="n">
         <v>2007</v>
@@ -19944,7 +19944,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H675" t="n">
         <v>9236</v>
@@ -19973,7 +19973,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G676" t="n">
-        <v>9.74478435516357</v>
+        <v>9.74478340148926</v>
       </c>
       <c r="H676" t="n">
         <v>941</v>
@@ -20002,7 +20002,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G677" t="n">
-        <v>9.79902172088623</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H677" t="n">
         <v>796</v>
@@ -20089,7 +20089,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G680" t="n">
-        <v>9.34703826904297</v>
+        <v>9.34703731536865</v>
       </c>
       <c r="H680" t="n">
         <v>2083</v>
@@ -20147,7 +20147,7 @@
         <v>10.5</v>
       </c>
       <c r="G682" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H682" t="n">
         <v>3455</v>
@@ -20205,7 +20205,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G684" t="n">
-        <v>9.47359180450439</v>
+        <v>9.47359085083008</v>
       </c>
       <c r="H684" t="n">
         <v>6197</v>
@@ -20350,7 +20350,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H689" t="n">
         <v>40400</v>
@@ -20437,7 +20437,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G692" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87133884429932</v>
       </c>
       <c r="H692" t="n">
         <v>17631</v>
@@ -20466,7 +20466,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G693" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87133884429932</v>
       </c>
       <c r="H693" t="n">
         <v>31130</v>
@@ -20495,7 +20495,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G694" t="n">
-        <v>9.90749835968018</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H694" t="n">
         <v>2518</v>
@@ -20524,7 +20524,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G695" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H695" t="n">
         <v>2757</v>
@@ -20553,7 +20553,7 @@
         <v>11</v>
       </c>
       <c r="G696" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H696" t="n">
         <v>20059</v>
@@ -20611,7 +20611,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G698" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H698" t="n">
         <v>55492</v>
@@ -20640,7 +20640,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G699" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H699" t="n">
         <v>10609</v>
@@ -20669,7 +20669,7 @@
         <v>10.5</v>
       </c>
       <c r="G700" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H700" t="n">
         <v>19523</v>
@@ -20756,7 +20756,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G703" t="n">
-        <v>9.40127468109131</v>
+        <v>9.40127563476562</v>
       </c>
       <c r="H703" t="n">
         <v>5337</v>
@@ -20988,7 +20988,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G711" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H711" t="n">
         <v>17094</v>
@@ -21017,7 +21017,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G712" t="n">
-        <v>9.43743228912354</v>
+        <v>9.43743324279785</v>
       </c>
       <c r="H712" t="n">
         <v>14263</v>
@@ -21046,7 +21046,7 @@
         <v>10.5</v>
       </c>
       <c r="G713" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H713" t="n">
         <v>5500</v>
@@ -21075,7 +21075,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G714" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H714" t="n">
         <v>5090</v>
@@ -21162,7 +21162,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G717" t="n">
-        <v>9.3831958770752</v>
+        <v>9.38319778442383</v>
       </c>
       <c r="H717" t="n">
         <v>5253</v>
@@ -21191,7 +21191,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G718" t="n">
-        <v>9.20240306854248</v>
+        <v>9.2024040222168</v>
       </c>
       <c r="H718" t="n">
         <v>8624</v>
@@ -21220,7 +21220,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G719" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H719" t="n">
         <v>7840</v>
@@ -21249,7 +21249,7 @@
         <v>10.1800003051758</v>
       </c>
       <c r="G720" t="n">
-        <v>9.20240306854248</v>
+        <v>9.2024040222168</v>
       </c>
       <c r="H720" t="n">
         <v>3455</v>
@@ -21278,7 +21278,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G721" t="n">
-        <v>9.13008499145508</v>
+        <v>9.13008594512939</v>
       </c>
       <c r="H721" t="n">
         <v>7096</v>
@@ -21336,7 +21336,7 @@
         <v>10.5</v>
       </c>
       <c r="G723" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H723" t="n">
         <v>14143</v>
@@ -21423,7 +21423,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H726" t="n">
         <v>2824</v>
@@ -21452,7 +21452,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G727" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H727" t="n">
         <v>4825</v>
@@ -21481,7 +21481,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G728" t="n">
-        <v>9.40127468109131</v>
+        <v>9.40127563476562</v>
       </c>
       <c r="H728" t="n">
         <v>5591</v>
@@ -21510,7 +21510,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G729" t="n">
-        <v>9.47359180450439</v>
+        <v>9.47359085083008</v>
       </c>
       <c r="H729" t="n">
         <v>1514</v>
@@ -21568,7 +21568,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H731" t="n">
         <v>12349</v>
@@ -21684,7 +21684,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G735" t="n">
-        <v>9.47359180450439</v>
+        <v>9.47359085083008</v>
       </c>
       <c r="H735" t="n">
         <v>2726</v>
@@ -21713,7 +21713,7 @@
         <v>10.5</v>
       </c>
       <c r="G736" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H736" t="n">
         <v>4129</v>
@@ -21771,7 +21771,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G738" t="n">
-        <v>9.07584762573242</v>
+        <v>9.07584667205811</v>
       </c>
       <c r="H738" t="n">
         <v>213763</v>
@@ -21800,7 +21800,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G739" t="n">
-        <v>9.3831958770752</v>
+        <v>9.38319778442383</v>
       </c>
       <c r="H739" t="n">
         <v>19525</v>
@@ -21858,7 +21858,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G741" t="n">
-        <v>9.47359180450439</v>
+        <v>9.47359085083008</v>
       </c>
       <c r="H741" t="n">
         <v>889</v>
@@ -21916,7 +21916,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G743" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H743" t="n">
         <v>6091</v>
@@ -21945,7 +21945,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G744" t="n">
-        <v>9.79902172088623</v>
+        <v>9.7990198135376</v>
       </c>
       <c r="H744" t="n">
         <v>8959</v>
@@ -21974,7 +21974,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G745" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H745" t="n">
         <v>887</v>
@@ -22003,7 +22003,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H746" t="n">
         <v>14467</v>
@@ -22032,7 +22032,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G747" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H747" t="n">
         <v>30322</v>
@@ -22061,7 +22061,7 @@
         <v>11</v>
       </c>
       <c r="G748" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H748" t="n">
         <v>18473</v>
@@ -22090,7 +22090,7 @@
         <v>11</v>
       </c>
       <c r="G749" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H749" t="n">
         <v>4869</v>
@@ -22119,7 +22119,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G750" t="n">
-        <v>10.2871646881104</v>
+        <v>10.2871656417847</v>
       </c>
       <c r="H750" t="n">
         <v>13018</v>
@@ -22148,7 +22148,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G751" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H751" t="n">
         <v>10706</v>
@@ -22177,7 +22177,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G752" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H752" t="n">
         <v>14565</v>
@@ -22206,7 +22206,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G753" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H753" t="n">
         <v>6719</v>
@@ -22264,7 +22264,7 @@
         <v>10.5</v>
       </c>
       <c r="G755" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H755" t="n">
         <v>4220</v>
@@ -22322,7 +22322,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G757" t="n">
-        <v>9.36511611938477</v>
+        <v>9.36511516571045</v>
       </c>
       <c r="H757" t="n">
         <v>13111</v>
@@ -22351,7 +22351,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G758" t="n">
-        <v>9.34703826904297</v>
+        <v>9.34703731536865</v>
       </c>
       <c r="H758" t="n">
         <v>5652</v>
@@ -22380,7 +22380,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G759" t="n">
-        <v>9.25664138793945</v>
+        <v>9.25664043426514</v>
       </c>
       <c r="H759" t="n">
         <v>23189</v>
@@ -22467,7 +22467,7 @@
         <v>10.3400001525879</v>
       </c>
       <c r="G762" t="n">
-        <v>9.34703826904297</v>
+        <v>9.34703731536865</v>
       </c>
       <c r="H762" t="n">
         <v>17485</v>
@@ -22583,7 +22583,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.757227897644</v>
+        <v>10.7572269439697</v>
       </c>
       <c r="H766" t="n">
         <v>35007</v>
@@ -22612,7 +22612,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G767" t="n">
-        <v>10.4860372543335</v>
+        <v>10.4860382080078</v>
       </c>
       <c r="H767" t="n">
         <v>11988</v>
@@ -22728,7 +22728,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G771" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H771" t="n">
         <v>12394</v>
@@ -22757,7 +22757,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G772" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H772" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>11.2600002288818</v>
       </c>
       <c r="G773" t="n">
-        <v>10.178689956665</v>
+        <v>10.1786880493164</v>
       </c>
       <c r="H773" t="n">
         <v>5450</v>
@@ -22844,7 +22844,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G775" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H775" t="n">
         <v>2385</v>
@@ -22873,7 +22873,7 @@
         <v>10.7399997711182</v>
       </c>
       <c r="G776" t="n">
-        <v>9.7086238861084</v>
+        <v>9.70862483978271</v>
       </c>
       <c r="H776" t="n">
         <v>5946</v>
@@ -22931,7 +22931,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G778" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H778" t="n">
         <v>12021</v>
@@ -22989,7 +22989,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G780" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H780" t="n">
         <v>13116</v>
@@ -23047,7 +23047,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G782" t="n">
-        <v>9.90749835968018</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H782" t="n">
         <v>4037</v>
@@ -23134,7 +23134,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>10.1244506835938</v>
+        <v>10.1244497299194</v>
       </c>
       <c r="H785" t="n">
         <v>11418</v>
@@ -23163,7 +23163,7 @@
         <v>10.5</v>
       </c>
       <c r="G786" t="n">
-        <v>9.49167156219482</v>
+        <v>9.49167251586914</v>
       </c>
       <c r="H786" t="n">
         <v>47266</v>
@@ -23192,7 +23192,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G787" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H787" t="n">
         <v>10528</v>
@@ -23250,7 +23250,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H789" t="n">
         <v>8577</v>
@@ -23308,7 +23308,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>9.58206939697266</v>
+        <v>9.58206844329834</v>
       </c>
       <c r="H791" t="n">
         <v>1816</v>
@@ -23395,7 +23395,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G794" t="n">
-        <v>9.74478435516357</v>
+        <v>9.74478340148926</v>
       </c>
       <c r="H794" t="n">
         <v>1251</v>
@@ -23453,7 +23453,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G796" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H796" t="n">
         <v>7098</v>
@@ -23482,7 +23482,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G797" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H797" t="n">
         <v>19404</v>
@@ -23511,7 +23511,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G798" t="n">
-        <v>9.76286220550537</v>
+        <v>9.76286315917969</v>
       </c>
       <c r="H798" t="n">
         <v>3557</v>
@@ -23569,7 +23569,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G800" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H800" t="n">
         <v>3357</v>
@@ -23598,7 +23598,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G801" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H801" t="n">
         <v>3647</v>
@@ -23627,7 +23627,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G802" t="n">
-        <v>9.78094100952148</v>
+        <v>9.7809419631958</v>
       </c>
       <c r="H802" t="n">
         <v>1774</v>
@@ -23743,7 +23743,7 @@
         <v>10.960000038147</v>
       </c>
       <c r="G806" t="n">
-        <v>9.90749835968018</v>
+        <v>9.90749740600586</v>
       </c>
       <c r="H806" t="n">
         <v>3793</v>
@@ -23801,7 +23801,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G808" t="n">
-        <v>9.96173572540283</v>
+        <v>9.96173667907715</v>
       </c>
       <c r="H808" t="n">
         <v>4865</v>
@@ -23859,7 +23859,7 @@
         <v>11.0200004577637</v>
       </c>
       <c r="G810" t="n">
-        <v>9.96173572540283</v>
+        <v>9.96173667907715</v>
       </c>
       <c r="H810" t="n">
         <v>5469</v>
@@ -23888,7 +23888,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G811" t="n">
-        <v>9.97981452941895</v>
+        <v>9.97981357574463</v>
       </c>
       <c r="H811" t="n">
         <v>7180</v>
@@ -23917,7 +23917,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G812" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882911682129</v>
       </c>
       <c r="H812" t="n">
         <v>6418</v>
@@ -23946,7 +23946,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G813" t="n">
-        <v>9.85325813293457</v>
+        <v>9.85325908660889</v>
       </c>
       <c r="H813" t="n">
         <v>10082</v>
@@ -23975,7 +23975,7 @@
         <v>11</v>
       </c>
       <c r="G814" t="n">
-        <v>9.94365501403809</v>
+        <v>9.9436559677124</v>
       </c>
       <c r="H814" t="n">
         <v>6928</v>
@@ -24033,7 +24033,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G816" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521326065063</v>
       </c>
       <c r="H816" t="n">
         <v>14899</v>
@@ -24091,7 +24091,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G818" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521326065063</v>
       </c>
       <c r="H818" t="n">
         <v>1167</v>
@@ -24120,7 +24120,7 @@
         <v>10.9399995803833</v>
       </c>
       <c r="G819" t="n">
-        <v>9.88941860198975</v>
+        <v>9.88941764831543</v>
       </c>
       <c r="H819" t="n">
         <v>13399</v>
@@ -24149,7 +24149,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G820" t="n">
-        <v>10.1967678070068</v>
+        <v>10.1967668533325</v>
       </c>
       <c r="H820" t="n">
         <v>10488</v>
@@ -24178,7 +24178,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G821" t="n">
-        <v>9.97981452941895</v>
+        <v>9.97981357574463</v>
       </c>
       <c r="H821" t="n">
         <v>9935</v>
@@ -24207,7 +24207,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G822" t="n">
-        <v>9.97981452941895</v>
+        <v>9.97981357574463</v>
       </c>
       <c r="H822" t="n">
         <v>7718</v>
@@ -24265,7 +24265,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G824" t="n">
-        <v>9.97981452941895</v>
+        <v>9.97981357574463</v>
       </c>
       <c r="H824" t="n">
         <v>11779</v>
@@ -24294,7 +24294,7 @@
         <v>10.9200000762939</v>
       </c>
       <c r="G825" t="n">
-        <v>9.87133979797363</v>
+        <v>9.87133884429932</v>
       </c>
       <c r="H825" t="n">
         <v>15736</v>
@@ -24352,7 +24352,7 @@
         <v>11.2200002670288</v>
       </c>
       <c r="G827" t="n">
-        <v>10.1425294876099</v>
+        <v>10.1425304412842</v>
       </c>
       <c r="H827" t="n">
         <v>6100</v>
@@ -24381,7 +24381,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G828" t="n">
-        <v>9.97981452941895</v>
+        <v>9.97981357574463</v>
       </c>
       <c r="H828" t="n">
         <v>9050</v>
@@ -24439,7 +24439,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G830" t="n">
-        <v>10.052131652832</v>
+        <v>10.0521326065063</v>
       </c>
       <c r="H830" t="n">
         <v>3659</v>
@@ -24497,7 +24497,7 @@
         <v>11.3599996566772</v>
       </c>
       <c r="G832" t="n">
-        <v>10.2690839767456</v>
+        <v>10.2690849304199</v>
       </c>
       <c r="H832" t="n">
         <v>2890</v>
@@ -24526,7 +24526,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G833" t="n">
-        <v>10.3052444458008</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H833" t="n">
         <v>1557</v>
@@ -24613,7 +24613,7 @@
         <v>11.1599998474121</v>
       </c>
       <c r="G836" t="n">
-        <v>10.0882921218872</v>
+        <v>10.0882911682129</v>
       </c>
       <c r="H836" t="n">
         <v>23721</v>
@@ -24642,7 +24642,7 @@
         <v>11.2799997329712</v>
       </c>
       <c r="G837" t="n">
-        <v>10.1967678070068</v>
+        <v>10.1967668533325</v>
       </c>
       <c r="H837" t="n">
         <v>21834</v>
@@ -24671,7 +24671,7 @@
         <v>11.3800001144409</v>
       </c>
       <c r="G838" t="n">
-        <v>10.2871646881104</v>
+        <v>10.2871656417847</v>
       </c>
       <c r="H838" t="n">
         <v>8300</v>
@@ -24729,7 +24729,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G840" t="n">
-        <v>10.4860372543335</v>
+        <v>10.4860382080078</v>
       </c>
       <c r="H840" t="n">
         <v>16132</v>
@@ -24758,7 +24758,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G841" t="n">
-        <v>10.757227897644</v>
+        <v>10.7572269439697</v>
       </c>
       <c r="H841" t="n">
         <v>45778</v>
@@ -24816,7 +24816,7 @@
         <v>11.7600002288818</v>
       </c>
       <c r="G843" t="n">
-        <v>10.6306734085083</v>
+        <v>10.630672454834</v>
       </c>
       <c r="H843" t="n">
         <v>1266</v>
@@ -24874,7 +24874,7 @@
         <v>12.1000003814697</v>
       </c>
       <c r="G845" t="n">
-        <v>10.9380216598511</v>
+        <v>10.9380226135254</v>
       </c>
       <c r="H845" t="n">
         <v>42170</v>
@@ -24932,7 +24932,7 @@
         <v>11.9399995803833</v>
       </c>
       <c r="G847" t="n">
-        <v>10.7933864593506</v>
+        <v>10.7933883666992</v>
       </c>
       <c r="H847" t="n">
         <v>2716</v>
@@ -24990,7 +24990,7 @@
         <v>11.7799997329712</v>
       </c>
       <c r="G849" t="n">
-        <v>10.6487522125244</v>
+        <v>10.6487512588501</v>
       </c>
       <c r="H849" t="n">
         <v>10824</v>
@@ -25193,7 +25193,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G856" t="n">
-        <v>10.3052444458008</v>
+        <v>10.3052434921265</v>
       </c>
       <c r="H856" t="n">
         <v>4772</v>
@@ -25280,7 +25280,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G859" t="n">
-        <v>11.1786937713623</v>
+        <v>11.178692817688</v>
       </c>
       <c r="H859" t="n">
         <v>14303</v>
@@ -25309,7 +25309,7 @@
         <v>12.039999961853</v>
       </c>
       <c r="G860" t="n">
-        <v>11.0502023696899</v>
+        <v>11.0502033233643</v>
       </c>
       <c r="H860" t="n">
         <v>11580</v>
@@ -25338,7 +25338,7 @@
         <v>12</v>
       </c>
       <c r="G861" t="n">
-        <v>11.0134916305542</v>
+        <v>11.0134925842285</v>
       </c>
       <c r="H861" t="n">
         <v>7434</v>
@@ -25367,7 +25367,7 @@
         <v>12</v>
       </c>
       <c r="G862" t="n">
-        <v>11.0134916305542</v>
+        <v>11.0134925842285</v>
       </c>
       <c r="H862" t="n">
         <v>15943</v>
@@ -25396,7 +25396,7 @@
         <v>12</v>
       </c>
       <c r="G863" t="n">
-        <v>11.0134916305542</v>
+        <v>11.0134925842285</v>
       </c>
       <c r="H863" t="n">
         <v>4501</v>
@@ -25483,7 +25483,7 @@
         <v>12.1800003051758</v>
       </c>
       <c r="G866" t="n">
-        <v>11.1786937713623</v>
+        <v>11.178692817688</v>
       </c>
       <c r="H866" t="n">
         <v>16654</v>
@@ -25512,7 +25512,7 @@
         <v>11.9200000762939</v>
       </c>
       <c r="G867" t="n">
-        <v>10.9400663375854</v>
+        <v>10.9400672912598</v>
       </c>
       <c r="H867" t="n">
         <v>14896</v>
@@ -25570,7 +25570,7 @@
         <v>11.7200002670288</v>
       </c>
       <c r="G869" t="n">
-        <v>10.7565116882324</v>
+        <v>10.7565107345581</v>
       </c>
       <c r="H869" t="n">
         <v>8550</v>
@@ -25599,7 +25599,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>10.6463747024536</v>
+        <v>10.6463756561279</v>
       </c>
       <c r="H870" t="n">
         <v>10072</v>
@@ -25628,7 +25628,7 @@
         <v>11.7399997711182</v>
       </c>
       <c r="G871" t="n">
-        <v>10.7748641967773</v>
+        <v>10.7748651504517</v>
       </c>
       <c r="H871" t="n">
         <v>5570</v>
@@ -25686,7 +25686,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G873" t="n">
-        <v>10.5913057327271</v>
+        <v>10.5913066864014</v>
       </c>
       <c r="H873" t="n">
         <v>6868</v>
@@ -25744,7 +25744,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G875" t="n">
-        <v>10.7014436721802</v>
+        <v>10.7014427185059</v>
       </c>
       <c r="H875" t="n">
         <v>4362</v>
@@ -25773,7 +25773,7 @@
         <v>11.539999961853</v>
       </c>
       <c r="G876" t="n">
-        <v>10.5913057327271</v>
+        <v>10.5913066864014</v>
       </c>
       <c r="H876" t="n">
         <v>7097</v>
@@ -25889,7 +25889,7 @@
         <v>11.4799995422363</v>
       </c>
       <c r="G880" t="n">
-        <v>10.5362396240234</v>
+        <v>10.5362405776978</v>
       </c>
       <c r="H880" t="n">
         <v>1976</v>
@@ -25918,7 +25918,7 @@
         <v>11.6599998474121</v>
       </c>
       <c r="G881" t="n">
-        <v>10.7014436721802</v>
+        <v>10.7014427185059</v>
       </c>
       <c r="H881" t="n">
         <v>1323</v>
@@ -25947,7 +25947,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>10.6463747024536</v>
+        <v>10.6463756561279</v>
       </c>
       <c r="H882" t="n">
         <v>1450</v>
@@ -26034,7 +26034,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G885" t="n">
-        <v>10.2058343887329</v>
+        <v>10.2058353424072</v>
       </c>
       <c r="H885" t="n">
         <v>10713</v>
@@ -26092,7 +26092,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G887" t="n">
-        <v>10.1874799728394</v>
+        <v>10.187479019165</v>
       </c>
       <c r="H887" t="n">
         <v>24059</v>
@@ -26208,7 +26208,7 @@
         <v>11.1800003051758</v>
       </c>
       <c r="G891" t="n">
-        <v>10.2609024047852</v>
+        <v>10.2609033584595</v>
       </c>
       <c r="H891" t="n">
         <v>10764</v>
@@ -26324,7 +26324,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G895" t="n">
-        <v>10.0039196014404</v>
+        <v>10.0039205551147</v>
       </c>
       <c r="H895" t="n">
         <v>10077</v>
@@ -26411,7 +26411,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G898" t="n">
-        <v>10.0039196014404</v>
+        <v>10.0039205551147</v>
       </c>
       <c r="H898" t="n">
         <v>46793</v>
@@ -26556,7 +26556,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G903" t="n">
-        <v>9.8937873840332</v>
+        <v>9.89378643035889</v>
       </c>
       <c r="H903" t="n">
         <v>8672</v>
@@ -26585,7 +26585,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G904" t="n">
-        <v>9.8937873840332</v>
+        <v>9.89378643035889</v>
       </c>
       <c r="H904" t="n">
         <v>2981</v>
@@ -26701,7 +26701,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G908" t="n">
-        <v>10.0773448944092</v>
+        <v>10.0773439407349</v>
       </c>
       <c r="H908" t="n">
         <v>24875</v>
@@ -26817,7 +26817,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G912" t="n">
-        <v>9.94885349273682</v>
+        <v>9.9488525390625</v>
       </c>
       <c r="H912" t="n">
         <v>24470</v>
@@ -26846,7 +26846,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G913" t="n">
-        <v>9.83871841430664</v>
+        <v>9.83871936798096</v>
       </c>
       <c r="H913" t="n">
         <v>1982</v>
@@ -26904,7 +26904,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G915" t="n">
-        <v>9.8937873840332</v>
+        <v>9.89378643035889</v>
       </c>
       <c r="H915" t="n">
         <v>2171</v>
@@ -26962,7 +26962,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G917" t="n">
-        <v>10.2058343887329</v>
+        <v>10.2058353424072</v>
       </c>
       <c r="H917" t="n">
         <v>15367</v>
@@ -27107,7 +27107,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G922" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H922" t="n">
         <v>4917</v>
@@ -27252,7 +27252,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G927" t="n">
-        <v>9.39818000793457</v>
+        <v>9.39817905426025</v>
       </c>
       <c r="H927" t="n">
         <v>11222</v>
@@ -27368,7 +27368,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G931" t="n">
-        <v>9.39818000793457</v>
+        <v>9.39817905426025</v>
       </c>
       <c r="H931" t="n">
         <v>9623</v>
@@ -27397,7 +27397,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G932" t="n">
-        <v>9.28804397583008</v>
+        <v>9.28804492950439</v>
       </c>
       <c r="H932" t="n">
         <v>26076</v>
@@ -27426,7 +27426,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G933" t="n">
-        <v>9.39818000793457</v>
+        <v>9.39817905426025</v>
       </c>
       <c r="H933" t="n">
         <v>5505</v>
@@ -27484,7 +27484,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G935" t="n">
-        <v>9.52667045593262</v>
+        <v>9.52667140960693</v>
       </c>
       <c r="H935" t="n">
         <v>23088</v>
@@ -27571,7 +27571,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G938" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844730377197</v>
       </c>
       <c r="H938" t="n">
         <v>21054</v>
@@ -27629,7 +27629,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G940" t="n">
-        <v>9.83871841430664</v>
+        <v>9.83871936798096</v>
       </c>
       <c r="H940" t="n">
         <v>8612</v>
@@ -27716,7 +27716,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G943" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H943" t="n">
         <v>39728</v>
@@ -27832,7 +27832,7 @@
         <v>10.7200002670288</v>
       </c>
       <c r="G947" t="n">
-        <v>9.83871841430664</v>
+        <v>9.83871936798096</v>
       </c>
       <c r="H947" t="n">
         <v>5228</v>
@@ -27948,7 +27948,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G951" t="n">
-        <v>9.71022796630859</v>
+        <v>9.71022701263428</v>
       </c>
       <c r="H951" t="n">
         <v>204</v>
@@ -28093,7 +28093,7 @@
         <v>10.8199996948242</v>
       </c>
       <c r="G956" t="n">
-        <v>9.93049716949463</v>
+        <v>9.93049812316895</v>
       </c>
       <c r="H956" t="n">
         <v>3876</v>
@@ -28267,7 +28267,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G962" t="n">
-        <v>9.8937873840332</v>
+        <v>9.89378643035889</v>
       </c>
       <c r="H962" t="n">
         <v>4406</v>
@@ -28412,7 +28412,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G967" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844730377197</v>
       </c>
       <c r="H967" t="n">
         <v>6277</v>
@@ -28441,7 +28441,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G968" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H968" t="n">
         <v>8417</v>
@@ -28470,7 +28470,7 @@
         <v>10.5799999237061</v>
       </c>
       <c r="G969" t="n">
-        <v>9.71022796630859</v>
+        <v>9.71022701263428</v>
       </c>
       <c r="H969" t="n">
         <v>9842</v>
@@ -28557,7 +28557,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G972" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H972" t="n">
         <v>12848</v>
@@ -28702,7 +28702,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G977" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H977" t="n">
         <v>1002</v>
@@ -28847,7 +28847,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844730377197</v>
       </c>
       <c r="H982" t="n">
         <v>13221</v>
@@ -28905,7 +28905,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G984" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844730377197</v>
       </c>
       <c r="H984" t="n">
         <v>32880</v>
@@ -28963,7 +28963,7 @@
         <v>10.3599996566772</v>
       </c>
       <c r="G986" t="n">
-        <v>9.50831317901611</v>
+        <v>9.5083122253418</v>
       </c>
       <c r="H986" t="n">
         <v>19204</v>
@@ -28992,7 +28992,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G987" t="n">
-        <v>9.52667045593262</v>
+        <v>9.52667140960693</v>
       </c>
       <c r="H987" t="n">
         <v>21603</v>
@@ -29079,7 +29079,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G990" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H990" t="n">
         <v>8914</v>
@@ -29340,7 +29340,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G999" t="n">
-        <v>10.1691226959229</v>
+        <v>10.1691236495972</v>
       </c>
       <c r="H999" t="n">
         <v>15576</v>
@@ -29369,7 +29369,7 @@
         <v>10.9799995422363</v>
       </c>
       <c r="G1000" t="n">
-        <v>10.0773448944092</v>
+        <v>10.0773439407349</v>
       </c>
       <c r="H1000" t="n">
         <v>13423</v>
@@ -29398,7 +29398,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1001" t="n">
-        <v>10.1324119567871</v>
+        <v>10.1324110031128</v>
       </c>
       <c r="H1001" t="n">
         <v>10832</v>
@@ -29456,7 +29456,7 @@
         <v>11.039999961853</v>
       </c>
       <c r="G1003" t="n">
-        <v>10.1324119567871</v>
+        <v>10.1324110031128</v>
       </c>
       <c r="H1003" t="n">
         <v>13007</v>
@@ -29485,7 +29485,7 @@
         <v>11.1199998855591</v>
       </c>
       <c r="G1004" t="n">
-        <v>10.2058343887329</v>
+        <v>10.2058353424072</v>
       </c>
       <c r="H1004" t="n">
         <v>11025</v>
@@ -29543,7 +29543,7 @@
         <v>10.7799997329712</v>
       </c>
       <c r="G1006" t="n">
-        <v>9.8937873840332</v>
+        <v>9.89378643035889</v>
       </c>
       <c r="H1006" t="n">
         <v>22883</v>
@@ -29630,7 +29630,7 @@
         <v>11.0799999237061</v>
       </c>
       <c r="G1009" t="n">
-        <v>10.1691226959229</v>
+        <v>10.1691236495972</v>
       </c>
       <c r="H1009" t="n">
         <v>14777</v>
@@ -29688,7 +29688,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1011" t="n">
-        <v>10.0039196014404</v>
+        <v>10.0039205551147</v>
       </c>
       <c r="H1011" t="n">
         <v>45476</v>
@@ -29717,7 +29717,7 @@
         <v>10.8400001525879</v>
       </c>
       <c r="G1012" t="n">
-        <v>9.94885349273682</v>
+        <v>9.9488525390625</v>
       </c>
       <c r="H1012" t="n">
         <v>14824</v>
@@ -29775,7 +29775,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="G1014" t="n">
-        <v>9.76529598236084</v>
+        <v>9.76529693603516</v>
       </c>
       <c r="H1014" t="n">
         <v>20334</v>
@@ -29891,7 +29891,7 @@
         <v>10.2399997711182</v>
       </c>
       <c r="G1018" t="n">
-        <v>9.39818000793457</v>
+        <v>9.39817905426025</v>
       </c>
       <c r="H1018" t="n">
         <v>38434</v>
@@ -30007,7 +30007,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1022" t="n">
-        <v>9.52667045593262</v>
+        <v>9.52667140960693</v>
       </c>
       <c r="H1022" t="n">
         <v>11887</v>
@@ -30094,7 +30094,7 @@
         <v>10.4399995803833</v>
       </c>
       <c r="G1025" t="n">
-        <v>9.58173656463623</v>
+        <v>9.58173751831055</v>
       </c>
       <c r="H1025" t="n">
         <v>33288</v>
@@ -30239,7 +30239,7 @@
         <v>10.4799995422363</v>
       </c>
       <c r="G1030" t="n">
-        <v>9.61844825744629</v>
+        <v>9.61844730377197</v>
       </c>
       <c r="H1030" t="n">
         <v>97562</v>
@@ -30268,7 +30268,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1031" t="n">
-        <v>9.52667045593262</v>
+        <v>9.52667140960693</v>
       </c>
       <c r="H1031" t="n">
         <v>8157</v>
@@ -30297,7 +30297,7 @@
         <v>10.3800001144409</v>
       </c>
       <c r="G1032" t="n">
-        <v>9.52667045593262</v>
+        <v>9.52667140960693</v>
       </c>
       <c r="H1032" t="n">
         <v>23518</v>
@@ -30326,7 +30326,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G1033" t="n">
-        <v>9.36146640777588</v>
+        <v>9.3614673614502</v>
       </c>
       <c r="H1033" t="n">
         <v>18579</v>
@@ -30384,7 +30384,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>9.32475566864014</v>
+        <v>9.32475471496582</v>
       </c>
       <c r="H1035" t="n">
         <v>13711</v>
@@ -30413,7 +30413,7 @@
         <v>10</v>
       </c>
       <c r="G1036" t="n">
-        <v>9.17790794372559</v>
+        <v>9.1779088973999</v>
       </c>
       <c r="H1036" t="n">
         <v>63272</v>
@@ -30442,7 +30442,7 @@
         <v>9.80000019073486</v>
       </c>
       <c r="G1037" t="n">
-        <v>8.99435138702393</v>
+        <v>8.99435234069824</v>
       </c>
       <c r="H1037" t="n">
         <v>182782</v>
@@ -30500,7 +30500,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>9.25133228302002</v>
+        <v>9.25133323669434</v>
       </c>
       <c r="H1039" t="n">
         <v>20536</v>
@@ -30529,7 +30529,7 @@
         <v>10.1199998855591</v>
       </c>
       <c r="G1040" t="n">
-        <v>9.28804397583008</v>
+        <v>9.28804492950439</v>
       </c>
       <c r="H1040" t="n">
         <v>15887</v>
@@ -30558,7 +30558,7 @@
         <v>10</v>
       </c>
       <c r="G1041" t="n">
-        <v>9.17790794372559</v>
+        <v>9.1779088973999</v>
       </c>
       <c r="H1041" t="n">
         <v>52588</v>
@@ -30587,7 +30587,7 @@
         <v>10.039999961853</v>
       </c>
       <c r="G1042" t="n">
-        <v>9.21462154388428</v>
+        <v>9.21462059020996</v>
       </c>
       <c r="H1042" t="n">
         <v>34966</v>
@@ -30616,7 +30616,7 @@
         <v>10.0200004577637</v>
       </c>
       <c r="G1043" t="n">
-        <v>9.19626426696777</v>
+        <v>9.19626617431641</v>
       </c>
       <c r="H1043" t="n">
         <v>7574</v>
@@ -30645,7 +30645,7 @@
         <v>10</v>
       </c>
       <c r="G1044" t="n">
-        <v>9.17790794372559</v>
+        <v>9.1779088973999</v>
       </c>
       <c r="H1044" t="n">
         <v>54355</v>
@@ -30674,7 +30674,7 @@
         <v>10.0799999237061</v>
       </c>
       <c r="G1045" t="n">
-        <v>9.25133228302002</v>
+        <v>9.25133323669434</v>
       </c>
       <c r="H1045" t="n">
         <v>20501</v>
@@ -30732,7 +30732,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G1047" t="n">
-        <v>9.15955257415771</v>
+        <v>9.15955352783203</v>
       </c>
       <c r="H1047" t="n">
         <v>53010</v>
@@ -30906,7 +30906,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G1053" t="n">
-        <v>8.95763969421387</v>
+        <v>8.95764064788818</v>
       </c>
       <c r="H1053" t="n">
         <v>104412</v>
@@ -30993,7 +30993,7 @@
         <v>9.6899995803833</v>
       </c>
       <c r="G1056" t="n">
-        <v>8.89339447021484</v>
+        <v>8.89339351654053</v>
       </c>
       <c r="H1056" t="n">
         <v>42175</v>
@@ -31051,7 +31051,7 @@
         <v>9.31999969482422</v>
       </c>
       <c r="G1058" t="n">
-        <v>8.55381202697754</v>
+        <v>8.55381107330322</v>
       </c>
       <c r="H1058" t="n">
         <v>39327</v>
@@ -31138,7 +31138,7 @@
         <v>9.01000022888184</v>
       </c>
       <c r="G1061" t="n">
-        <v>8.26929664611816</v>
+        <v>8.26929569244385</v>
       </c>
       <c r="H1061" t="n">
         <v>66806</v>
@@ -31225,7 +31225,7 @@
         <v>8.44999980926514</v>
       </c>
       <c r="G1064" t="n">
-        <v>7.7553334236145</v>
+        <v>7.75533246994019</v>
       </c>
       <c r="H1064" t="n">
         <v>54217</v>
@@ -31283,7 +31283,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G1066" t="n">
-        <v>7.43410730361938</v>
+        <v>7.43410682678223</v>
       </c>
       <c r="H1066" t="n">
         <v>111498</v>
@@ -31312,7 +31312,7 @@
         <v>8.5</v>
       </c>
       <c r="G1067" t="n">
-        <v>7.80122327804565</v>
+        <v>7.80122184753418</v>
       </c>
       <c r="H1067" t="n">
         <v>78080</v>
@@ -31399,7 +31399,7 @@
         <v>8.5</v>
       </c>
       <c r="G1070" t="n">
-        <v>7.80122327804565</v>
+        <v>7.80122184753418</v>
       </c>
       <c r="H1070" t="n">
         <v>116366</v>
@@ -31631,7 +31631,7 @@
         <v>9.86999988555908</v>
       </c>
       <c r="G1078" t="n">
-        <v>9.05859756469727</v>
+        <v>9.05859661102295</v>
       </c>
       <c r="H1078" t="n">
         <v>123632</v>
@@ -31660,7 +31660,7 @@
         <v>9.82999992370605</v>
       </c>
       <c r="G1079" t="n">
-        <v>9.02188396453857</v>
+        <v>9.02188491821289</v>
       </c>
       <c r="H1079" t="n">
         <v>54346</v>
@@ -31979,7 +31979,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1090" t="n">
-        <v>9.14119720458984</v>
+        <v>9.14119625091553</v>
       </c>
       <c r="H1090" t="n">
         <v>13430</v>
@@ -32037,7 +32037,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G1092" t="n">
-        <v>9.14119720458984</v>
+        <v>9.14119625091553</v>
       </c>
       <c r="H1092" t="n">
         <v>11127</v>
@@ -32066,7 +32066,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1093" t="n">
-        <v>9.1044864654541</v>
+        <v>9.10448551177979</v>
       </c>
       <c r="H1093" t="n">
         <v>20767</v>
@@ -32124,7 +32124,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G1095" t="n">
-        <v>9.1044864654541</v>
+        <v>9.10448551177979</v>
       </c>
       <c r="H1095" t="n">
         <v>16121</v>
@@ -32298,7 +32298,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G1101" t="n">
-        <v>8.82914924621582</v>
+        <v>8.8291482925415</v>
       </c>
       <c r="H1101" t="n">
         <v>13070</v>
@@ -32356,7 +32356,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G1103" t="n">
-        <v>8.68230152130127</v>
+        <v>8.68230247497559</v>
       </c>
       <c r="H1103" t="n">
         <v>19266</v>
@@ -32501,7 +32501,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G1108" t="n">
-        <v>8.57216644287109</v>
+        <v>8.57216739654541</v>
       </c>
       <c r="H1108" t="n">
         <v>17767</v>
@@ -32530,7 +32530,7 @@
         <v>9.42000007629395</v>
       </c>
       <c r="G1109" t="n">
-        <v>8.64559078216553</v>
+        <v>8.64558982849121</v>
       </c>
       <c r="H1109" t="n">
         <v>22137</v>
@@ -32820,7 +32820,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G1119" t="n">
-        <v>9.66937160491943</v>
+        <v>9.66937255859375</v>
       </c>
       <c r="H1119" t="n">
         <v>36736</v>
@@ -32994,7 +32994,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1125" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1125" t="n">
         <v>67968</v>
@@ -33023,7 +33023,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1126" t="n">
-        <v>10.3700513839722</v>
+        <v>10.3700504302979</v>
       </c>
       <c r="H1126" t="n">
         <v>28484</v>
@@ -33110,7 +33110,7 @@
         <v>10.75</v>
       </c>
       <c r="G1129" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1129" t="n">
         <v>76685</v>
@@ -33284,7 +33284,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1135" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1135" t="n">
         <v>35971</v>
@@ -33313,7 +33313,7 @@
         <v>10.75</v>
       </c>
       <c r="G1136" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1136" t="n">
         <v>20678</v>
@@ -33342,7 +33342,7 @@
         <v>10.75</v>
       </c>
       <c r="G1137" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1137" t="n">
         <v>24865</v>
@@ -33603,7 +33603,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1146" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1146" t="n">
         <v>47994</v>
@@ -33632,7 +33632,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1147" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1147" t="n">
         <v>8123</v>
@@ -33777,7 +33777,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1152" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1152" t="n">
         <v>32453</v>
@@ -33806,7 +33806,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1153" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1153" t="n">
         <v>7823</v>
@@ -33864,7 +33864,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1155" t="n">
-        <v>10.3700513839722</v>
+        <v>10.3700504302979</v>
       </c>
       <c r="H1155" t="n">
         <v>31838</v>
@@ -33893,7 +33893,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1156" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1156" t="n">
         <v>30170</v>
@@ -33980,7 +33980,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1159" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1159" t="n">
         <v>8839</v>
@@ -34009,7 +34009,7 @@
         <v>10.75</v>
       </c>
       <c r="G1160" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1160" t="n">
         <v>7697</v>
@@ -34038,7 +34038,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1161" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1161" t="n">
         <v>4942</v>
@@ -34125,7 +34125,7 @@
         <v>10.75</v>
       </c>
       <c r="G1164" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1164" t="n">
         <v>9176</v>
@@ -34154,7 +34154,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1165" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1165" t="n">
         <v>14879</v>
@@ -34183,7 +34183,7 @@
         <v>10.75</v>
       </c>
       <c r="G1166" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1166" t="n">
         <v>17323</v>
@@ -34299,7 +34299,7 @@
         <v>10.75</v>
       </c>
       <c r="G1170" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1170" t="n">
         <v>10452</v>
@@ -34328,7 +34328,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1171" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1171" t="n">
         <v>13532</v>
@@ -34357,7 +34357,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1172" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1172" t="n">
         <v>3617</v>
@@ -34386,7 +34386,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1173" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1173" t="n">
         <v>20073</v>
@@ -34444,7 +34444,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1175" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1175" t="n">
         <v>9765</v>
@@ -34473,7 +34473,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1176" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1176" t="n">
         <v>7711</v>
@@ -34502,7 +34502,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1177" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1177" t="n">
         <v>10175</v>
@@ -34531,7 +34531,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1178" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1178" t="n">
         <v>4342</v>
@@ -34560,7 +34560,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1179" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1179" t="n">
         <v>7541</v>
@@ -34589,7 +34589,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G1180" t="n">
-        <v>10.4167633056641</v>
+        <v>10.4167623519897</v>
       </c>
       <c r="H1180" t="n">
         <v>27377</v>
@@ -34618,7 +34618,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1181" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1181" t="n">
         <v>25010</v>
@@ -34647,7 +34647,7 @@
         <v>11.1000003814697</v>
       </c>
       <c r="G1182" t="n">
-        <v>10.3700513839722</v>
+        <v>10.3700504302979</v>
       </c>
       <c r="H1182" t="n">
         <v>28161</v>
@@ -34850,7 +34850,7 @@
         <v>10.75</v>
       </c>
       <c r="G1189" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1189" t="n">
         <v>11792</v>
@@ -34908,7 +34908,7 @@
         <v>10.75</v>
       </c>
       <c r="G1191" t="n">
-        <v>10.0430669784546</v>
+        <v>10.0430679321289</v>
       </c>
       <c r="H1191" t="n">
         <v>13063</v>
@@ -34966,7 +34966,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G1193" t="n">
-        <v>10.183201789856</v>
+        <v>10.1832027435303</v>
       </c>
       <c r="H1193" t="n">
         <v>98337</v>
@@ -34995,7 +34995,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G1194" t="n">
-        <v>10.2299146652222</v>
+        <v>10.2299137115479</v>
       </c>
       <c r="H1194" t="n">
         <v>259092</v>
@@ -35111,7 +35111,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>11.1174421310425</v>
+        <v>11.1174411773682</v>
       </c>
       <c r="H1198" t="n">
         <v>103624</v>
@@ -35140,7 +35140,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1199" t="n">
-        <v>11.0707302093506</v>
+        <v>11.0707311630249</v>
       </c>
       <c r="H1199" t="n">
         <v>93015</v>
@@ -35285,7 +35285,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1204" t="n">
-        <v>10.6970338821411</v>
+        <v>10.6970348358154</v>
       </c>
       <c r="H1204" t="n">
         <v>26462</v>
@@ -35372,7 +35372,7 @@
         <v>11.8500003814697</v>
       </c>
       <c r="G1207" t="n">
-        <v>11.0707302093506</v>
+        <v>11.0707311630249</v>
       </c>
       <c r="H1207" t="n">
         <v>6674</v>
@@ -35517,7 +35517,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1212" t="n">
-        <v>10.8371706008911</v>
+        <v>10.8371715545654</v>
       </c>
       <c r="H1212" t="n">
         <v>108728</v>
@@ -35662,7 +35662,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1217" t="n">
-        <v>10.6970338821411</v>
+        <v>10.6970348358154</v>
       </c>
       <c r="H1217" t="n">
         <v>16353</v>
@@ -35691,7 +35691,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1218" t="n">
-        <v>10.7904567718506</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1218" t="n">
         <v>32050</v>
@@ -35749,7 +35749,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1220" t="n">
-        <v>10.7904567718506</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1220" t="n">
         <v>10357</v>
@@ -35778,7 +35778,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1221" t="n">
-        <v>10.7904567718506</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1221" t="n">
         <v>46127</v>
@@ -35807,7 +35807,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1222" t="n">
-        <v>10.7904567718506</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1222" t="n">
         <v>30407</v>
@@ -35865,7 +35865,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1224" t="n">
-        <v>10.8371706008911</v>
+        <v>10.8371715545654</v>
       </c>
       <c r="H1224" t="n">
         <v>15413</v>
@@ -35894,7 +35894,7 @@
         <v>11.4499998092651</v>
       </c>
       <c r="G1225" t="n">
-        <v>10.6970338821411</v>
+        <v>10.6970348358154</v>
       </c>
       <c r="H1225" t="n">
         <v>18947</v>
@@ -36010,7 +36010,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1229" t="n">
-        <v>10.5568981170654</v>
+        <v>10.5568990707397</v>
       </c>
       <c r="H1229" t="n">
         <v>68396</v>
@@ -36068,7 +36068,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1231" t="n">
-        <v>10.5568981170654</v>
+        <v>10.5568990707397</v>
       </c>
       <c r="H1231" t="n">
         <v>45171</v>
@@ -36097,7 +36097,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G1232" t="n">
-        <v>10.5568981170654</v>
+        <v>10.5568990707397</v>
       </c>
       <c r="H1232" t="n">
         <v>27148</v>
@@ -36184,7 +36184,7 @@
         <v>11.5500001907349</v>
       </c>
       <c r="G1235" t="n">
-        <v>10.7904567718506</v>
+        <v>10.7904577255249</v>
       </c>
       <c r="H1235" t="n">
         <v>130559</v>
@@ -36213,7 +36213,7 @@
         <v>11.6000003814697</v>
       </c>
       <c r="G1236" t="n">
-        <v>10.8371706008911</v>
+        <v>10.8371715545654</v>
       </c>
       <c r="H1236" t="n">
         <v>65487</v>
@@ -36271,7 +36271,7 @@
         <v>12.25</v>
       </c>
       <c r="G1238" t="n">
-        <v>11.4444255828857</v>
+        <v>11.4444246292114</v>
       </c>
       <c r="H1238" t="n">
         <v>109803</v>
@@ -36300,7 +36300,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>11.5378503799438</v>
+        <v>11.5378494262695</v>
       </c>
       <c r="H1239" t="n">
         <v>77544</v>
@@ -36329,7 +36329,7 @@
         <v>12.5</v>
       </c>
       <c r="G1240" t="n">
-        <v>11.6779851913452</v>
+        <v>11.6779842376709</v>
       </c>
       <c r="H1240" t="n">
         <v>60992</v>
@@ -36358,7 +36358,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G1241" t="n">
-        <v>11.5378503799438</v>
+        <v>11.5378494262695</v>
       </c>
       <c r="H1241" t="n">
         <v>42735</v>
@@ -36445,7 +36445,7 @@
         <v>12.5</v>
       </c>
       <c r="G1244" t="n">
-        <v>11.6779851913452</v>
+        <v>11.6779842376709</v>
       </c>
       <c r="H1244" t="n">
         <v>22267</v>
@@ -36503,7 +36503,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1246" t="n">
-        <v>11.6312742233276</v>
+        <v>11.631272315979</v>
       </c>
       <c r="H1246" t="n">
         <v>74739</v>
@@ -36561,7 +36561,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G1248" t="n">
-        <v>11.6312742233276</v>
+        <v>11.631272315979</v>
       </c>
       <c r="H1248" t="n">
         <v>16479</v>
@@ -36590,7 +36590,7 @@
         <v>12.5</v>
       </c>
       <c r="G1249" t="n">
-        <v>11.6779851913452</v>
+        <v>11.6779842376709</v>
       </c>
       <c r="H1249" t="n">
         <v>53331</v>
@@ -36793,7 +36793,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1256" t="n">
-        <v>12.799072265625</v>
+        <v>12.7990713119507</v>
       </c>
       <c r="H1256" t="n">
         <v>47612</v>
@@ -36822,7 +36822,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1257" t="n">
-        <v>12.6589365005493</v>
+        <v>12.658935546875</v>
       </c>
       <c r="H1257" t="n">
         <v>54197</v>
@@ -36851,7 +36851,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1258" t="n">
-        <v>12.6589365005493</v>
+        <v>12.658935546875</v>
       </c>
       <c r="H1258" t="n">
         <v>57779</v>
@@ -36909,7 +36909,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>12.518798828125</v>
+        <v>12.5187997817993</v>
       </c>
       <c r="H1260" t="n">
         <v>19578</v>
@@ -36938,7 +36938,7 @@
         <v>13.3999996185303</v>
       </c>
       <c r="G1261" t="n">
-        <v>12.518798828125</v>
+        <v>12.5187997817993</v>
       </c>
       <c r="H1261" t="n">
         <v>143329</v>
@@ -36996,7 +36996,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1263" t="n">
-        <v>12.7056484222412</v>
+        <v>12.7056474685669</v>
       </c>
       <c r="H1263" t="n">
         <v>85655</v>
@@ -37025,7 +37025,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1264" t="n">
-        <v>12.7523612976074</v>
+        <v>12.7523603439331</v>
       </c>
       <c r="H1264" t="n">
         <v>99561</v>
@@ -37054,7 +37054,7 @@
         <v>13.5500001907349</v>
       </c>
       <c r="G1265" t="n">
-        <v>12.6589365005493</v>
+        <v>12.658935546875</v>
       </c>
       <c r="H1265" t="n">
         <v>33917</v>
@@ -37083,7 +37083,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1266" t="n">
-        <v>12.7056484222412</v>
+        <v>12.7056474685669</v>
       </c>
       <c r="H1266" t="n">
         <v>26225</v>
@@ -37112,7 +37112,7 @@
         <v>13.6499996185303</v>
       </c>
       <c r="G1267" t="n">
-        <v>12.7523612976074</v>
+        <v>12.7523603439331</v>
       </c>
       <c r="H1267" t="n">
         <v>24915</v>
@@ -37141,7 +37141,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G1268" t="n">
-        <v>12.8924961090088</v>
+        <v>12.8924951553345</v>
       </c>
       <c r="H1268" t="n">
         <v>26997</v>
@@ -37170,7 +37170,7 @@
         <v>13.6999998092651</v>
       </c>
       <c r="G1269" t="n">
-        <v>12.799072265625</v>
+        <v>12.7990713119507</v>
       </c>
       <c r="H1269" t="n">
         <v>27520</v>
@@ -37199,7 +37199,7 @@
         <v>14</v>
       </c>
       <c r="G1270" t="n">
-        <v>13.0793428421021</v>
+        <v>13.0793418884277</v>
       </c>
       <c r="H1270" t="n">
         <v>29015</v>
@@ -37257,7 +37257,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1272" t="n">
-        <v>13.7333097457886</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1272" t="n">
         <v>66362</v>
@@ -37286,7 +37286,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1273" t="n">
-        <v>13.6398868560791</v>
+        <v>13.6398878097534</v>
       </c>
       <c r="H1273" t="n">
         <v>50997</v>
@@ -37315,7 +37315,7 @@
         <v>14.5</v>
       </c>
       <c r="G1274" t="n">
-        <v>13.5464630126953</v>
+        <v>13.5464639663696</v>
       </c>
       <c r="H1274" t="n">
         <v>42667</v>
@@ -37402,7 +37402,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1277" t="n">
-        <v>13.7333097457886</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1277" t="n">
         <v>44773</v>
@@ -37431,7 +37431,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G1278" t="n">
-        <v>13.7333097457886</v>
+        <v>13.7333106994629</v>
       </c>
       <c r="H1278" t="n">
         <v>25963</v>
@@ -37489,7 +37489,7 @@
         <v>14.5</v>
       </c>
       <c r="G1280" t="n">
-        <v>13.5464630126953</v>
+        <v>13.5464639663696</v>
       </c>
       <c r="H1280" t="n">
         <v>38339</v>
@@ -37518,7 +37518,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1281" t="n">
-        <v>13.6398868560791</v>
+        <v>13.6398878097534</v>
       </c>
       <c r="H1281" t="n">
         <v>11818</v>
@@ -37547,7 +37547,7 @@
         <v>14.75</v>
       </c>
       <c r="G1282" t="n">
-        <v>13.7800216674805</v>
+        <v>13.7800226211548</v>
       </c>
       <c r="H1282" t="n">
         <v>46705</v>
@@ -37692,7 +37692,7 @@
         <v>14.75</v>
       </c>
       <c r="G1287" t="n">
-        <v>13.7800216674805</v>
+        <v>13.7800226211548</v>
       </c>
       <c r="H1287" t="n">
         <v>62941</v>
@@ -37721,7 +37721,7 @@
         <v>14.5</v>
       </c>
       <c r="G1288" t="n">
-        <v>13.5464630126953</v>
+        <v>13.5464639663696</v>
       </c>
       <c r="H1288" t="n">
         <v>37653</v>
@@ -37750,7 +37750,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G1289" t="n">
-        <v>13.6398868560791</v>
+        <v>13.6398878097534</v>
       </c>
       <c r="H1289" t="n">
         <v>48281</v>
@@ -37837,7 +37837,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1292" t="n">
-        <v>14.0602931976318</v>
+        <v>14.0602941513062</v>
       </c>
       <c r="H1292" t="n">
         <v>38772</v>
@@ -37982,7 +37982,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1297" t="n">
-        <v>14.1070070266724</v>
+        <v>14.107006072998</v>
       </c>
       <c r="H1297" t="n">
         <v>52067</v>
@@ -38098,7 +38098,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1301" t="n">
-        <v>14.0602931976318</v>
+        <v>14.0602941513062</v>
       </c>
       <c r="H1301" t="n">
         <v>133291</v>
@@ -38243,7 +38243,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1306" t="n">
-        <v>14.574125289917</v>
+        <v>14.5741262435913</v>
       </c>
       <c r="H1306" t="n">
         <v>137379</v>
@@ -38359,7 +38359,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1310" t="n">
-        <v>14.0602931976318</v>
+        <v>14.0602941513062</v>
       </c>
       <c r="H1310" t="n">
         <v>75144</v>
@@ -38446,7 +38446,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G1313" t="n">
-        <v>14.0602931976318</v>
+        <v>14.0602941513062</v>
       </c>
       <c r="H1313" t="n">
         <v>81324</v>
@@ -38475,7 +38475,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1314" t="n">
-        <v>14.1070070266724</v>
+        <v>14.107006072998</v>
       </c>
       <c r="H1314" t="n">
         <v>141761</v>
@@ -38504,7 +38504,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1315" t="n">
-        <v>14.1070070266724</v>
+        <v>14.107006072998</v>
       </c>
       <c r="H1315" t="n">
         <v>94574</v>
@@ -38562,7 +38562,7 @@
         <v>15.5</v>
       </c>
       <c r="G1317" t="n">
-        <v>14.4807004928589</v>
+        <v>14.4807014465332</v>
       </c>
       <c r="H1317" t="n">
         <v>46874</v>
@@ -38707,7 +38707,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1322" t="n">
-        <v>14.6675481796265</v>
+        <v>14.6675491333008</v>
       </c>
       <c r="H1322" t="n">
         <v>27348</v>
@@ -38736,7 +38736,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1323" t="n">
-        <v>14.574125289917</v>
+        <v>14.5741262435913</v>
       </c>
       <c r="H1323" t="n">
         <v>36668</v>
@@ -38765,7 +38765,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1324" t="n">
-        <v>14.6675481796265</v>
+        <v>14.6675491333008</v>
       </c>
       <c r="H1324" t="n">
         <v>41138</v>
@@ -38794,7 +38794,7 @@
         <v>15.75</v>
       </c>
       <c r="G1325" t="n">
-        <v>14.714262008667</v>
+        <v>14.7142629623413</v>
       </c>
       <c r="H1325" t="n">
         <v>1075608</v>
@@ -38823,7 +38823,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1326" t="n">
-        <v>14.7609729766846</v>
+        <v>14.7609739303589</v>
       </c>
       <c r="H1326" t="n">
         <v>33249</v>
@@ -38910,7 +38910,7 @@
         <v>15.5</v>
       </c>
       <c r="G1329" t="n">
-        <v>14.4807004928589</v>
+        <v>14.4807014465332</v>
       </c>
       <c r="H1329" t="n">
         <v>26684</v>
@@ -38968,7 +38968,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G1331" t="n">
-        <v>14.7609729766846</v>
+        <v>14.7609739303589</v>
       </c>
       <c r="H1331" t="n">
         <v>50318</v>
@@ -39026,7 +39026,7 @@
         <v>16.75</v>
       </c>
       <c r="G1333" t="n">
-        <v>15.6485004425049</v>
+        <v>15.6484994888306</v>
       </c>
       <c r="H1333" t="n">
         <v>146955</v>
@@ -39055,7 +39055,7 @@
         <v>17</v>
       </c>
       <c r="G1334" t="n">
-        <v>15.8820610046387</v>
+        <v>15.8820581436157</v>
       </c>
       <c r="H1334" t="n">
         <v>62603</v>
@@ -39113,7 +39113,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1336" t="n">
-        <v>15.9567966461182</v>
+        <v>15.9567975997925</v>
       </c>
       <c r="H1336" t="n">
         <v>60305</v>
@@ -39200,7 +39200,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1339" t="n">
-        <v>16.1062774658203</v>
+        <v>16.1062793731689</v>
       </c>
       <c r="H1339" t="n">
         <v>52146</v>
@@ -39229,7 +39229,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>16.2557563781738</v>
+        <v>16.2557544708252</v>
       </c>
       <c r="H1340" t="n">
         <v>57410</v>
@@ -39287,7 +39287,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.2931251525879</v>
+        <v>16.2931270599365</v>
       </c>
       <c r="H1342" t="n">
         <v>34303</v>
@@ -39345,7 +39345,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1344" t="n">
-        <v>16.143648147583</v>
+        <v>16.1436462402344</v>
       </c>
       <c r="H1344" t="n">
         <v>56638</v>
@@ -39374,7 +39374,7 @@
         <v>16.9200000762939</v>
       </c>
       <c r="G1345" t="n">
-        <v>15.8073205947876</v>
+        <v>15.8073215484619</v>
       </c>
       <c r="H1345" t="n">
         <v>80732</v>
@@ -39403,7 +39403,7 @@
         <v>17</v>
       </c>
       <c r="G1346" t="n">
-        <v>15.8820610046387</v>
+        <v>15.8820581436157</v>
       </c>
       <c r="H1346" t="n">
         <v>29061</v>
@@ -39432,7 +39432,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1347" t="n">
-        <v>15.7699508666992</v>
+        <v>15.7699518203735</v>
       </c>
       <c r="H1347" t="n">
         <v>19151</v>
@@ -39461,7 +39461,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1348" t="n">
-        <v>15.6952114105225</v>
+        <v>15.6952095031738</v>
       </c>
       <c r="H1348" t="n">
         <v>50373</v>
@@ -39577,7 +39577,7 @@
         <v>16.5</v>
       </c>
       <c r="G1352" t="n">
-        <v>15.4149417877197</v>
+        <v>15.4149408340454</v>
       </c>
       <c r="H1352" t="n">
         <v>15347</v>
@@ -39635,7 +39635,7 @@
         <v>16.6800003051758</v>
       </c>
       <c r="G1354" t="n">
-        <v>15.5831031799316</v>
+        <v>15.5831022262573</v>
       </c>
       <c r="H1354" t="n">
         <v>28026</v>
@@ -39664,7 +39664,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G1355" t="n">
-        <v>15.1533517837524</v>
+        <v>15.1533527374268</v>
       </c>
       <c r="H1355" t="n">
         <v>25092</v>
@@ -39925,7 +39925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1364" t="n">
-        <v>15.6952114105225</v>
+        <v>15.6952095031738</v>
       </c>
       <c r="H1364" t="n">
         <v>54661</v>
@@ -39983,7 +39983,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1366" t="n">
-        <v>15.6578435897827</v>
+        <v>15.6578426361084</v>
       </c>
       <c r="H1366" t="n">
         <v>27677</v>
@@ -40070,7 +40070,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1369" t="n">
-        <v>15.8616733551025</v>
+        <v>15.8616743087769</v>
       </c>
       <c r="H1369" t="n">
         <v>26022</v>
@@ -40099,7 +40099,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1370" t="n">
-        <v>15.8427457809448</v>
+        <v>15.8427448272705</v>
       </c>
       <c r="H1370" t="n">
         <v>43040</v>
@@ -40157,7 +40157,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1372" t="n">
-        <v>15.3695430755615</v>
+        <v>15.3695440292358</v>
       </c>
       <c r="H1372" t="n">
         <v>50885</v>
@@ -40215,7 +40215,7 @@
         <v>16.5799999237061</v>
       </c>
       <c r="G1374" t="n">
-        <v>15.6913185119629</v>
+        <v>15.6913194656372</v>
       </c>
       <c r="H1374" t="n">
         <v>14243</v>
@@ -40302,7 +40302,7 @@
         <v>16</v>
       </c>
       <c r="G1377" t="n">
-        <v>15.1424074172974</v>
+        <v>15.1424083709717</v>
       </c>
       <c r="H1377" t="n">
         <v>79159</v>
@@ -40389,7 +40389,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.7102470397949</v>
+        <v>15.7102460861206</v>
       </c>
       <c r="H1380" t="n">
         <v>25395</v>
@@ -40447,7 +40447,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.1266670227051</v>
+        <v>16.1266651153564</v>
       </c>
       <c r="H1382" t="n">
         <v>47756</v>
@@ -40476,7 +40476,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1383" t="n">
-        <v>16.1266670227051</v>
+        <v>16.1266651153564</v>
       </c>
       <c r="H1383" t="n">
         <v>57764</v>
@@ -40534,7 +40534,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1385" t="n">
-        <v>15.8427457809448</v>
+        <v>15.8427448272705</v>
       </c>
       <c r="H1385" t="n">
         <v>12320</v>
@@ -40563,7 +40563,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.1077365875244</v>
+        <v>16.107738494873</v>
       </c>
       <c r="H1386" t="n">
         <v>15100</v>
@@ -40592,7 +40592,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1387" t="n">
-        <v>16.1077365875244</v>
+        <v>16.107738494873</v>
       </c>
       <c r="H1387" t="n">
         <v>39809</v>
@@ -40621,7 +40621,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1388" t="n">
-        <v>15.8806028366089</v>
+        <v>15.8806018829346</v>
       </c>
       <c r="H1388" t="n">
         <v>33594</v>
@@ -40650,7 +40650,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1389" t="n">
-        <v>15.8427457809448</v>
+        <v>15.8427448272705</v>
       </c>
       <c r="H1389" t="n">
         <v>18004</v>
@@ -40737,7 +40737,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1392" t="n">
-        <v>16.1266670227051</v>
+        <v>16.1266651153564</v>
       </c>
       <c r="H1392" t="n">
         <v>17745</v>
@@ -40766,7 +40766,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1393" t="n">
-        <v>16.1077365875244</v>
+        <v>16.107738494873</v>
       </c>
       <c r="H1393" t="n">
         <v>50197</v>
@@ -40795,7 +40795,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.1455936431885</v>
+        <v>16.1455917358398</v>
       </c>
       <c r="H1394" t="n">
         <v>27774</v>
@@ -40853,7 +40853,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1396" t="n">
-        <v>16.1077365875244</v>
+        <v>16.107738494873</v>
       </c>
       <c r="H1396" t="n">
         <v>15189</v>
@@ -40882,7 +40882,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1397" t="n">
-        <v>16.3348712921143</v>
+        <v>16.3348731994629</v>
       </c>
       <c r="H1397" t="n">
         <v>23638</v>
@@ -40940,7 +40940,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1399" t="n">
-        <v>16.4105854034424</v>
+        <v>16.4105834960938</v>
       </c>
       <c r="H1399" t="n">
         <v>17766</v>
@@ -40969,7 +40969,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1400" t="n">
-        <v>16.4295139312744</v>
+        <v>16.4295120239258</v>
       </c>
       <c r="H1400" t="n">
         <v>17192</v>
@@ -41085,7 +41085,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1404" t="n">
-        <v>17.0919952392578</v>
+        <v>17.0919933319092</v>
       </c>
       <c r="H1404" t="n">
         <v>22603</v>
@@ -41230,7 +41230,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.7134342193604</v>
+        <v>16.7134323120117</v>
       </c>
       <c r="H1409" t="n">
         <v>39032</v>
@@ -41288,7 +41288,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.8459300994873</v>
+        <v>16.8459281921387</v>
       </c>
       <c r="H1411" t="n">
         <v>23036</v>
@@ -41404,7 +41404,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1415" t="n">
-        <v>17.3759155273438</v>
+        <v>17.3759136199951</v>
       </c>
       <c r="H1415" t="n">
         <v>25055</v>
@@ -41462,7 +41462,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1417" t="n">
-        <v>17.6219806671143</v>
+        <v>17.621976852417</v>
       </c>
       <c r="H1417" t="n">
         <v>50571</v>
@@ -41491,7 +41491,7 @@
         <v>18.5</v>
       </c>
       <c r="G1418" t="n">
-        <v>17.5084095001221</v>
+        <v>17.5084075927734</v>
       </c>
       <c r="H1418" t="n">
         <v>22090</v>
@@ -41520,7 +41520,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1419" t="n">
-        <v>17.6030502319336</v>
+        <v>17.6030521392822</v>
       </c>
       <c r="H1419" t="n">
         <v>14750</v>
@@ -41607,7 +41607,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1422" t="n">
-        <v>17.3380565643311</v>
+        <v>17.3380546569824</v>
       </c>
       <c r="H1422" t="n">
         <v>17570</v>
@@ -41694,7 +41694,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1425" t="n">
-        <v>17.16770362854</v>
+        <v>17.1677055358887</v>
       </c>
       <c r="H1425" t="n">
         <v>15269</v>
@@ -41839,7 +41839,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1430" t="n">
-        <v>16.8837833404541</v>
+        <v>16.8837852478027</v>
       </c>
       <c r="H1430" t="n">
         <v>15319</v>
@@ -41897,7 +41897,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1432" t="n">
-        <v>17.319128036499</v>
+        <v>17.3191299438477</v>
       </c>
       <c r="H1432" t="n">
         <v>15682</v>
@@ -41926,7 +41926,7 @@
         <v>18.5</v>
       </c>
       <c r="G1433" t="n">
-        <v>17.5084095001221</v>
+        <v>17.5084075927734</v>
       </c>
       <c r="H1433" t="n">
         <v>34242</v>
@@ -42013,7 +42013,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1436" t="n">
-        <v>17.7355461120605</v>
+        <v>17.7355442047119</v>
       </c>
       <c r="H1436" t="n">
         <v>17890</v>
@@ -42071,7 +42071,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1438" t="n">
-        <v>17.8869686126709</v>
+        <v>17.8869705200195</v>
       </c>
       <c r="H1438" t="n">
         <v>22975</v>
@@ -42100,7 +42100,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1439" t="n">
-        <v>18.2844562530518</v>
+        <v>18.2844581604004</v>
       </c>
       <c r="H1439" t="n">
         <v>42302</v>
@@ -42245,7 +42245,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1444" t="n">
-        <v>18.568380355835</v>
+        <v>18.5683784484863</v>
       </c>
       <c r="H1444" t="n">
         <v>37661</v>
@@ -42477,7 +42477,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.2119293212891</v>
+        <v>19.2119274139404</v>
       </c>
       <c r="H1452" t="n">
         <v>26109</v>
@@ -42535,7 +42535,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1454" t="n">
-        <v>18.6440906524658</v>
+        <v>18.6440925598145</v>
       </c>
       <c r="H1454" t="n">
         <v>41807</v>
@@ -42564,7 +42564,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>18.5494518280029</v>
+        <v>18.5494499206543</v>
       </c>
       <c r="H1455" t="n">
         <v>49974</v>
@@ -42709,7 +42709,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1460" t="n">
-        <v>17.7734031677246</v>
+        <v>17.773401260376</v>
       </c>
       <c r="H1460" t="n">
         <v>68439</v>
@@ -42738,7 +42738,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1461" t="n">
-        <v>17.7355461120605</v>
+        <v>17.7355442047119</v>
       </c>
       <c r="H1461" t="n">
         <v>44118</v>
@@ -42796,7 +42796,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1463" t="n">
-        <v>17.7355461120605</v>
+        <v>17.7355442047119</v>
       </c>
       <c r="H1463" t="n">
         <v>23394</v>
@@ -42854,7 +42854,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1465" t="n">
-        <v>17.7355461120605</v>
+        <v>17.7355442047119</v>
       </c>
       <c r="H1465" t="n">
         <v>40287</v>
@@ -42883,7 +42883,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1466" t="n">
-        <v>17.7544727325439</v>
+        <v>17.7544746398926</v>
       </c>
       <c r="H1466" t="n">
         <v>29156</v>
@@ -42941,7 +42941,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.1141052246094</v>
+        <v>18.114107131958</v>
       </c>
       <c r="H1468" t="n">
         <v>31591</v>
@@ -42970,7 +42970,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1469" t="n">
-        <v>17.8301849365234</v>
+        <v>17.8301868438721</v>
       </c>
       <c r="H1469" t="n">
         <v>20997</v>
@@ -43028,7 +43028,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1471" t="n">
-        <v>18.6440906524658</v>
+        <v>18.6440925598145</v>
       </c>
       <c r="H1471" t="n">
         <v>70480</v>
@@ -43086,7 +43086,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1473" t="n">
-        <v>18.8522987365723</v>
+        <v>18.8522968292236</v>
       </c>
       <c r="H1473" t="n">
         <v>28747</v>
@@ -43260,7 +43260,7 @@
         <v>19.9200000762939</v>
       </c>
       <c r="G1479" t="n">
-        <v>18.8522987365723</v>
+        <v>18.8522968292236</v>
       </c>
       <c r="H1479" t="n">
         <v>26838</v>
@@ -43550,7 +43550,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.7576560974121</v>
+        <v>18.7576599121094</v>
       </c>
       <c r="H1489" t="n">
         <v>39485</v>
@@ -43666,7 +43666,7 @@
         <v>21</v>
       </c>
       <c r="G1493" t="n">
-        <v>19.8744087219238</v>
+        <v>19.8744106292725</v>
       </c>
       <c r="H1493" t="n">
         <v>196630</v>
@@ -43811,7 +43811,7 @@
         <v>22.25</v>
       </c>
       <c r="G1498" t="n">
-        <v>21.0574111938477</v>
+        <v>21.0574131011963</v>
       </c>
       <c r="H1498" t="n">
         <v>91396</v>
@@ -43840,7 +43840,7 @@
         <v>22.5</v>
       </c>
       <c r="G1499" t="n">
-        <v>21.2940101623535</v>
+        <v>21.2940120697021</v>
       </c>
       <c r="H1499" t="n">
         <v>80065</v>
@@ -43869,7 +43869,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1500" t="n">
-        <v>20.5368919372559</v>
+        <v>20.5368938446045</v>
       </c>
       <c r="H1500" t="n">
         <v>115458</v>
@@ -43927,7 +43927,7 @@
         <v>21.4500007629395</v>
       </c>
       <c r="G1502" t="n">
-        <v>20.30029296875</v>
+        <v>20.3002910614014</v>
       </c>
       <c r="H1502" t="n">
         <v>89734</v>
@@ -43956,7 +43956,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1503" t="n">
-        <v>20.5368919372559</v>
+        <v>20.5368938446045</v>
       </c>
       <c r="H1503" t="n">
         <v>221886</v>
@@ -43985,7 +43985,7 @@
         <v>22</v>
       </c>
       <c r="G1504" t="n">
-        <v>20.8208103179932</v>
+        <v>20.8208122253418</v>
       </c>
       <c r="H1504" t="n">
         <v>142844</v>
@@ -44014,7 +44014,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.6851291656494</v>
+        <v>19.685131072998</v>
       </c>
       <c r="H1505" t="n">
         <v>1000975</v>
@@ -44043,7 +44043,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1506" t="n">
-        <v>20.2529697418213</v>
+        <v>20.2529716491699</v>
       </c>
       <c r="H1506" t="n">
         <v>111627</v>
@@ -44072,7 +44072,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1507" t="n">
-        <v>19.9690494537354</v>
+        <v>19.969051361084</v>
       </c>
       <c r="H1507" t="n">
         <v>162332</v>
@@ -44130,7 +44130,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1509" t="n">
-        <v>19.2119293212891</v>
+        <v>19.2119274139404</v>
       </c>
       <c r="H1509" t="n">
         <v>72152</v>
@@ -44159,7 +44159,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1510" t="n">
-        <v>19.6851291656494</v>
+        <v>19.685131072998</v>
       </c>
       <c r="H1510" t="n">
         <v>29511</v>
@@ -44391,7 +44391,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1518" t="n">
-        <v>19.6851291656494</v>
+        <v>19.685131072998</v>
       </c>
       <c r="H1518" t="n">
         <v>118921</v>
@@ -44420,7 +44420,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1519" t="n">
-        <v>19.2119293212891</v>
+        <v>19.2119274139404</v>
       </c>
       <c r="H1519" t="n">
         <v>36403</v>
@@ -44507,7 +44507,7 @@
         <v>20.6000003814697</v>
       </c>
       <c r="G1522" t="n">
-        <v>19.4958534240723</v>
+        <v>19.4958515167236</v>
       </c>
       <c r="H1522" t="n">
         <v>25370</v>
@@ -44536,7 +44536,7 @@
         <v>20.7999992370605</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.6851291656494</v>
+        <v>19.685131072998</v>
       </c>
       <c r="H1523" t="n">
         <v>7067</v>
@@ -44594,7 +44594,7 @@
         <v>21</v>
       </c>
       <c r="G1525" t="n">
-        <v>19.8744087219238</v>
+        <v>19.8744106292725</v>
       </c>
       <c r="H1525" t="n">
         <v>28738</v>
@@ -44623,7 +44623,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>20.0163726806641</v>
+        <v>20.0163707733154</v>
       </c>
       <c r="H1526" t="n">
         <v>44752</v>
@@ -44797,7 +44797,7 @@
         <v>19.8199996948242</v>
       </c>
       <c r="G1532" t="n">
-        <v>18.7576560974121</v>
+        <v>18.7576599121094</v>
       </c>
       <c r="H1532" t="n">
         <v>37664</v>
@@ -45029,7 +45029,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1540" t="n">
-        <v>18.8712253570557</v>
+        <v>18.8712272644043</v>
       </c>
       <c r="H1540" t="n">
         <v>24493</v>
@@ -45087,7 +45087,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1542" t="n">
-        <v>17.9058990478516</v>
+        <v>17.9058952331543</v>
       </c>
       <c r="H1542" t="n">
         <v>56101</v>
@@ -45232,7 +45232,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1547" t="n">
-        <v>17.9437503814697</v>
+        <v>17.9437522888184</v>
       </c>
       <c r="H1547" t="n">
         <v>34573</v>
@@ -45290,7 +45290,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1549" t="n">
-        <v>17.9058990478516</v>
+        <v>17.9058952331543</v>
       </c>
       <c r="H1549" t="n">
         <v>44274</v>
@@ -45348,7 +45348,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1551" t="n">
-        <v>17.1298484802246</v>
+        <v>17.1298503875732</v>
       </c>
       <c r="H1551" t="n">
         <v>55702</v>
@@ -45406,7 +45406,7 @@
         <v>17.0799999237061</v>
       </c>
       <c r="G1553" t="n">
-        <v>16.1645202636719</v>
+        <v>16.1645221710205</v>
       </c>
       <c r="H1553" t="n">
         <v>87387</v>
@@ -45493,7 +45493,7 @@
         <v>17.5400009155273</v>
       </c>
       <c r="G1556" t="n">
-        <v>16.5998630523682</v>
+        <v>16.5998649597168</v>
       </c>
       <c r="H1556" t="n">
         <v>109612</v>
@@ -45580,7 +45580,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1559" t="n">
-        <v>16.9405708312988</v>
+        <v>16.9405689239502</v>
       </c>
       <c r="H1559" t="n">
         <v>59330</v>
@@ -45725,7 +45725,7 @@
         <v>17.6800003051758</v>
       </c>
       <c r="G1564" t="n">
-        <v>16.7323608398438</v>
+        <v>16.7323627471924</v>
       </c>
       <c r="H1564" t="n">
         <v>49800</v>
@@ -45899,7 +45899,7 @@
         <v>16.7800006866455</v>
       </c>
       <c r="G1570" t="n">
-        <v>15.8806028366089</v>
+        <v>15.8806018829346</v>
       </c>
       <c r="H1570" t="n">
         <v>32668</v>
@@ -45928,7 +45928,7 @@
         <v>16.0200004577637</v>
       </c>
       <c r="G1571" t="n">
-        <v>15.1613359451294</v>
+        <v>15.1613368988037</v>
       </c>
       <c r="H1571" t="n">
         <v>58682</v>
@@ -45986,7 +45986,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G1573" t="n">
-        <v>14.3852882385254</v>
+        <v>14.3852872848511</v>
       </c>
       <c r="H1573" t="n">
         <v>97495</v>
@@ -46044,7 +46044,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G1575" t="n">
-        <v>14.8774156570435</v>
+        <v>14.8774166107178</v>
       </c>
       <c r="H1575" t="n">
         <v>43208</v>
@@ -46073,7 +46073,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1576" t="n">
-        <v>14.9720554351807</v>
+        <v>14.972056388855</v>
       </c>
       <c r="H1576" t="n">
         <v>78244</v>
@@ -46247,7 +46247,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1582" t="n">
-        <v>15.9184560775757</v>
+        <v>15.91845703125</v>
       </c>
       <c r="H1582" t="n">
         <v>27830</v>
@@ -46276,7 +46276,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.1266670227051</v>
+        <v>16.1266651153564</v>
       </c>
       <c r="H1583" t="n">
         <v>22015</v>
@@ -46363,7 +46363,7 @@
         <v>17.3799991607666</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.4484386444092</v>
+        <v>16.4484405517578</v>
       </c>
       <c r="H1586" t="n">
         <v>15043</v>
@@ -46392,7 +46392,7 @@
         <v>17.5</v>
       </c>
       <c r="G1587" t="n">
-        <v>16.5620098114014</v>
+        <v>16.5620079040527</v>
       </c>
       <c r="H1587" t="n">
         <v>24152</v>
@@ -46421,7 +46421,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1588" t="n">
-        <v>16.3916549682617</v>
+        <v>16.3916568756104</v>
       </c>
       <c r="H1588" t="n">
         <v>22030</v>
@@ -46537,7 +46537,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1592" t="n">
-        <v>15.8616733551025</v>
+        <v>15.8616743087769</v>
       </c>
       <c r="H1592" t="n">
         <v>61968</v>
@@ -46566,7 +46566,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1593" t="n">
-        <v>15.7102470397949</v>
+        <v>15.7102460861206</v>
       </c>
       <c r="H1593" t="n">
         <v>51939</v>
@@ -46595,7 +46595,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1594" t="n">
-        <v>15.3884725570679</v>
+        <v>15.3884716033936</v>
       </c>
       <c r="H1594" t="n">
         <v>27567</v>
@@ -46653,7 +46653,7 @@
         <v>16</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.1424074172974</v>
+        <v>15.1424083709717</v>
       </c>
       <c r="H1596" t="n">
         <v>21153</v>
@@ -46682,7 +46682,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G1597" t="n">
-        <v>14.8584890365601</v>
+        <v>14.8584871292114</v>
       </c>
       <c r="H1597" t="n">
         <v>51943</v>
@@ -46711,7 +46711,7 @@
         <v>16</v>
       </c>
       <c r="G1598" t="n">
-        <v>15.1424074172974</v>
+        <v>15.1424083709717</v>
       </c>
       <c r="H1598" t="n">
         <v>36577</v>
@@ -46740,7 +46740,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1599" t="n">
-        <v>15.2181205749512</v>
+        <v>15.2181196212769</v>
       </c>
       <c r="H1599" t="n">
         <v>10911</v>
@@ -46769,7 +46769,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.3884725570679</v>
+        <v>15.3884716033936</v>
       </c>
       <c r="H1600" t="n">
         <v>21816</v>
@@ -46856,7 +46856,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1603" t="n">
-        <v>15.2181205749512</v>
+        <v>15.2181196212769</v>
       </c>
       <c r="H1603" t="n">
         <v>60493</v>
@@ -46885,7 +46885,7 @@
         <v>15.8199996948242</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.9720554351807</v>
+        <v>14.972056388855</v>
       </c>
       <c r="H1604" t="n">
         <v>23750</v>
@@ -46914,7 +46914,7 @@
         <v>15.6400003433228</v>
       </c>
       <c r="G1605" t="n">
-        <v>14.8017044067383</v>
+        <v>14.801703453064</v>
       </c>
       <c r="H1605" t="n">
         <v>24387</v>
@@ -46972,7 +46972,7 @@
         <v>15.6199998855591</v>
       </c>
       <c r="G1607" t="n">
-        <v>14.7827758789062</v>
+        <v>14.7827749252319</v>
       </c>
       <c r="H1607" t="n">
         <v>28534</v>
@@ -47001,7 +47001,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1608" t="n">
-        <v>15.5209665298462</v>
+        <v>15.5209674835205</v>
       </c>
       <c r="H1608" t="n">
         <v>83474</v>
@@ -47030,7 +47030,7 @@
         <v>16.7399997711182</v>
       </c>
       <c r="G1609" t="n">
-        <v>15.8427457809448</v>
+        <v>15.8427448272705</v>
       </c>
       <c r="H1609" t="n">
         <v>40978</v>
@@ -47088,7 +47088,7 @@
         <v>16.7600002288818</v>
       </c>
       <c r="G1611" t="n">
-        <v>15.8616733551025</v>
+        <v>15.8616743087769</v>
       </c>
       <c r="H1611" t="n">
         <v>41397</v>
@@ -47117,7 +47117,7 @@
         <v>16.8799991607666</v>
       </c>
       <c r="G1612" t="n">
-        <v>15.9752407073975</v>
+        <v>15.9752397537231</v>
       </c>
       <c r="H1612" t="n">
         <v>16554</v>
@@ -47175,7 +47175,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>15.7102470397949</v>
+        <v>15.7102460861206</v>
       </c>
       <c r="H1614" t="n">
         <v>27465</v>
@@ -47204,7 +47204,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G1615" t="n">
-        <v>15.123480796814</v>
+        <v>15.1234798431396</v>
       </c>
       <c r="H1615" t="n">
         <v>52910</v>
@@ -47233,7 +47233,7 @@
         <v>16.2399997711182</v>
       </c>
       <c r="G1616" t="n">
-        <v>15.3695430755615</v>
+        <v>15.3695440292358</v>
       </c>
       <c r="H1616" t="n">
         <v>29844</v>
@@ -47262,7 +47262,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1617" t="n">
-        <v>15.5209665298462</v>
+        <v>15.5209674835205</v>
       </c>
       <c r="H1617" t="n">
         <v>31061</v>
@@ -47291,7 +47291,7 @@
         <v>15.8400001525879</v>
       </c>
       <c r="G1618" t="n">
-        <v>14.9909839630127</v>
+        <v>14.990984916687</v>
       </c>
       <c r="H1618" t="n">
         <v>45709</v>
@@ -80183,6 +80183,35 @@
         <v>29750</v>
       </c>
       <c r="I2752" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2753" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C2753" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D2753" t="n">
+        <v>61.0999984741211</v>
+      </c>
+      <c r="E2753" t="n">
+        <v>59.2000007629395</v>
+      </c>
+      <c r="F2753" t="n">
+        <v>60.2999992370605</v>
+      </c>
+      <c r="G2753" t="n">
+        <v>60.2999992370605</v>
+      </c>
+      <c r="H2753" t="n">
+        <v>38447</v>
+      </c>
+      <c r="I2753" t="s">
         <v>9</v>
       </c>
     </row>
